--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124900661</v>
+        <v>124900313</v>
       </c>
       <c r="B3" t="n">
         <v>79891</v>
@@ -823,14 +823,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599813</v>
+        <v>599854</v>
       </c>
       <c r="R3" t="n">
-        <v>6923781</v>
+        <v>6923776</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1015,7 +1015,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124900313</v>
+        <v>124900661</v>
       </c>
       <c r="B5" t="n">
         <v>79891</v>
@@ -1051,14 +1051,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599854</v>
+        <v>599813</v>
       </c>
       <c r="R5" t="n">
-        <v>6923776</v>
+        <v>6923781</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1361,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124898060</v>
+        <v>124900786</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,37 +1377,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599916</v>
+        <v>599791</v>
       </c>
       <c r="R8" t="n">
-        <v>6923847</v>
+        <v>6923786</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1436,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,22 +1466,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124898571</v>
+        <v>124898060</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,42 +1494,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599904</v>
+        <v>599916</v>
       </c>
       <c r="R9" t="n">
-        <v>6923812</v>
+        <v>6923847</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,12 +1563,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:05</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,22 +1578,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124900786</v>
+        <v>124898571</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,16 +1606,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1631,19 +1626,19 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599791</v>
+        <v>599904</v>
       </c>
       <c r="R10" t="n">
-        <v>6923786</v>
+        <v>6923812</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1675,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1685,7 +1680,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2896,10 +2896,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124901624</v>
+        <v>124900465</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2908,47 +2908,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599703</v>
+        <v>599856</v>
       </c>
       <c r="R21" t="n">
-        <v>6923832</v>
+        <v>6923803</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2980,7 +2971,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2990,7 +2981,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3005,22 +2996,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124900465</v>
+        <v>124898290</v>
       </c>
       <c r="B22" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3033,34 +3024,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>599856</v>
+        <v>599911</v>
       </c>
       <c r="R22" t="n">
-        <v>6923803</v>
+        <v>6923836</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3092,7 +3088,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3102,7 +3098,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3117,22 +3118,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124898290</v>
+        <v>124901624</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3141,43 +3142,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>599911</v>
+        <v>599703</v>
       </c>
       <c r="R23" t="n">
-        <v>6923836</v>
+        <v>6923832</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3209,7 +3214,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3219,12 +3224,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3704,10 +3704,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124898316</v>
+        <v>124899616</v>
       </c>
       <c r="B28" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3720,34 +3720,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>599918</v>
+        <v>599899</v>
       </c>
       <c r="R28" t="n">
-        <v>6923822</v>
+        <v>6923765</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3804,22 +3804,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124899616</v>
+        <v>124898316</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3832,34 +3832,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>599899</v>
+        <v>599918</v>
       </c>
       <c r="R29" t="n">
-        <v>6923765</v>
+        <v>6923822</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3916,12 +3916,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -5081,10 +5081,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124899644</v>
+        <v>124898096</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5097,34 +5097,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>599898</v>
+        <v>599930</v>
       </c>
       <c r="R40" t="n">
-        <v>6923799</v>
+        <v>6923840</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5181,22 +5181,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124901634</v>
+        <v>124899644</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5205,38 +5205,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>599734</v>
+        <v>599898</v>
       </c>
       <c r="R41" t="n">
-        <v>6923810</v>
+        <v>6923799</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5268,7 +5268,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5293,22 +5293,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124900764</v>
+        <v>124901634</v>
       </c>
       <c r="B42" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5317,25 +5317,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>599814</v>
+        <v>599734</v>
       </c>
       <c r="R42" t="n">
-        <v>6923824</v>
+        <v>6923810</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5417,10 +5417,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124898096</v>
+        <v>124900764</v>
       </c>
       <c r="B43" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5433,21 +5433,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5457,10 +5457,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>599930</v>
+        <v>599814</v>
       </c>
       <c r="R43" t="n">
-        <v>6923840</v>
+        <v>6923824</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124899421</v>
+        <v>124900313</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599899</v>
+        <v>599854</v>
       </c>
       <c r="R2" t="n">
-        <v>6923798</v>
+        <v>6923776</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124900313</v>
+        <v>124901922</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +799,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599854</v>
+        <v>599783</v>
       </c>
       <c r="R3" t="n">
-        <v>6923776</v>
+        <v>6923858</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124901922</v>
+        <v>124900661</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,42 +915,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599783</v>
+        <v>599813</v>
       </c>
       <c r="R4" t="n">
-        <v>6923858</v>
+        <v>6923781</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124900661</v>
+        <v>124899421</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,34 +1031,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599813</v>
+        <v>599899</v>
       </c>
       <c r="R5" t="n">
-        <v>6923781</v>
+        <v>6923798</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,12 +1115,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1361,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124900786</v>
+        <v>124898060</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,42 +1377,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599791</v>
+        <v>599916</v>
       </c>
       <c r="R8" t="n">
-        <v>6923786</v>
+        <v>6923847</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1441,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,22 +1461,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124898060</v>
+        <v>124898571</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,37 +1489,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599916</v>
+        <v>599904</v>
       </c>
       <c r="R9" t="n">
-        <v>6923847</v>
+        <v>6923812</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,7 +1563,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,22 +1583,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124898571</v>
+        <v>124900786</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,16 +1611,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1626,19 +1631,19 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599904</v>
+        <v>599791</v>
       </c>
       <c r="R10" t="n">
-        <v>6923812</v>
+        <v>6923786</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1670,7 +1675,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,12 +1685,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:05</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2896,10 +2896,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124900465</v>
+        <v>124901624</v>
       </c>
       <c r="B21" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2908,38 +2908,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599856</v>
+        <v>599703</v>
       </c>
       <c r="R21" t="n">
-        <v>6923803</v>
+        <v>6923832</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2971,7 +2980,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2981,7 +2990,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2996,22 +3005,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124898290</v>
+        <v>124900465</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3024,39 +3033,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>599911</v>
+        <v>599856</v>
       </c>
       <c r="R22" t="n">
-        <v>6923836</v>
+        <v>6923803</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3088,7 +3092,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3098,12 +3102,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3118,22 +3117,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124901624</v>
+        <v>124898290</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3142,47 +3141,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>599703</v>
+        <v>599911</v>
       </c>
       <c r="R23" t="n">
-        <v>6923832</v>
+        <v>6923836</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3214,7 +3209,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3224,7 +3219,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -4517,10 +4517,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124899503</v>
+        <v>124900330</v>
       </c>
       <c r="B35" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4533,21 +4533,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4557,10 +4557,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>599912</v>
+        <v>599899</v>
       </c>
       <c r="R35" t="n">
-        <v>6923800</v>
+        <v>6923798</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4617,22 +4617,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124900330</v>
+        <v>124899503</v>
       </c>
       <c r="B36" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4645,21 +4645,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>599899</v>
+        <v>599912</v>
       </c>
       <c r="R36" t="n">
-        <v>6923798</v>
+        <v>6923800</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4729,12 +4729,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -5081,10 +5081,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124898096</v>
+        <v>124899644</v>
       </c>
       <c r="B40" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5097,34 +5097,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>599930</v>
+        <v>599898</v>
       </c>
       <c r="R40" t="n">
-        <v>6923840</v>
+        <v>6923799</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5181,22 +5181,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124899644</v>
+        <v>124898096</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5209,34 +5209,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>599898</v>
+        <v>599930</v>
       </c>
       <c r="R41" t="n">
-        <v>6923799</v>
+        <v>6923840</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5268,7 +5268,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5293,12 +5293,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5870,10 +5870,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124900226</v>
+        <v>124898191</v>
       </c>
       <c r="B47" t="n">
-        <v>79891</v>
+        <v>91673</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5882,43 +5882,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>898</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>599882</v>
+        <v>599930</v>
       </c>
       <c r="R47" t="n">
-        <v>6923778</v>
+        <v>6923840</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5950,7 +5945,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5960,12 +5955,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:43</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Över 20 apothecier</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5992,10 +5982,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124898191</v>
+        <v>124902015</v>
       </c>
       <c r="B48" t="n">
-        <v>91673</v>
+        <v>91012</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6004,38 +5994,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>599930</v>
+        <v>599777</v>
       </c>
       <c r="R48" t="n">
-        <v>6923840</v>
+        <v>6923857</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6067,7 +6057,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6077,7 +6067,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6092,22 +6082,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124902015</v>
+        <v>124900226</v>
       </c>
       <c r="B49" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6120,34 +6110,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>599777</v>
+        <v>599882</v>
       </c>
       <c r="R49" t="n">
-        <v>6923857</v>
+        <v>6923778</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6179,7 +6174,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6189,7 +6184,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Över 20 apothecier</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6204,12 +6204,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124900313</v>
+        <v>124899503</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599854</v>
+        <v>599912</v>
       </c>
       <c r="R2" t="n">
-        <v>6923776</v>
+        <v>6923800</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124901922</v>
+        <v>124901880</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,42 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599783</v>
+        <v>599771</v>
       </c>
       <c r="R3" t="n">
-        <v>6923858</v>
+        <v>6923841</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +872,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på asp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124900661</v>
+        <v>124900663</v>
       </c>
       <c r="B4" t="n">
         <v>79891</v>
@@ -939,14 +940,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599813</v>
+        <v>599824</v>
       </c>
       <c r="R4" t="n">
-        <v>6923781</v>
+        <v>6923802</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,22 +1004,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124899421</v>
+        <v>124901584</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,25 +1028,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1090,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124897942</v>
+        <v>124901679</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,39 +1144,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599929</v>
+        <v>599728</v>
       </c>
       <c r="R6" t="n">
-        <v>6923847</v>
+        <v>6923812</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,12 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,22 +1228,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124902691</v>
+        <v>124899644</v>
       </c>
       <c r="B7" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,34 +1256,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599798</v>
+        <v>599898</v>
       </c>
       <c r="R7" t="n">
-        <v>6923975</v>
+        <v>6923799</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124898060</v>
+        <v>124901624</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,41 +1364,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599916</v>
+        <v>599703</v>
       </c>
       <c r="R8" t="n">
-        <v>6923847</v>
+        <v>6923832</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,22 +1461,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124898571</v>
+        <v>124901922</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,43 +1485,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599904</v>
+        <v>599783</v>
       </c>
       <c r="R9" t="n">
-        <v>6923812</v>
+        <v>6923858</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,7 +1552,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,12 +1562,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:05</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,22 +1577,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124900786</v>
+        <v>124900294</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,43 +1601,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599791</v>
+        <v>599864</v>
       </c>
       <c r="R10" t="n">
-        <v>6923786</v>
+        <v>6923773</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1675,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1685,7 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1712,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124900663</v>
+        <v>124902839</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,34 +1726,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599824</v>
+        <v>599810</v>
       </c>
       <c r="R11" t="n">
-        <v>6923802</v>
+        <v>6923980</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1787,7 +1785,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1797,7 +1795,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1812,22 +1810,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124902765</v>
+        <v>124897942</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,42 +1834,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599800</v>
+        <v>599929</v>
       </c>
       <c r="R12" t="n">
-        <v>6923959</v>
+        <v>6923847</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,7 +1902,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1913,7 +1912,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1928,22 +1932,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124900294</v>
+        <v>124899196</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>91457</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,43 +1960,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599864</v>
+        <v>599888</v>
       </c>
       <c r="R13" t="n">
-        <v>6923773</v>
+        <v>6923798</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2024,7 +2019,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2034,7 +2029,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,22 +2044,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124900362</v>
+        <v>124899564</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2073,44 +2068,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599864</v>
+        <v>599910</v>
       </c>
       <c r="R14" t="n">
         <v>6923786</v>
@@ -2145,7 +2131,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2155,7 +2141,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,22 +2156,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124900025</v>
+        <v>124900863</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2194,42 +2180,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599878</v>
+        <v>599779</v>
       </c>
       <c r="R15" t="n">
-        <v>6923820</v>
+        <v>6923783</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2261,7 +2243,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2271,7 +2253,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2298,7 +2280,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124899798</v>
+        <v>124901767</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2333,19 +2315,19 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599883</v>
+        <v>599748</v>
       </c>
       <c r="R16" t="n">
-        <v>6923782</v>
+        <v>6923842</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2377,7 +2359,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2387,7 +2369,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2414,10 +2396,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124900827</v>
+        <v>124900773</v>
       </c>
       <c r="B17" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2430,39 +2412,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599787</v>
+        <v>599801</v>
       </c>
       <c r="R17" t="n">
-        <v>6923799</v>
+        <v>6923797</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2494,7 +2471,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2504,7 +2481,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2531,10 +2508,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124899839</v>
+        <v>124898316</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2547,39 +2524,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599893</v>
+        <v>599918</v>
       </c>
       <c r="R18" t="n">
-        <v>6923773</v>
+        <v>6923822</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2611,7 +2583,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2621,12 +2593,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:35</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2641,22 +2608,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124901921</v>
+        <v>124900661</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2665,47 +2632,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599742</v>
+        <v>599813</v>
       </c>
       <c r="R19" t="n">
-        <v>6923857</v>
+        <v>6923781</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2737,7 +2695,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2747,7 +2705,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2762,19 +2720,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124902509</v>
+        <v>124898290</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2810,19 +2768,19 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599754</v>
+        <v>599911</v>
       </c>
       <c r="R20" t="n">
-        <v>6923921</v>
+        <v>6923836</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2854,7 +2812,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2864,12 +2822,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2884,22 +2842,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124901624</v>
+        <v>124900465</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2908,47 +2866,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599703</v>
+        <v>599856</v>
       </c>
       <c r="R21" t="n">
-        <v>6923832</v>
+        <v>6923803</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2980,7 +2929,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2990,7 +2939,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3005,22 +2954,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124900465</v>
+        <v>124901921</v>
       </c>
       <c r="B22" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3029,38 +2978,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>599856</v>
+        <v>599742</v>
       </c>
       <c r="R22" t="n">
-        <v>6923803</v>
+        <v>6923857</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3092,7 +3050,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3102,7 +3060,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3117,22 +3075,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124898290</v>
+        <v>124898995</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3141,43 +3099,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>599911</v>
+        <v>599930</v>
       </c>
       <c r="R23" t="n">
-        <v>6923836</v>
+        <v>6923840</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3209,7 +3162,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3219,12 +3172,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3239,22 +3187,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124899564</v>
+        <v>124901780</v>
       </c>
       <c r="B24" t="n">
-        <v>91299</v>
+        <v>79891</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3267,21 +3215,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3291,10 +3239,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>599910</v>
+        <v>599756</v>
       </c>
       <c r="R24" t="n">
-        <v>6923786</v>
+        <v>6923823</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3326,7 +3274,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3336,7 +3284,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3363,10 +3311,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124898995</v>
+        <v>124899195</v>
       </c>
       <c r="B25" t="n">
-        <v>96979</v>
+        <v>91012</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3375,25 +3323,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3475,10 +3423,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124898168</v>
+        <v>124901634</v>
       </c>
       <c r="B26" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3487,38 +3435,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>599920</v>
+        <v>599734</v>
       </c>
       <c r="R26" t="n">
-        <v>6923834</v>
+        <v>6923810</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3550,7 +3498,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3560,7 +3508,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3575,22 +3523,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124898054</v>
+        <v>124900362</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3599,38 +3547,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>599930</v>
+        <v>599864</v>
       </c>
       <c r="R27" t="n">
-        <v>6923840</v>
+        <v>6923786</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3662,7 +3619,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3672,12 +3629,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3692,22 +3644,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124899616</v>
+        <v>124902765</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3716,38 +3668,42 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>599899</v>
+        <v>599800</v>
       </c>
       <c r="R28" t="n">
-        <v>6923765</v>
+        <v>6923959</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3779,7 +3735,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3789,7 +3745,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3804,22 +3760,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124898316</v>
+        <v>124901889</v>
       </c>
       <c r="B29" t="n">
-        <v>91299</v>
+        <v>79891</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3832,34 +3788,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>599918</v>
+        <v>599775</v>
       </c>
       <c r="R29" t="n">
-        <v>6923822</v>
+        <v>6923855</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3891,7 +3847,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3901,7 +3857,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3916,22 +3872,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124901679</v>
+        <v>124900018</v>
       </c>
       <c r="B30" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3944,34 +3900,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>599728</v>
+        <v>599883</v>
       </c>
       <c r="R30" t="n">
-        <v>6923812</v>
+        <v>6923768</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4003,7 +3959,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4013,7 +3969,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4028,22 +3984,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124902350</v>
+        <v>124899341</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>90977</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4052,62 +4008,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>599899</v>
+        <v>599908</v>
       </c>
       <c r="R31" t="n">
-        <v>6923798</v>
+        <v>6923811</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4139,7 +4071,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4149,12 +4081,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:17</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett hona födosöker I en gran.</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4169,22 +4096,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124901889</v>
+        <v>124899798</v>
       </c>
       <c r="B32" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4193,38 +4120,42 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>599775</v>
+        <v>599883</v>
       </c>
       <c r="R32" t="n">
-        <v>6923855</v>
+        <v>6923782</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4256,7 +4187,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4266,7 +4197,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4281,22 +4212,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124900018</v>
+        <v>124900226</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4309,34 +4240,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>599883</v>
+        <v>599882</v>
       </c>
       <c r="R33" t="n">
-        <v>6923768</v>
+        <v>6923778</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4368,7 +4304,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4378,7 +4314,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Över 20 apothecier</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4405,10 +4346,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124899341</v>
+        <v>124899421</v>
       </c>
       <c r="B34" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4417,25 +4358,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4445,10 +4386,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>599908</v>
+        <v>599899</v>
       </c>
       <c r="R34" t="n">
-        <v>6923811</v>
+        <v>6923798</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4480,7 +4421,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4490,7 +4431,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4505,22 +4446,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124900330</v>
+        <v>124902691</v>
       </c>
       <c r="B35" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4533,34 +4474,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>599899</v>
+        <v>599798</v>
       </c>
       <c r="R35" t="n">
-        <v>6923798</v>
+        <v>6923975</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4592,7 +4533,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4602,7 +4543,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4617,22 +4558,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124899503</v>
+        <v>124902509</v>
       </c>
       <c r="B36" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4645,34 +4586,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>599912</v>
+        <v>599754</v>
       </c>
       <c r="R36" t="n">
-        <v>6923800</v>
+        <v>6923921</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4704,7 +4650,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4714,7 +4660,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>18:29</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4729,22 +4680,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124902839</v>
+        <v>124899839</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4757,34 +4708,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>599810</v>
+        <v>599893</v>
       </c>
       <c r="R37" t="n">
-        <v>6923980</v>
+        <v>6923773</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4816,7 +4772,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4826,7 +4782,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4841,19 +4802,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124901767</v>
+        <v>124900025</v>
       </c>
       <c r="B38" t="n">
         <v>98101</v>
@@ -4888,19 +4849,19 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>599748</v>
+        <v>599878</v>
       </c>
       <c r="R38" t="n">
-        <v>6923842</v>
+        <v>6923820</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4932,7 +4893,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4942,7 +4903,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4969,10 +4930,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124901584</v>
+        <v>124900764</v>
       </c>
       <c r="B39" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4981,25 +4942,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5009,10 +4970,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>599899</v>
+        <v>599814</v>
       </c>
       <c r="R39" t="n">
-        <v>6923798</v>
+        <v>6923824</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5044,7 +5005,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5054,7 +5015,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5069,22 +5030,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124899644</v>
+        <v>124900786</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5097,34 +5058,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>599898</v>
+        <v>599791</v>
       </c>
       <c r="R40" t="n">
-        <v>6923799</v>
+        <v>6923786</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5156,7 +5122,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5166,7 +5132,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5181,22 +5147,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124898096</v>
+        <v>124899616</v>
       </c>
       <c r="B41" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5209,21 +5175,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5233,10 +5199,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>599930</v>
+        <v>599899</v>
       </c>
       <c r="R41" t="n">
-        <v>6923840</v>
+        <v>6923765</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5268,7 +5234,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5278,7 +5244,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5305,10 +5271,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124901634</v>
+        <v>124900827</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5317,38 +5283,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>599734</v>
+        <v>599787</v>
       </c>
       <c r="R42" t="n">
-        <v>6923810</v>
+        <v>6923799</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5380,7 +5351,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5390,7 +5361,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5405,22 +5376,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124900764</v>
+        <v>124902350</v>
       </c>
       <c r="B43" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5433,34 +5404,58 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>599814</v>
+        <v>599899</v>
       </c>
       <c r="R43" t="n">
-        <v>6923824</v>
+        <v>6923798</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5492,7 +5487,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5502,7 +5497,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett hona födosöker I en gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5517,22 +5517,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124901880</v>
+        <v>124900330</v>
       </c>
       <c r="B44" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5545,34 +5545,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>599771</v>
+        <v>599899</v>
       </c>
       <c r="R44" t="n">
-        <v>6923841</v>
+        <v>6923798</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5614,12 +5614,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:58</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på asp</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5634,19 +5629,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124900773</v>
+        <v>124898054</v>
       </c>
       <c r="B45" t="n">
         <v>78810</v>
@@ -5682,14 +5677,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>599801</v>
+        <v>599930</v>
       </c>
       <c r="R45" t="n">
-        <v>6923797</v>
+        <v>6923840</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5721,7 +5716,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5731,7 +5726,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5746,22 +5746,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124899196</v>
+        <v>124898168</v>
       </c>
       <c r="B46" t="n">
-        <v>91457</v>
+        <v>91299</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5770,25 +5770,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5798,10 +5798,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>599888</v>
+        <v>599920</v>
       </c>
       <c r="R46" t="n">
-        <v>6923798</v>
+        <v>6923834</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5870,10 +5870,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124898191</v>
+        <v>124898060</v>
       </c>
       <c r="B47" t="n">
-        <v>91673</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5882,41 +5882,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>898</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>599930</v>
+        <v>599916</v>
       </c>
       <c r="R47" t="n">
-        <v>6923840</v>
+        <v>6923847</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5970,22 +5970,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124902015</v>
+        <v>124900313</v>
       </c>
       <c r="B48" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5998,34 +5998,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>599777</v>
+        <v>599854</v>
       </c>
       <c r="R48" t="n">
-        <v>6923857</v>
+        <v>6923776</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6057,7 +6057,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6094,10 +6094,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124900226</v>
+        <v>124898571</v>
       </c>
       <c r="B49" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6110,39 +6110,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>599882</v>
+        <v>599904</v>
       </c>
       <c r="R49" t="n">
-        <v>6923778</v>
+        <v>6923812</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Över 20 apothecier</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6204,22 +6204,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124900863</v>
+        <v>124898191</v>
       </c>
       <c r="B50" t="n">
-        <v>91012</v>
+        <v>91673</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6228,38 +6228,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>599779</v>
+        <v>599930</v>
       </c>
       <c r="R50" t="n">
-        <v>6923783</v>
+        <v>6923840</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6291,7 +6291,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6316,22 +6316,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124901780</v>
+        <v>124902015</v>
       </c>
       <c r="B51" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6344,34 +6344,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>599756</v>
+        <v>599777</v>
       </c>
       <c r="R51" t="n">
-        <v>6923823</v>
+        <v>6923857</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6403,7 +6403,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6428,12 +6428,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124899503</v>
+        <v>124899616</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599912</v>
+        <v>599899</v>
       </c>
       <c r="R2" t="n">
-        <v>6923800</v>
+        <v>6923765</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124901880</v>
+        <v>124902839</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599771</v>
+        <v>599810</v>
       </c>
       <c r="R3" t="n">
-        <v>6923841</v>
+        <v>6923980</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:58</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på asp</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124900663</v>
+        <v>124898168</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599824</v>
+        <v>599920</v>
       </c>
       <c r="R4" t="n">
-        <v>6923802</v>
+        <v>6923834</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,22 +999,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124901584</v>
+        <v>124898060</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,41 +1023,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599899</v>
+        <v>599916</v>
       </c>
       <c r="R5" t="n">
-        <v>6923798</v>
+        <v>6923847</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,22 +1111,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124901679</v>
+        <v>124901922</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,38 +1135,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599728</v>
+        <v>599783</v>
       </c>
       <c r="R6" t="n">
-        <v>6923812</v>
+        <v>6923858</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124899644</v>
+        <v>124902765</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,38 +1251,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599898</v>
+        <v>599800</v>
       </c>
       <c r="R7" t="n">
-        <v>6923799</v>
+        <v>6923959</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1328,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124901624</v>
+        <v>124898995</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,47 +1367,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599703</v>
+        <v>599930</v>
       </c>
       <c r="R8" t="n">
-        <v>6923832</v>
+        <v>6923840</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,7 +1430,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1440,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,19 +1455,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124901922</v>
+        <v>124901767</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1508,7 +1502,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1517,10 +1511,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599783</v>
+        <v>599748</v>
       </c>
       <c r="R9" t="n">
-        <v>6923858</v>
+        <v>6923842</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1552,7 +1546,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,7 +1556,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,10 +1583,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124900294</v>
+        <v>124900226</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,47 +1595,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599864</v>
+        <v>599882</v>
       </c>
       <c r="R10" t="n">
-        <v>6923773</v>
+        <v>6923778</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1673,7 +1663,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1673,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Över 20 apothecier</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,22 +1693,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124902839</v>
+        <v>124902350</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1726,34 +1721,58 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599810</v>
+        <v>599899</v>
       </c>
       <c r="R11" t="n">
-        <v>6923980</v>
+        <v>6923798</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,7 +1804,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,7 +1814,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett hona födosöker I en gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,22 +1834,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124897942</v>
+        <v>124901880</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1838,39 +1862,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599929</v>
+        <v>599771</v>
       </c>
       <c r="R12" t="n">
-        <v>6923847</v>
+        <v>6923841</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,7 +1921,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1912,12 +1931,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Rikligt med lunglav på asp</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,22 +1951,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124899196</v>
+        <v>124900294</v>
       </c>
       <c r="B13" t="n">
-        <v>91457</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1960,34 +1979,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599888</v>
+        <v>599864</v>
       </c>
       <c r="R13" t="n">
-        <v>6923798</v>
+        <v>6923773</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,7 +2047,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2029,7 +2057,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,22 +2072,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124899564</v>
+        <v>124899341</v>
       </c>
       <c r="B14" t="n">
-        <v>91299</v>
+        <v>90977</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2068,25 +2096,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2096,10 +2124,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599910</v>
+        <v>599908</v>
       </c>
       <c r="R14" t="n">
-        <v>6923786</v>
+        <v>6923811</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2131,7 +2159,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2141,7 +2169,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2168,10 +2196,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124900863</v>
+        <v>124898290</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2184,34 +2212,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599779</v>
+        <v>599911</v>
       </c>
       <c r="R15" t="n">
-        <v>6923783</v>
+        <v>6923836</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2243,7 +2276,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2253,7 +2286,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,22 +2306,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124901767</v>
+        <v>124897942</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2292,42 +2330,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599748</v>
+        <v>599929</v>
       </c>
       <c r="R16" t="n">
-        <v>6923842</v>
+        <v>6923847</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2359,7 +2398,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2369,7 +2408,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2384,19 +2428,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124900773</v>
+        <v>124899644</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2432,14 +2476,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599801</v>
+        <v>599898</v>
       </c>
       <c r="R17" t="n">
-        <v>6923797</v>
+        <v>6923799</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2471,7 +2515,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2481,7 +2525,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2508,10 +2552,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124898316</v>
+        <v>124900465</v>
       </c>
       <c r="B18" t="n">
-        <v>91299</v>
+        <v>79891</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2524,34 +2568,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599918</v>
+        <v>599856</v>
       </c>
       <c r="R18" t="n">
-        <v>6923822</v>
+        <v>6923803</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2583,7 +2627,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2593,7 +2637,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2608,22 +2652,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124900661</v>
+        <v>124900786</v>
       </c>
       <c r="B19" t="n">
-        <v>79891</v>
+        <v>57529</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2636,34 +2680,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599813</v>
+        <v>599791</v>
       </c>
       <c r="R19" t="n">
-        <v>6923781</v>
+        <v>6923786</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2720,22 +2769,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124898290</v>
+        <v>124901921</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2744,43 +2793,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599911</v>
+        <v>599742</v>
       </c>
       <c r="R20" t="n">
-        <v>6923836</v>
+        <v>6923857</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2812,7 +2865,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2822,12 +2875,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2854,10 +2902,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124900465</v>
+        <v>124900827</v>
       </c>
       <c r="B21" t="n">
-        <v>79891</v>
+        <v>57529</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2870,34 +2918,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599856</v>
+        <v>599787</v>
       </c>
       <c r="R21" t="n">
-        <v>6923803</v>
+        <v>6923799</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2929,7 +2982,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2939,7 +2992,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2954,22 +3007,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124901921</v>
+        <v>124898054</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2978,47 +3031,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>599742</v>
+        <v>599930</v>
       </c>
       <c r="R22" t="n">
-        <v>6923857</v>
+        <v>6923840</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3050,7 +3094,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3060,7 +3104,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3075,22 +3124,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124898995</v>
+        <v>124902015</v>
       </c>
       <c r="B23" t="n">
-        <v>96979</v>
+        <v>91012</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3099,38 +3148,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>599930</v>
+        <v>599777</v>
       </c>
       <c r="R23" t="n">
-        <v>6923840</v>
+        <v>6923857</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3162,7 +3211,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3172,7 +3221,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3187,22 +3236,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124901780</v>
+        <v>124900863</v>
       </c>
       <c r="B24" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3215,34 +3264,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>599756</v>
+        <v>599779</v>
       </c>
       <c r="R24" t="n">
-        <v>6923823</v>
+        <v>6923783</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3274,7 +3323,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3284,7 +3333,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3299,22 +3348,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124899195</v>
+        <v>124900055</v>
       </c>
       <c r="B25" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3323,25 +3372,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3351,10 +3400,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>599930</v>
+        <v>599899</v>
       </c>
       <c r="R25" t="n">
-        <v>6923840</v>
+        <v>6923798</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3386,7 +3435,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3396,7 +3445,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3411,22 +3460,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124901634</v>
+        <v>124898096</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3435,25 +3484,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3463,10 +3512,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>599734</v>
+        <v>599930</v>
       </c>
       <c r="R26" t="n">
-        <v>6923810</v>
+        <v>6923840</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3498,7 +3547,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3508,7 +3557,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3535,7 +3584,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124900362</v>
+        <v>124901624</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3570,24 +3619,24 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>599864</v>
+        <v>599703</v>
       </c>
       <c r="R27" t="n">
-        <v>6923786</v>
+        <v>6923832</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3619,7 +3668,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3629,7 +3678,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3656,10 +3705,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124902765</v>
+        <v>124898571</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3668,42 +3717,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>599800</v>
+        <v>599904</v>
       </c>
       <c r="R28" t="n">
-        <v>6923959</v>
+        <v>6923812</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3735,7 +3785,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3745,7 +3795,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3760,22 +3815,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124901889</v>
+        <v>124899503</v>
       </c>
       <c r="B29" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3788,21 +3843,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3812,10 +3867,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>599775</v>
+        <v>599912</v>
       </c>
       <c r="R29" t="n">
-        <v>6923855</v>
+        <v>6923800</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3847,7 +3902,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3857,7 +3912,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3884,10 +3939,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124900018</v>
+        <v>124899421</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3900,21 +3955,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3924,10 +3979,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>599883</v>
+        <v>599899</v>
       </c>
       <c r="R30" t="n">
-        <v>6923768</v>
+        <v>6923798</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3959,7 +4014,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3969,7 +4024,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3984,22 +4039,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124899341</v>
+        <v>124899798</v>
       </c>
       <c r="B31" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4008,38 +4063,42 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>599908</v>
+        <v>599883</v>
       </c>
       <c r="R31" t="n">
-        <v>6923811</v>
+        <v>6923782</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4071,7 +4130,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4081,7 +4140,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4096,22 +4155,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124899798</v>
+        <v>124899564</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4120,42 +4179,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>599883</v>
+        <v>599910</v>
       </c>
       <c r="R32" t="n">
-        <v>6923782</v>
+        <v>6923786</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4187,7 +4242,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4197,7 +4252,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4212,19 +4267,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124900226</v>
+        <v>124900661</v>
       </c>
       <c r="B33" t="n">
         <v>79891</v>
@@ -4258,21 +4313,16 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>599882</v>
+        <v>599813</v>
       </c>
       <c r="R33" t="n">
-        <v>6923778</v>
+        <v>6923781</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4304,7 +4354,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4314,12 +4364,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:43</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Över 20 apothecier</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4334,22 +4379,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124899421</v>
+        <v>124899196</v>
       </c>
       <c r="B34" t="n">
-        <v>91012</v>
+        <v>91457</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4358,35 +4403,35 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>599899</v>
+        <v>599888</v>
       </c>
       <c r="R34" t="n">
         <v>6923798</v>
@@ -4421,7 +4466,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4431,7 +4476,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4446,22 +4491,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124902691</v>
+        <v>124901679</v>
       </c>
       <c r="B35" t="n">
-        <v>91030</v>
+        <v>79891</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4474,21 +4519,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4498,10 +4543,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>599798</v>
+        <v>599728</v>
       </c>
       <c r="R35" t="n">
-        <v>6923975</v>
+        <v>6923812</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4533,7 +4578,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4543,7 +4588,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4692,10 +4737,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124899839</v>
+        <v>124898191</v>
       </c>
       <c r="B37" t="n">
-        <v>57513</v>
+        <v>91673</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4704,43 +4749,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>599893</v>
+        <v>599930</v>
       </c>
       <c r="R37" t="n">
-        <v>6923773</v>
+        <v>6923840</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4772,7 +4812,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4782,12 +4822,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:35</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4802,22 +4837,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124900025</v>
+        <v>124900764</v>
       </c>
       <c r="B38" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4826,42 +4861,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>599878</v>
+        <v>599814</v>
       </c>
       <c r="R38" t="n">
-        <v>6923820</v>
+        <v>6923824</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4893,7 +4924,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4903,7 +4934,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4918,19 +4949,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124900764</v>
+        <v>124900313</v>
       </c>
       <c r="B39" t="n">
         <v>79891</v>
@@ -4966,14 +4997,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>599814</v>
+        <v>599854</v>
       </c>
       <c r="R39" t="n">
-        <v>6923824</v>
+        <v>6923776</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5005,7 +5036,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5015,7 +5046,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5030,22 +5061,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124900786</v>
+        <v>124900773</v>
       </c>
       <c r="B40" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5058,39 +5089,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>599791</v>
+        <v>599801</v>
       </c>
       <c r="R40" t="n">
-        <v>6923786</v>
+        <v>6923797</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5122,7 +5148,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5132,7 +5158,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5147,22 +5173,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124899616</v>
+        <v>124901889</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5175,21 +5201,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5199,10 +5225,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>599899</v>
+        <v>599775</v>
       </c>
       <c r="R41" t="n">
-        <v>6923765</v>
+        <v>6923855</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5234,7 +5260,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5244,7 +5270,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5271,10 +5297,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124900827</v>
+        <v>124900025</v>
       </c>
       <c r="B42" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5283,43 +5309,42 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>599787</v>
+        <v>599878</v>
       </c>
       <c r="R42" t="n">
-        <v>6923799</v>
+        <v>6923820</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5351,7 +5376,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5361,7 +5386,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5388,10 +5413,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124902350</v>
+        <v>124900330</v>
       </c>
       <c r="B43" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5404,48 +5429,24 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Backtjärnen, Mpd</t>
@@ -5487,7 +5488,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5497,12 +5498,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:17</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett hona födosöker I en gran.</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5529,10 +5525,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124900330</v>
+        <v>124901634</v>
       </c>
       <c r="B44" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5541,25 +5537,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5569,10 +5565,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>599899</v>
+        <v>599734</v>
       </c>
       <c r="R44" t="n">
-        <v>6923798</v>
+        <v>6923810</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5604,7 +5600,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5614,7 +5610,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5629,22 +5625,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124898054</v>
+        <v>124899839</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5657,34 +5653,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>599930</v>
+        <v>599893</v>
       </c>
       <c r="R45" t="n">
-        <v>6923840</v>
+        <v>6923773</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5716,7 +5717,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5726,12 +5727,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5746,22 +5747,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124898168</v>
+        <v>124900018</v>
       </c>
       <c r="B46" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5774,34 +5775,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>599920</v>
+        <v>599883</v>
       </c>
       <c r="R46" t="n">
-        <v>6923834</v>
+        <v>6923768</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5833,7 +5834,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5843,7 +5844,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5858,22 +5859,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124898060</v>
+        <v>124902691</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5886,37 +5887,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>599916</v>
+        <v>599798</v>
       </c>
       <c r="R47" t="n">
-        <v>6923847</v>
+        <v>6923975</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5945,7 +5946,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5955,7 +5956,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5982,7 +5983,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124900313</v>
+        <v>124901780</v>
       </c>
       <c r="B48" t="n">
         <v>79891</v>
@@ -6018,14 +6019,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>599854</v>
+        <v>599756</v>
       </c>
       <c r="R48" t="n">
-        <v>6923776</v>
+        <v>6923823</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6057,7 +6058,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6067,7 +6068,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6082,22 +6083,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124898571</v>
+        <v>124900663</v>
       </c>
       <c r="B49" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6110,39 +6111,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>599904</v>
+        <v>599824</v>
       </c>
       <c r="R49" t="n">
-        <v>6923812</v>
+        <v>6923802</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6174,7 +6170,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6184,12 +6180,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:05</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6204,22 +6195,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124898191</v>
+        <v>124900362</v>
       </c>
       <c r="B50" t="n">
-        <v>91673</v>
+        <v>98101</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6232,34 +6223,43 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>898</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>599930</v>
+        <v>599864</v>
       </c>
       <c r="R50" t="n">
-        <v>6923840</v>
+        <v>6923786</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6291,7 +6291,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6316,22 +6316,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124902015</v>
+        <v>124898316</v>
       </c>
       <c r="B51" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6344,34 +6344,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>599777</v>
+        <v>599918</v>
       </c>
       <c r="R51" t="n">
-        <v>6923857</v>
+        <v>6923822</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6403,7 +6403,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124899616</v>
+        <v>124902839</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599899</v>
+        <v>599810</v>
       </c>
       <c r="R2" t="n">
-        <v>6923765</v>
+        <v>6923980</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,19 +775,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124902839</v>
+        <v>124899616</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -823,14 +823,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599810</v>
+        <v>599899</v>
       </c>
       <c r="R3" t="n">
-        <v>6923980</v>
+        <v>6923765</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,12 +887,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1239,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124902765</v>
+        <v>124898995</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,42 +1251,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599800</v>
+        <v>599930</v>
       </c>
       <c r="R7" t="n">
-        <v>6923959</v>
+        <v>6923840</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1328,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,22 +1339,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124898995</v>
+        <v>124901767</v>
       </c>
       <c r="B8" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,38 +1363,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599930</v>
+        <v>599748</v>
       </c>
       <c r="R8" t="n">
-        <v>6923840</v>
+        <v>6923842</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,19 +1455,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124901767</v>
+        <v>124902765</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599748</v>
+        <v>599800</v>
       </c>
       <c r="R9" t="n">
-        <v>6923842</v>
+        <v>6923959</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124902839</v>
+        <v>124901889</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599810</v>
+        <v>599775</v>
       </c>
       <c r="R2" t="n">
-        <v>6923980</v>
+        <v>6923855</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,19 +775,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124899616</v>
+        <v>124900773</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -823,14 +823,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599899</v>
+        <v>599801</v>
       </c>
       <c r="R3" t="n">
-        <v>6923765</v>
+        <v>6923797</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124898168</v>
+        <v>124899503</v>
       </c>
       <c r="B4" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599920</v>
+        <v>599912</v>
       </c>
       <c r="R4" t="n">
-        <v>6923834</v>
+        <v>6923800</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,19 +999,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124898060</v>
+        <v>124899616</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1047,17 +1047,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599916</v>
+        <v>599899</v>
       </c>
       <c r="R5" t="n">
-        <v>6923847</v>
+        <v>6923765</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,22 +1111,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124901922</v>
+        <v>124900226</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,42 +1135,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599783</v>
+        <v>599882</v>
       </c>
       <c r="R6" t="n">
-        <v>6923858</v>
+        <v>6923778</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1213,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Över 20 apothecier</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,22 +1233,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124898995</v>
+        <v>124901131</v>
       </c>
       <c r="B7" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,25 +1257,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1279,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599930</v>
+        <v>599899</v>
       </c>
       <c r="R7" t="n">
-        <v>6923840</v>
+        <v>6923798</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,12 +1345,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1467,7 +1473,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124902765</v>
+        <v>124901921</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1505,16 +1511,21 @@
           <t>10</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599800</v>
+        <v>599742</v>
       </c>
       <c r="R9" t="n">
-        <v>6923959</v>
+        <v>6923857</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,7 +1557,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1556,7 +1567,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,22 +1582,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124900226</v>
+        <v>124898054</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1599,39 +1610,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599882</v>
+        <v>599930</v>
       </c>
       <c r="R10" t="n">
-        <v>6923778</v>
+        <v>6923840</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1663,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1673,12 +1679,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Över 20 apothecier</t>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1705,10 +1711,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124902350</v>
+        <v>124899798</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1717,62 +1723,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599899</v>
+        <v>599883</v>
       </c>
       <c r="R11" t="n">
-        <v>6923798</v>
+        <v>6923782</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1804,7 +1790,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1814,12 +1800,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:17</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett hona födosöker I en gran.</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1834,22 +1815,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124901880</v>
+        <v>124898168</v>
       </c>
       <c r="B12" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1862,34 +1843,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599771</v>
+        <v>599920</v>
       </c>
       <c r="R12" t="n">
-        <v>6923841</v>
+        <v>6923834</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1921,7 +1902,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1931,12 +1912,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:58</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på asp</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1963,10 +1939,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124900294</v>
+        <v>124898571</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1975,35 +1951,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2012,10 +1984,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599864</v>
+        <v>599904</v>
       </c>
       <c r="R13" t="n">
-        <v>6923773</v>
+        <v>6923812</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2047,7 +2019,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2057,7 +2029,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2084,10 +2061,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124899341</v>
+        <v>124901624</v>
       </c>
       <c r="B14" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2096,38 +2073,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599908</v>
+        <v>599703</v>
       </c>
       <c r="R14" t="n">
-        <v>6923811</v>
+        <v>6923832</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2159,7 +2145,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2169,7 +2155,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2184,22 +2170,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124898290</v>
+        <v>124900294</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2208,31 +2194,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2241,10 +2231,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599911</v>
+        <v>599864</v>
       </c>
       <c r="R15" t="n">
-        <v>6923836</v>
+        <v>6923773</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2276,7 +2266,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2286,12 +2276,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2318,10 +2303,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124897942</v>
+        <v>124899421</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2334,39 +2319,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599929</v>
+        <v>599899</v>
       </c>
       <c r="R16" t="n">
-        <v>6923847</v>
+        <v>6923798</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2398,7 +2378,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2408,12 +2388,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2428,12 +2403,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2552,10 +2527,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124900465</v>
+        <v>124901922</v>
       </c>
       <c r="B18" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2564,38 +2539,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599856</v>
+        <v>599783</v>
       </c>
       <c r="R18" t="n">
-        <v>6923803</v>
+        <v>6923858</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2627,7 +2606,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2637,7 +2616,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2652,22 +2631,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124900786</v>
+        <v>124900330</v>
       </c>
       <c r="B19" t="n">
-        <v>57529</v>
+        <v>91299</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2680,39 +2659,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599791</v>
+        <v>599899</v>
       </c>
       <c r="R19" t="n">
-        <v>6923786</v>
+        <v>6923798</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2744,7 +2718,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2754,7 +2728,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2769,22 +2743,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124901921</v>
+        <v>124902350</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2793,47 +2767,62 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599742</v>
+        <v>599899</v>
       </c>
       <c r="R20" t="n">
-        <v>6923857</v>
+        <v>6923798</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2865,7 +2854,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2875,7 +2864,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett hona födosöker I en gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2890,22 +2884,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124900827</v>
+        <v>124902691</v>
       </c>
       <c r="B21" t="n">
-        <v>57529</v>
+        <v>91030</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2918,39 +2912,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599787</v>
+        <v>599798</v>
       </c>
       <c r="R21" t="n">
-        <v>6923799</v>
+        <v>6923975</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2982,7 +2971,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2992,7 +2981,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3019,10 +3008,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124898054</v>
+        <v>124901679</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3035,34 +3024,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>599930</v>
+        <v>599728</v>
       </c>
       <c r="R22" t="n">
-        <v>6923840</v>
+        <v>6923812</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3094,7 +3083,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3104,12 +3093,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3124,22 +3108,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124902015</v>
+        <v>124898995</v>
       </c>
       <c r="B23" t="n">
-        <v>91012</v>
+        <v>96979</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3148,38 +3132,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>599777</v>
+        <v>599930</v>
       </c>
       <c r="R23" t="n">
-        <v>6923857</v>
+        <v>6923840</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3211,7 +3195,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3221,7 +3205,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3236,22 +3220,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124900863</v>
+        <v>124898316</v>
       </c>
       <c r="B24" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3264,34 +3248,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>599779</v>
+        <v>599918</v>
       </c>
       <c r="R24" t="n">
-        <v>6923783</v>
+        <v>6923822</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3323,7 +3307,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3333,7 +3317,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3360,10 +3344,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124900055</v>
+        <v>124900827</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3372,38 +3356,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>599899</v>
+        <v>599787</v>
       </c>
       <c r="R25" t="n">
-        <v>6923798</v>
+        <v>6923799</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3435,7 +3424,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3445,7 +3434,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3460,22 +3449,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124898096</v>
+        <v>124897942</v>
       </c>
       <c r="B26" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3488,34 +3477,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>599930</v>
+        <v>599929</v>
       </c>
       <c r="R26" t="n">
-        <v>6923840</v>
+        <v>6923847</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3547,7 +3541,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3557,7 +3551,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3572,22 +3571,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124901624</v>
+        <v>124902509</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3596,35 +3595,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3633,10 +3628,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>599703</v>
+        <v>599754</v>
       </c>
       <c r="R27" t="n">
-        <v>6923832</v>
+        <v>6923921</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3668,7 +3663,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3678,7 +3673,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:29</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3693,22 +3693,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124898571</v>
+        <v>124900786</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3721,16 +3721,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3741,19 +3741,19 @@
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>599904</v>
+        <v>599791</v>
       </c>
       <c r="R28" t="n">
-        <v>6923812</v>
+        <v>6923786</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3795,12 +3795,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:05</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3827,10 +3822,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124899503</v>
+        <v>124899564</v>
       </c>
       <c r="B29" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3843,21 +3838,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3867,10 +3862,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>599912</v>
+        <v>599910</v>
       </c>
       <c r="R29" t="n">
-        <v>6923800</v>
+        <v>6923786</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3939,7 +3934,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124899421</v>
+        <v>124899195</v>
       </c>
       <c r="B30" t="n">
         <v>91012</v>
@@ -3979,10 +3974,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>599899</v>
+        <v>599930</v>
       </c>
       <c r="R30" t="n">
-        <v>6923798</v>
+        <v>6923840</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4014,7 +4009,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4024,7 +4019,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4039,22 +4034,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124899798</v>
+        <v>124902015</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4063,42 +4058,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>599883</v>
+        <v>599777</v>
       </c>
       <c r="R31" t="n">
-        <v>6923782</v>
+        <v>6923857</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4130,7 +4121,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4140,7 +4131,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4167,10 +4158,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124899564</v>
+        <v>124902839</v>
       </c>
       <c r="B32" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4183,34 +4174,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>599910</v>
+        <v>599810</v>
       </c>
       <c r="R32" t="n">
-        <v>6923786</v>
+        <v>6923980</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4242,7 +4233,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4252,7 +4243,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4267,22 +4258,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124900661</v>
+        <v>124900362</v>
       </c>
       <c r="B33" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4291,38 +4282,47 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>599813</v>
+        <v>599864</v>
       </c>
       <c r="R33" t="n">
-        <v>6923781</v>
+        <v>6923786</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4379,22 +4379,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124899196</v>
+        <v>124900764</v>
       </c>
       <c r="B34" t="n">
-        <v>91457</v>
+        <v>79891</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4403,38 +4403,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>599888</v>
+        <v>599814</v>
       </c>
       <c r="R34" t="n">
-        <v>6923798</v>
+        <v>6923824</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4491,22 +4491,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124901679</v>
+        <v>124899839</v>
       </c>
       <c r="B35" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4519,34 +4519,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>599728</v>
+        <v>599893</v>
       </c>
       <c r="R35" t="n">
-        <v>6923812</v>
+        <v>6923773</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4578,7 +4583,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4588,7 +4593,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4603,22 +4613,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124902509</v>
+        <v>124898191</v>
       </c>
       <c r="B36" t="n">
-        <v>57513</v>
+        <v>91673</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4627,43 +4637,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>599754</v>
+        <v>599930</v>
       </c>
       <c r="R36" t="n">
-        <v>6923921</v>
+        <v>6923840</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4695,7 +4700,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4705,12 +4710,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>18:29</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4725,22 +4725,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124898191</v>
+        <v>124900313</v>
       </c>
       <c r="B37" t="n">
-        <v>91673</v>
+        <v>79891</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4749,38 +4749,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>898</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>599930</v>
+        <v>599854</v>
       </c>
       <c r="R37" t="n">
-        <v>6923840</v>
+        <v>6923776</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4812,7 +4812,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4837,22 +4837,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124900764</v>
+        <v>124901634</v>
       </c>
       <c r="B38" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4861,25 +4861,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4889,10 +4889,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>599814</v>
+        <v>599734</v>
       </c>
       <c r="R38" t="n">
-        <v>6923824</v>
+        <v>6923810</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4924,7 +4924,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4961,10 +4961,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124900313</v>
+        <v>124900025</v>
       </c>
       <c r="B39" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4973,38 +4973,42 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>599854</v>
+        <v>599878</v>
       </c>
       <c r="R39" t="n">
-        <v>6923776</v>
+        <v>6923820</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5036,7 +5040,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5046,7 +5050,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5073,7 +5077,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124900773</v>
+        <v>124898060</v>
       </c>
       <c r="B40" t="n">
         <v>78810</v>
@@ -5109,17 +5113,17 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>599801</v>
+        <v>599916</v>
       </c>
       <c r="R40" t="n">
-        <v>6923797</v>
+        <v>6923847</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5148,7 +5152,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5158,7 +5162,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5185,7 +5189,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124901889</v>
+        <v>124900661</v>
       </c>
       <c r="B41" t="n">
         <v>79891</v>
@@ -5221,14 +5225,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>599775</v>
+        <v>599813</v>
       </c>
       <c r="R41" t="n">
-        <v>6923855</v>
+        <v>6923781</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5260,7 +5264,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5270,7 +5274,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5285,19 +5289,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124900025</v>
+        <v>124902765</v>
       </c>
       <c r="B42" t="n">
         <v>98101</v>
@@ -5332,19 +5336,19 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>599878</v>
+        <v>599800</v>
       </c>
       <c r="R42" t="n">
-        <v>6923820</v>
+        <v>6923959</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5376,7 +5380,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5386,7 +5390,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5413,10 +5417,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124900330</v>
+        <v>124898290</v>
       </c>
       <c r="B43" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5429,34 +5433,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>599899</v>
+        <v>599911</v>
       </c>
       <c r="R43" t="n">
-        <v>6923798</v>
+        <v>6923836</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5488,7 +5497,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5498,7 +5507,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5513,22 +5527,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124901634</v>
+        <v>124900465</v>
       </c>
       <c r="B44" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5537,25 +5551,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5565,10 +5579,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>599734</v>
+        <v>599856</v>
       </c>
       <c r="R44" t="n">
-        <v>6923810</v>
+        <v>6923803</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5600,7 +5614,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5610,7 +5624,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5637,10 +5651,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124899839</v>
+        <v>124901880</v>
       </c>
       <c r="B45" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5653,39 +5667,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>599893</v>
+        <v>599771</v>
       </c>
       <c r="R45" t="n">
-        <v>6923773</v>
+        <v>6923841</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5717,7 +5726,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5727,12 +5736,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Rikligt med lunglav på asp</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5747,12 +5756,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5871,10 +5880,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124902691</v>
+        <v>124899196</v>
       </c>
       <c r="B47" t="n">
-        <v>91030</v>
+        <v>91457</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5883,38 +5892,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>599798</v>
+        <v>599888</v>
       </c>
       <c r="R47" t="n">
-        <v>6923975</v>
+        <v>6923798</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5946,7 +5955,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5956,7 +5965,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5983,10 +5992,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124901780</v>
+        <v>124899341</v>
       </c>
       <c r="B48" t="n">
-        <v>79891</v>
+        <v>90977</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5995,25 +6004,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6023,10 +6032,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>599756</v>
+        <v>599908</v>
       </c>
       <c r="R48" t="n">
-        <v>6923823</v>
+        <v>6923811</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6058,7 +6067,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6068,7 +6077,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6095,10 +6104,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124900663</v>
+        <v>124900863</v>
       </c>
       <c r="B49" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6111,34 +6120,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>599824</v>
+        <v>599779</v>
       </c>
       <c r="R49" t="n">
-        <v>6923802</v>
+        <v>6923783</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6170,7 +6179,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6180,7 +6189,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6195,22 +6204,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124900362</v>
+        <v>124900663</v>
       </c>
       <c r="B50" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6219,47 +6228,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>599864</v>
+        <v>599824</v>
       </c>
       <c r="R50" t="n">
-        <v>6923786</v>
+        <v>6923802</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6291,7 +6291,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6316,22 +6316,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124898316</v>
+        <v>124901780</v>
       </c>
       <c r="B51" t="n">
-        <v>91299</v>
+        <v>79891</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6344,34 +6344,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>599918</v>
+        <v>599756</v>
       </c>
       <c r="R51" t="n">
-        <v>6923822</v>
+        <v>6923823</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6403,7 +6403,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6428,12 +6428,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -1473,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124901921</v>
+        <v>124898168</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,47 +1485,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599742</v>
+        <v>599920</v>
       </c>
       <c r="R9" t="n">
-        <v>6923857</v>
+        <v>6923834</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1557,7 +1548,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,7 +1558,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,22 +1573,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124898054</v>
+        <v>124898571</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,34 +1601,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599930</v>
+        <v>599904</v>
       </c>
       <c r="R10" t="n">
-        <v>6923840</v>
+        <v>6923812</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1665,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,12 +1675,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1699,12 +1695,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1827,10 +1823,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124898168</v>
+        <v>124901921</v>
       </c>
       <c r="B12" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1839,38 +1835,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599920</v>
+        <v>599742</v>
       </c>
       <c r="R12" t="n">
-        <v>6923834</v>
+        <v>6923857</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,7 +1907,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1912,7 +1917,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,22 +1932,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124898571</v>
+        <v>124898054</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1955,39 +1960,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599904</v>
+        <v>599930</v>
       </c>
       <c r="R13" t="n">
-        <v>6923812</v>
+        <v>6923840</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,12 +2049,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2415,10 +2415,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124899644</v>
+        <v>124902350</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2431,34 +2431,58 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599898</v>
+        <v>599899</v>
       </c>
       <c r="R17" t="n">
-        <v>6923799</v>
+        <v>6923798</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2490,7 +2514,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2500,7 +2524,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett hona födosöker I en gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2515,22 +2544,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124901922</v>
+        <v>124902691</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>91030</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2539,42 +2568,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599783</v>
+        <v>599798</v>
       </c>
       <c r="R18" t="n">
-        <v>6923858</v>
+        <v>6923975</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2606,7 +2631,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2616,7 +2641,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2643,10 +2668,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124900330</v>
+        <v>124901922</v>
       </c>
       <c r="B19" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2655,38 +2680,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599899</v>
+        <v>599783</v>
       </c>
       <c r="R19" t="n">
-        <v>6923798</v>
+        <v>6923858</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2718,7 +2747,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2728,7 +2757,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2743,22 +2772,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124902350</v>
+        <v>124899644</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2771,58 +2800,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599899</v>
+        <v>599898</v>
       </c>
       <c r="R20" t="n">
-        <v>6923798</v>
+        <v>6923799</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2854,7 +2859,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2864,12 +2869,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:17</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett hona födosöker I en gran.</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2884,22 +2884,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124902691</v>
+        <v>124900330</v>
       </c>
       <c r="B21" t="n">
-        <v>91030</v>
+        <v>91299</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2912,34 +2912,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599798</v>
+        <v>599899</v>
       </c>
       <c r="R21" t="n">
-        <v>6923975</v>
+        <v>6923798</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2996,12 +2996,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3344,10 +3344,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124900827</v>
+        <v>124897942</v>
       </c>
       <c r="B25" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3360,16 +3360,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3380,19 +3380,19 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>599787</v>
+        <v>599929</v>
       </c>
       <c r="R25" t="n">
-        <v>6923799</v>
+        <v>6923847</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3434,7 +3434,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3449,22 +3454,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124897942</v>
+        <v>124900827</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3477,16 +3482,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3497,19 +3502,19 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>599929</v>
+        <v>599787</v>
       </c>
       <c r="R26" t="n">
-        <v>6923847</v>
+        <v>6923799</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3541,7 +3546,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3551,12 +3556,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3571,12 +3571,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -4503,10 +4503,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124899839</v>
+        <v>124901634</v>
       </c>
       <c r="B35" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4515,43 +4515,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>599893</v>
+        <v>599734</v>
       </c>
       <c r="R35" t="n">
-        <v>6923773</v>
+        <v>6923810</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4583,7 +4578,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4593,12 +4588,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:35</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4613,12 +4603,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4737,10 +4727,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124900313</v>
+        <v>124899839</v>
       </c>
       <c r="B37" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4753,34 +4743,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>599854</v>
+        <v>599893</v>
       </c>
       <c r="R37" t="n">
-        <v>6923776</v>
+        <v>6923773</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4812,7 +4807,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4822,7 +4817,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4837,22 +4837,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124901634</v>
+        <v>124900313</v>
       </c>
       <c r="B38" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4861,38 +4861,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>599734</v>
+        <v>599854</v>
       </c>
       <c r="R38" t="n">
-        <v>6923810</v>
+        <v>6923776</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4924,7 +4924,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4949,12 +4949,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5077,10 +5077,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124898060</v>
+        <v>124902765</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5089,41 +5089,45 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>599916</v>
+        <v>599800</v>
       </c>
       <c r="R40" t="n">
-        <v>6923847</v>
+        <v>6923959</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5152,7 +5156,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5162,7 +5166,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5189,10 +5193,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124900661</v>
+        <v>124898060</v>
       </c>
       <c r="B41" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5205,37 +5209,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>599813</v>
+        <v>599916</v>
       </c>
       <c r="R41" t="n">
-        <v>6923781</v>
+        <v>6923847</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5264,7 +5268,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5274,7 +5278,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5301,10 +5305,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124902765</v>
+        <v>124900661</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5313,42 +5317,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>599800</v>
+        <v>599813</v>
       </c>
       <c r="R42" t="n">
-        <v>6923959</v>
+        <v>6923781</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124901889</v>
+        <v>124901880</v>
       </c>
       <c r="B2" t="n">
         <v>79891</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599775</v>
+        <v>599771</v>
       </c>
       <c r="R2" t="n">
-        <v>6923855</v>
+        <v>6923841</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på asp</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124900773</v>
+        <v>124898995</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>96979</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +804,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599801</v>
+        <v>599930</v>
       </c>
       <c r="R3" t="n">
-        <v>6923797</v>
+        <v>6923840</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,19 +892,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124899503</v>
+        <v>124900863</v>
       </c>
       <c r="B4" t="n">
         <v>91012</v>
@@ -935,14 +940,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599912</v>
+        <v>599779</v>
       </c>
       <c r="R4" t="n">
-        <v>6923800</v>
+        <v>6923783</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,22 +1004,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124899616</v>
+        <v>124902015</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599899</v>
+        <v>599777</v>
       </c>
       <c r="R5" t="n">
-        <v>6923765</v>
+        <v>6923857</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,22 +1116,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124900226</v>
+        <v>124898168</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,39 +1144,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599882</v>
+        <v>599920</v>
       </c>
       <c r="R6" t="n">
-        <v>6923778</v>
+        <v>6923834</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,12 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:43</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Över 20 apothecier</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,22 +1228,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124901131</v>
+        <v>124899644</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,38 +1252,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599899</v>
+        <v>599898</v>
       </c>
       <c r="R7" t="n">
-        <v>6923798</v>
+        <v>6923799</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,19 +1340,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124901767</v>
+        <v>124901624</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1392,7 +1387,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599748</v>
+        <v>599703</v>
       </c>
       <c r="R8" t="n">
-        <v>6923842</v>
+        <v>6923832</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,22 +1461,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124898168</v>
+        <v>124901584</v>
       </c>
       <c r="B9" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,38 +1485,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599920</v>
+        <v>599899</v>
       </c>
       <c r="R9" t="n">
-        <v>6923834</v>
+        <v>6923798</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1573,22 +1573,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124898571</v>
+        <v>124901921</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,43 +1597,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599904</v>
+        <v>599742</v>
       </c>
       <c r="R10" t="n">
-        <v>6923812</v>
+        <v>6923857</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1675,12 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:05</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,10 +1706,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124899798</v>
+        <v>124902350</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,42 +1718,62 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599883</v>
+        <v>599899</v>
       </c>
       <c r="R11" t="n">
-        <v>6923782</v>
+        <v>6923798</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1786,7 +1805,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,7 +1815,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett hona födosöker I en gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1811,22 +1835,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124901921</v>
+        <v>124899564</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1835,47 +1859,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599742</v>
+        <v>599910</v>
       </c>
       <c r="R12" t="n">
-        <v>6923857</v>
+        <v>6923786</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,7 +1922,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1917,7 +1932,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,22 +1947,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124898054</v>
+        <v>124900313</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1960,34 +1975,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599930</v>
+        <v>599854</v>
       </c>
       <c r="R13" t="n">
-        <v>6923840</v>
+        <v>6923776</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,7 +2034,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2029,12 +2044,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,22 +2059,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124901624</v>
+        <v>124902691</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>91030</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2073,47 +2083,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599703</v>
+        <v>599798</v>
       </c>
       <c r="R14" t="n">
-        <v>6923832</v>
+        <v>6923975</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2145,7 +2146,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2155,7 +2156,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,19 +2171,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124900294</v>
+        <v>124901634</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2215,26 +2216,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599864</v>
+        <v>599734</v>
       </c>
       <c r="R15" t="n">
-        <v>6923773</v>
+        <v>6923810</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2266,7 +2258,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2276,7 +2268,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,22 +2283,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124899421</v>
+        <v>124899616</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2319,21 +2311,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2346,7 +2338,7 @@
         <v>599899</v>
       </c>
       <c r="R16" t="n">
-        <v>6923798</v>
+        <v>6923765</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2378,7 +2370,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2388,7 +2380,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2403,22 +2395,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124902350</v>
+        <v>124902839</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2431,58 +2423,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599899</v>
+        <v>599810</v>
       </c>
       <c r="R17" t="n">
-        <v>6923798</v>
+        <v>6923980</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2514,7 +2482,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2524,12 +2492,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:17</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett hona födosöker I en gran.</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2544,22 +2507,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124902691</v>
+        <v>124898290</v>
       </c>
       <c r="B18" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2572,34 +2535,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599798</v>
+        <v>599911</v>
       </c>
       <c r="R18" t="n">
-        <v>6923975</v>
+        <v>6923836</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2631,7 +2599,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2641,7 +2609,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2656,22 +2629,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124901922</v>
+        <v>124900764</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2680,42 +2653,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599783</v>
+        <v>599814</v>
       </c>
       <c r="R19" t="n">
-        <v>6923858</v>
+        <v>6923824</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2747,7 +2716,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2757,7 +2726,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2772,22 +2741,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124899644</v>
+        <v>124901889</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2800,34 +2769,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599898</v>
+        <v>599775</v>
       </c>
       <c r="R20" t="n">
-        <v>6923799</v>
+        <v>6923855</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2859,7 +2828,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2869,7 +2838,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2884,22 +2853,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124900330</v>
+        <v>124900663</v>
       </c>
       <c r="B21" t="n">
-        <v>91299</v>
+        <v>79891</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2912,21 +2881,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2936,10 +2905,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599899</v>
+        <v>599824</v>
       </c>
       <c r="R21" t="n">
-        <v>6923798</v>
+        <v>6923802</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2971,7 +2940,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2981,7 +2950,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2996,22 +2965,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124901679</v>
+        <v>124900025</v>
       </c>
       <c r="B22" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3020,38 +2989,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>599728</v>
+        <v>599878</v>
       </c>
       <c r="R22" t="n">
-        <v>6923812</v>
+        <v>6923820</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3083,7 +3056,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3093,7 +3066,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3120,10 +3093,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124898995</v>
+        <v>124899196</v>
       </c>
       <c r="B23" t="n">
-        <v>96979</v>
+        <v>91457</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3132,38 +3105,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>599930</v>
+        <v>599888</v>
       </c>
       <c r="R23" t="n">
-        <v>6923840</v>
+        <v>6923798</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3195,7 +3168,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3205,7 +3178,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3220,12 +3193,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3344,10 +3317,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124897942</v>
+        <v>124899421</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3360,39 +3333,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>599929</v>
+        <v>599899</v>
       </c>
       <c r="R25" t="n">
-        <v>6923847</v>
+        <v>6923798</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3424,7 +3392,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3434,12 +3402,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3454,19 +3417,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124900827</v>
+        <v>124900786</v>
       </c>
       <c r="B26" t="n">
         <v>57529</v>
@@ -3502,7 +3465,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3511,10 +3474,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>599787</v>
+        <v>599791</v>
       </c>
       <c r="R26" t="n">
-        <v>6923799</v>
+        <v>6923786</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3546,7 +3509,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3556,7 +3519,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3571,22 +3534,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124902509</v>
+        <v>124899341</v>
       </c>
       <c r="B27" t="n">
-        <v>57513</v>
+        <v>90977</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3595,43 +3558,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>599754</v>
+        <v>599908</v>
       </c>
       <c r="R27" t="n">
-        <v>6923921</v>
+        <v>6923811</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3663,7 +3621,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3673,12 +3631,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:29</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3693,19 +3646,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124900786</v>
+        <v>124900827</v>
       </c>
       <c r="B28" t="n">
         <v>57529</v>
@@ -3741,7 +3694,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3750,10 +3703,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>599791</v>
+        <v>599787</v>
       </c>
       <c r="R28" t="n">
-        <v>6923786</v>
+        <v>6923799</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3785,7 +3738,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3795,7 +3748,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3810,22 +3763,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124899564</v>
+        <v>124899839</v>
       </c>
       <c r="B29" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3838,34 +3791,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>599910</v>
+        <v>599893</v>
       </c>
       <c r="R29" t="n">
-        <v>6923786</v>
+        <v>6923773</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3897,7 +3855,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3907,7 +3865,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3922,22 +3885,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124899195</v>
+        <v>124901780</v>
       </c>
       <c r="B30" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3950,21 +3913,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3974,10 +3937,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>599930</v>
+        <v>599756</v>
       </c>
       <c r="R30" t="n">
-        <v>6923840</v>
+        <v>6923823</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4009,7 +3972,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4019,7 +3982,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4046,10 +4009,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124902015</v>
+        <v>124898191</v>
       </c>
       <c r="B31" t="n">
-        <v>91012</v>
+        <v>91673</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4058,38 +4021,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>599777</v>
+        <v>599930</v>
       </c>
       <c r="R31" t="n">
-        <v>6923857</v>
+        <v>6923840</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4121,7 +4084,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4131,7 +4094,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4146,19 +4109,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124902839</v>
+        <v>124898054</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -4194,14 +4157,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>599810</v>
+        <v>599930</v>
       </c>
       <c r="R32" t="n">
-        <v>6923980</v>
+        <v>6923840</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4233,7 +4196,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4243,7 +4206,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4258,22 +4226,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124900362</v>
+        <v>124898060</v>
       </c>
       <c r="B33" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4282,50 +4250,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>599864</v>
+        <v>599916</v>
       </c>
       <c r="R33" t="n">
-        <v>6923786</v>
+        <v>6923847</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4354,7 +4313,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4364,7 +4323,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4379,19 +4338,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124900764</v>
+        <v>124900226</v>
       </c>
       <c r="B34" t="n">
         <v>79891</v>
@@ -4425,16 +4384,21 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>599814</v>
+        <v>599882</v>
       </c>
       <c r="R34" t="n">
-        <v>6923824</v>
+        <v>6923778</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4466,7 +4430,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4476,7 +4440,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Över 20 apothecier</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4503,10 +4472,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124901634</v>
+        <v>124897942</v>
       </c>
       <c r="B35" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4515,38 +4484,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>599734</v>
+        <v>599929</v>
       </c>
       <c r="R35" t="n">
-        <v>6923810</v>
+        <v>6923847</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4578,7 +4552,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4588,7 +4562,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4603,22 +4582,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124898191</v>
+        <v>124900362</v>
       </c>
       <c r="B36" t="n">
-        <v>91673</v>
+        <v>98101</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4631,34 +4610,43 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>898</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>599930</v>
+        <v>599864</v>
       </c>
       <c r="R36" t="n">
-        <v>6923840</v>
+        <v>6923786</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4690,7 +4678,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4700,7 +4688,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4715,22 +4703,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124899839</v>
+        <v>124898096</v>
       </c>
       <c r="B37" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4743,39 +4731,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>599893</v>
+        <v>599930</v>
       </c>
       <c r="R37" t="n">
-        <v>6923773</v>
+        <v>6923840</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4807,7 +4790,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4817,12 +4800,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:35</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4837,22 +4815,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124900313</v>
+        <v>124899798</v>
       </c>
       <c r="B38" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4861,38 +4839,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>599854</v>
+        <v>599883</v>
       </c>
       <c r="R38" t="n">
-        <v>6923776</v>
+        <v>6923782</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4924,7 +4906,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4934,7 +4916,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4961,10 +4943,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124900025</v>
+        <v>124900330</v>
       </c>
       <c r="B39" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4973,42 +4955,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>599878</v>
+        <v>599899</v>
       </c>
       <c r="R39" t="n">
-        <v>6923820</v>
+        <v>6923798</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5040,7 +5018,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5050,7 +5028,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5065,22 +5043,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124902765</v>
+        <v>124901679</v>
       </c>
       <c r="B40" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5089,42 +5067,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>599800</v>
+        <v>599728</v>
       </c>
       <c r="R40" t="n">
-        <v>6923959</v>
+        <v>6923812</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5156,7 +5130,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5166,7 +5140,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5193,10 +5167,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124898060</v>
+        <v>124900465</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5209,37 +5183,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>599916</v>
+        <v>599856</v>
       </c>
       <c r="R41" t="n">
-        <v>6923847</v>
+        <v>6923803</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5268,7 +5242,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5278,7 +5252,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5293,22 +5267,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124900661</v>
+        <v>124901922</v>
       </c>
       <c r="B42" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5317,38 +5291,42 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>599813</v>
+        <v>599783</v>
       </c>
       <c r="R42" t="n">
-        <v>6923781</v>
+        <v>6923858</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5380,7 +5358,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5390,7 +5368,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5417,10 +5395,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124898290</v>
+        <v>124901767</v>
       </c>
       <c r="B43" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5429,43 +5407,42 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>599911</v>
+        <v>599748</v>
       </c>
       <c r="R43" t="n">
-        <v>6923836</v>
+        <v>6923842</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5497,7 +5474,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5507,12 +5484,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5527,22 +5499,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124900465</v>
+        <v>124900294</v>
       </c>
       <c r="B44" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5551,38 +5523,47 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>599856</v>
+        <v>599864</v>
       </c>
       <c r="R44" t="n">
-        <v>6923803</v>
+        <v>6923773</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5614,7 +5595,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5624,7 +5605,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5639,22 +5620,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124901880</v>
+        <v>124902509</v>
       </c>
       <c r="B45" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5667,34 +5648,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>599771</v>
+        <v>599754</v>
       </c>
       <c r="R45" t="n">
-        <v>6923841</v>
+        <v>6923921</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5726,7 +5712,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5736,12 +5722,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på asp</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5768,7 +5754,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124900018</v>
+        <v>124900773</v>
       </c>
       <c r="B46" t="n">
         <v>78810</v>
@@ -5804,14 +5790,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>599883</v>
+        <v>599801</v>
       </c>
       <c r="R46" t="n">
-        <v>6923768</v>
+        <v>6923797</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5843,7 +5829,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5853,7 +5839,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5868,22 +5854,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124899196</v>
+        <v>124899503</v>
       </c>
       <c r="B47" t="n">
-        <v>91457</v>
+        <v>91012</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5892,38 +5878,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>599888</v>
+        <v>599912</v>
       </c>
       <c r="R47" t="n">
-        <v>6923798</v>
+        <v>6923800</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5955,7 +5941,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5965,7 +5951,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5980,22 +5966,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124899341</v>
+        <v>124900661</v>
       </c>
       <c r="B48" t="n">
-        <v>90977</v>
+        <v>79891</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6004,38 +5990,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>599908</v>
+        <v>599813</v>
       </c>
       <c r="R48" t="n">
-        <v>6923811</v>
+        <v>6923781</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6067,7 +6053,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6077,7 +6063,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6092,22 +6078,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124900863</v>
+        <v>124900018</v>
       </c>
       <c r="B49" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6120,34 +6106,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>599779</v>
+        <v>599883</v>
       </c>
       <c r="R49" t="n">
-        <v>6923783</v>
+        <v>6923768</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6179,7 +6165,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6189,7 +6175,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6204,22 +6190,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124900663</v>
+        <v>124898571</v>
       </c>
       <c r="B50" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6232,34 +6218,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>599824</v>
+        <v>599904</v>
       </c>
       <c r="R50" t="n">
-        <v>6923802</v>
+        <v>6923812</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6291,7 +6282,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6301,7 +6292,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6316,22 +6312,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124901780</v>
+        <v>124902765</v>
       </c>
       <c r="B51" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6340,38 +6336,42 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>599756</v>
+        <v>599800</v>
       </c>
       <c r="R51" t="n">
-        <v>6923823</v>
+        <v>6923959</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6403,7 +6403,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6428,12 +6428,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124901880</v>
+        <v>124899616</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599771</v>
+        <v>599899</v>
       </c>
       <c r="R2" t="n">
-        <v>6923841</v>
+        <v>6923765</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:58</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på asp</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124898995</v>
+        <v>124900465</v>
       </c>
       <c r="B3" t="n">
-        <v>96979</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599930</v>
+        <v>599856</v>
       </c>
       <c r="R3" t="n">
-        <v>6923840</v>
+        <v>6923803</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124900863</v>
+        <v>124900661</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599779</v>
+        <v>599813</v>
       </c>
       <c r="R4" t="n">
-        <v>6923783</v>
+        <v>6923781</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124902015</v>
+        <v>124900362</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,38 +1023,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599777</v>
+        <v>599864</v>
       </c>
       <c r="R5" t="n">
-        <v>6923857</v>
+        <v>6923786</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,22 +1120,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124898168</v>
+        <v>124901624</v>
       </c>
       <c r="B6" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,38 +1144,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599920</v>
+        <v>599703</v>
       </c>
       <c r="R6" t="n">
-        <v>6923834</v>
+        <v>6923832</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,22 +1241,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124899644</v>
+        <v>124902015</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,34 +1269,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599898</v>
+        <v>599777</v>
       </c>
       <c r="R7" t="n">
-        <v>6923799</v>
+        <v>6923857</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124901624</v>
+        <v>124899503</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,47 +1377,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599703</v>
+        <v>599912</v>
       </c>
       <c r="R8" t="n">
-        <v>6923832</v>
+        <v>6923800</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,22 +1465,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124901584</v>
+        <v>124899196</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>91457</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,31 +1493,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599899</v>
+        <v>599888</v>
       </c>
       <c r="R9" t="n">
         <v>6923798</v>
@@ -1548,7 +1552,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1558,7 +1562,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1573,22 +1577,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124901921</v>
+        <v>124898168</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,47 +1601,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599742</v>
+        <v>599920</v>
       </c>
       <c r="R10" t="n">
-        <v>6923857</v>
+        <v>6923834</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1664,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1674,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1694,22 +1689,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124902350</v>
+        <v>124900313</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,58 +1717,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599899</v>
+        <v>599854</v>
       </c>
       <c r="R11" t="n">
-        <v>6923798</v>
+        <v>6923776</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1805,7 +1776,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1815,12 +1786,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:17</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett hona födosöker I en gran.</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,22 +1801,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124899564</v>
+        <v>124900018</v>
       </c>
       <c r="B12" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1863,21 +1829,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1887,10 +1853,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599910</v>
+        <v>599883</v>
       </c>
       <c r="R12" t="n">
-        <v>6923786</v>
+        <v>6923768</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1922,7 +1888,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1932,7 +1898,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1959,10 +1925,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124900313</v>
+        <v>124899644</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1975,21 +1941,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1999,10 +1965,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599854</v>
+        <v>599898</v>
       </c>
       <c r="R13" t="n">
-        <v>6923776</v>
+        <v>6923799</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2034,7 +2000,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2044,7 +2010,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2071,10 +2037,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124902691</v>
+        <v>124902350</v>
       </c>
       <c r="B14" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2087,34 +2053,58 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599798</v>
+        <v>599899</v>
       </c>
       <c r="R14" t="n">
-        <v>6923975</v>
+        <v>6923798</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2146,7 +2136,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2156,7 +2146,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett hona födosöker I en gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2171,19 +2166,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124901634</v>
+        <v>124900025</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2216,17 +2211,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599734</v>
+        <v>599878</v>
       </c>
       <c r="R15" t="n">
-        <v>6923810</v>
+        <v>6923820</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2258,7 +2257,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2268,7 +2267,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2283,22 +2282,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124899616</v>
+        <v>124901131</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2307,25 +2306,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2338,7 +2337,7 @@
         <v>599899</v>
       </c>
       <c r="R16" t="n">
-        <v>6923765</v>
+        <v>6923798</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2370,7 +2369,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2380,7 +2379,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2395,22 +2394,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124902839</v>
+        <v>124899421</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2423,34 +2422,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599810</v>
+        <v>599899</v>
       </c>
       <c r="R17" t="n">
-        <v>6923980</v>
+        <v>6923798</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2482,7 +2481,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2492,7 +2491,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2507,22 +2506,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124898290</v>
+        <v>124898995</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2531,43 +2530,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599911</v>
+        <v>599930</v>
       </c>
       <c r="R18" t="n">
-        <v>6923836</v>
+        <v>6923840</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2599,7 +2593,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2609,12 +2603,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2629,22 +2618,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124900764</v>
+        <v>124899839</v>
       </c>
       <c r="B19" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2657,34 +2646,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599814</v>
+        <v>599893</v>
       </c>
       <c r="R19" t="n">
-        <v>6923824</v>
+        <v>6923773</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2716,7 +2710,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2726,7 +2720,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2741,19 +2740,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124901889</v>
+        <v>124900764</v>
       </c>
       <c r="B20" t="n">
         <v>79891</v>
@@ -2793,10 +2792,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599775</v>
+        <v>599814</v>
       </c>
       <c r="R20" t="n">
-        <v>6923855</v>
+        <v>6923824</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2828,7 +2827,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2838,7 +2837,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2865,10 +2864,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124900663</v>
+        <v>124902691</v>
       </c>
       <c r="B21" t="n">
-        <v>79891</v>
+        <v>91030</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2881,34 +2880,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599824</v>
+        <v>599798</v>
       </c>
       <c r="R21" t="n">
-        <v>6923802</v>
+        <v>6923975</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2940,7 +2939,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2950,7 +2949,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2965,22 +2964,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124900025</v>
+        <v>124898316</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2989,42 +2988,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>599878</v>
+        <v>599918</v>
       </c>
       <c r="R22" t="n">
-        <v>6923820</v>
+        <v>6923822</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3056,7 +3051,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3066,7 +3061,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3093,10 +3088,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124899196</v>
+        <v>124900827</v>
       </c>
       <c r="B23" t="n">
-        <v>91457</v>
+        <v>57529</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3105,38 +3100,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>599888</v>
+        <v>599787</v>
       </c>
       <c r="R23" t="n">
-        <v>6923798</v>
+        <v>6923799</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3205,10 +3205,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124898316</v>
+        <v>124900663</v>
       </c>
       <c r="B24" t="n">
-        <v>91299</v>
+        <v>79891</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3221,34 +3221,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>599918</v>
+        <v>599824</v>
       </c>
       <c r="R24" t="n">
-        <v>6923822</v>
+        <v>6923802</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3305,22 +3305,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124899421</v>
+        <v>124901634</v>
       </c>
       <c r="B25" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3329,25 +3329,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3357,10 +3357,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>599899</v>
+        <v>599734</v>
       </c>
       <c r="R25" t="n">
-        <v>6923798</v>
+        <v>6923810</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3417,22 +3417,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124900786</v>
+        <v>124898290</v>
       </c>
       <c r="B26" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3445,16 +3445,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3465,19 +3465,19 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>599791</v>
+        <v>599911</v>
       </c>
       <c r="R26" t="n">
-        <v>6923786</v>
+        <v>6923836</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3519,7 +3519,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3546,10 +3551,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124899341</v>
+        <v>124898191</v>
       </c>
       <c r="B27" t="n">
-        <v>90977</v>
+        <v>91673</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3558,25 +3563,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>898</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3586,10 +3591,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>599908</v>
+        <v>599930</v>
       </c>
       <c r="R27" t="n">
-        <v>6923811</v>
+        <v>6923840</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3621,7 +3626,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3631,7 +3636,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3658,10 +3663,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124900827</v>
+        <v>124899564</v>
       </c>
       <c r="B28" t="n">
-        <v>57529</v>
+        <v>91299</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3674,39 +3679,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>599787</v>
+        <v>599910</v>
       </c>
       <c r="R28" t="n">
-        <v>6923799</v>
+        <v>6923786</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3763,19 +3763,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124899839</v>
+        <v>124898571</v>
       </c>
       <c r="B29" t="n">
         <v>57513</v>
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>599893</v>
+        <v>599904</v>
       </c>
       <c r="R29" t="n">
-        <v>6923773</v>
+        <v>6923812</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3855,7 +3855,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3897,7 +3897,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124901780</v>
+        <v>124901889</v>
       </c>
       <c r="B30" t="n">
         <v>79891</v>
@@ -3937,10 +3937,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>599756</v>
+        <v>599775</v>
       </c>
       <c r="R30" t="n">
-        <v>6923823</v>
+        <v>6923855</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3972,7 +3972,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4009,10 +4009,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124898191</v>
+        <v>124902509</v>
       </c>
       <c r="B31" t="n">
-        <v>91673</v>
+        <v>57513</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4021,38 +4021,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>599930</v>
+        <v>599754</v>
       </c>
       <c r="R31" t="n">
-        <v>6923840</v>
+        <v>6923921</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4084,7 +4089,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4094,7 +4099,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>18:29</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4109,22 +4119,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124898054</v>
+        <v>124901922</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4133,38 +4143,42 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>599930</v>
+        <v>599783</v>
       </c>
       <c r="R32" t="n">
-        <v>6923840</v>
+        <v>6923858</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4196,7 +4210,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4206,12 +4220,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4226,22 +4235,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124898060</v>
+        <v>124901921</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4250,41 +4259,50 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>599916</v>
+        <v>599742</v>
       </c>
       <c r="R33" t="n">
-        <v>6923847</v>
+        <v>6923857</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4313,7 +4331,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4323,7 +4341,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4338,22 +4356,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124900226</v>
+        <v>124897942</v>
       </c>
       <c r="B34" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4366,39 +4384,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>599882</v>
+        <v>599929</v>
       </c>
       <c r="R34" t="n">
-        <v>6923778</v>
+        <v>6923847</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4430,7 +4448,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4440,12 +4458,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Över 20 apothecier</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4460,22 +4478,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124897942</v>
+        <v>124899195</v>
       </c>
       <c r="B35" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4488,39 +4506,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>599929</v>
+        <v>599930</v>
       </c>
       <c r="R35" t="n">
-        <v>6923847</v>
+        <v>6923840</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4552,7 +4565,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4562,12 +4575,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4582,22 +4590,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124900362</v>
+        <v>124899341</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4606,47 +4614,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>599864</v>
+        <v>599908</v>
       </c>
       <c r="R36" t="n">
-        <v>6923786</v>
+        <v>6923811</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4678,7 +4677,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4688,7 +4687,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4703,22 +4702,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124898096</v>
+        <v>124901679</v>
       </c>
       <c r="B37" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4731,34 +4730,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>599930</v>
+        <v>599728</v>
       </c>
       <c r="R37" t="n">
-        <v>6923840</v>
+        <v>6923812</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4790,7 +4789,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4800,7 +4799,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4815,22 +4814,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124899798</v>
+        <v>124898054</v>
       </c>
       <c r="B38" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4839,42 +4838,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>599883</v>
+        <v>599930</v>
       </c>
       <c r="R38" t="n">
-        <v>6923782</v>
+        <v>6923840</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4906,7 +4901,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4916,7 +4911,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4931,22 +4931,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124900330</v>
+        <v>124899798</v>
       </c>
       <c r="B39" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4955,38 +4955,42 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>599899</v>
+        <v>599883</v>
       </c>
       <c r="R39" t="n">
-        <v>6923798</v>
+        <v>6923782</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5018,7 +5022,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5028,7 +5032,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5043,22 +5047,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124901679</v>
+        <v>124902839</v>
       </c>
       <c r="B40" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5071,21 +5075,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5095,10 +5099,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>599728</v>
+        <v>599810</v>
       </c>
       <c r="R40" t="n">
-        <v>6923812</v>
+        <v>6923980</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5130,7 +5134,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5140,7 +5144,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5167,10 +5171,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124900465</v>
+        <v>124900330</v>
       </c>
       <c r="B41" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5183,21 +5187,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5207,10 +5211,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>599856</v>
+        <v>599899</v>
       </c>
       <c r="R41" t="n">
-        <v>6923803</v>
+        <v>6923798</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5242,7 +5246,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5252,7 +5256,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5267,22 +5271,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124901922</v>
+        <v>124898060</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5291,45 +5295,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>599783</v>
+        <v>599916</v>
       </c>
       <c r="R42" t="n">
-        <v>6923858</v>
+        <v>6923847</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5395,10 +5395,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124901767</v>
+        <v>124900226</v>
       </c>
       <c r="B43" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5407,42 +5407,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>599748</v>
+        <v>599882</v>
       </c>
       <c r="R43" t="n">
-        <v>6923842</v>
+        <v>6923778</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5474,7 +5475,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5484,7 +5485,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Över 20 apothecier</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5499,19 +5505,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124900294</v>
+        <v>124901767</v>
       </c>
       <c r="B44" t="n">
         <v>98101</v>
@@ -5546,24 +5552,19 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>599864</v>
+        <v>599748</v>
       </c>
       <c r="R44" t="n">
-        <v>6923773</v>
+        <v>6923842</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5595,7 +5596,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5605,7 +5606,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5620,22 +5621,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124902509</v>
+        <v>124900786</v>
       </c>
       <c r="B45" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5648,16 +5649,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5677,10 +5678,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>599754</v>
+        <v>599791</v>
       </c>
       <c r="R45" t="n">
-        <v>6923921</v>
+        <v>6923786</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5712,7 +5713,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5722,12 +5723,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:29</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5742,22 +5738,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124900773</v>
+        <v>124900863</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5770,21 +5766,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5794,10 +5790,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>599801</v>
+        <v>599779</v>
       </c>
       <c r="R46" t="n">
-        <v>6923797</v>
+        <v>6923783</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5829,7 +5825,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5839,7 +5835,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5866,10 +5862,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124899503</v>
+        <v>124900773</v>
       </c>
       <c r="B47" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5882,34 +5878,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>599912</v>
+        <v>599801</v>
       </c>
       <c r="R47" t="n">
-        <v>6923800</v>
+        <v>6923797</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5941,7 +5937,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5951,7 +5947,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5966,22 +5962,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124900661</v>
+        <v>124902765</v>
       </c>
       <c r="B48" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5990,38 +5986,42 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>599813</v>
+        <v>599800</v>
       </c>
       <c r="R48" t="n">
-        <v>6923781</v>
+        <v>6923959</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6053,7 +6053,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6063,7 +6063,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6090,10 +6090,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124900018</v>
+        <v>124901880</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6106,34 +6106,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>599883</v>
+        <v>599771</v>
       </c>
       <c r="R49" t="n">
-        <v>6923768</v>
+        <v>6923841</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6165,7 +6165,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6175,7 +6175,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på asp</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6190,22 +6195,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124898571</v>
+        <v>124900294</v>
       </c>
       <c r="B50" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6214,31 +6219,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6247,10 +6256,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>599904</v>
+        <v>599864</v>
       </c>
       <c r="R50" t="n">
-        <v>6923812</v>
+        <v>6923773</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6282,7 +6291,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6292,12 +6301,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:05</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6324,10 +6328,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124902765</v>
+        <v>124901780</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6336,42 +6340,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>599800</v>
+        <v>599756</v>
       </c>
       <c r="R51" t="n">
-        <v>6923959</v>
+        <v>6923823</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6403,7 +6403,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6428,12 +6428,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124899616</v>
+        <v>124900465</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599899</v>
+        <v>599856</v>
       </c>
       <c r="R2" t="n">
-        <v>6923765</v>
+        <v>6923803</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124900465</v>
+        <v>124899616</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599856</v>
+        <v>599899</v>
       </c>
       <c r="R3" t="n">
-        <v>6923803</v>
+        <v>6923765</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1589,10 +1589,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124898168</v>
+        <v>124900025</v>
       </c>
       <c r="B10" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,38 +1601,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599920</v>
+        <v>599878</v>
       </c>
       <c r="R10" t="n">
-        <v>6923834</v>
+        <v>6923820</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1664,7 +1668,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1674,7 +1678,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1701,10 +1705,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124900313</v>
+        <v>124898168</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1717,21 +1721,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1741,10 +1745,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599854</v>
+        <v>599920</v>
       </c>
       <c r="R11" t="n">
-        <v>6923776</v>
+        <v>6923834</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1776,7 +1780,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1786,7 +1790,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1813,7 +1817,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124900018</v>
+        <v>124899644</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1849,14 +1853,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599883</v>
+        <v>599898</v>
       </c>
       <c r="R12" t="n">
-        <v>6923768</v>
+        <v>6923799</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1888,7 +1892,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1898,7 +1902,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1913,22 +1917,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124899644</v>
+        <v>124900313</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1941,21 +1945,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1965,10 +1969,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599898</v>
+        <v>599854</v>
       </c>
       <c r="R13" t="n">
-        <v>6923799</v>
+        <v>6923776</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2000,7 +2004,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2010,7 +2014,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2037,10 +2041,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124902350</v>
+        <v>124900018</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2053,58 +2057,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599899</v>
+        <v>599883</v>
       </c>
       <c r="R14" t="n">
-        <v>6923798</v>
+        <v>6923768</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2136,7 +2116,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2146,12 +2126,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:17</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett hona födosöker I en gran.</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2166,22 +2141,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124900025</v>
+        <v>124902350</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2190,42 +2165,62 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599878</v>
+        <v>599899</v>
       </c>
       <c r="R15" t="n">
-        <v>6923820</v>
+        <v>6923798</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2257,7 +2252,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2267,7 +2262,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett hona födosöker I en gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2282,12 +2282,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -3429,10 +3429,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124898290</v>
+        <v>124898191</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>91673</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3441,43 +3441,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>599911</v>
+        <v>599930</v>
       </c>
       <c r="R26" t="n">
-        <v>6923836</v>
+        <v>6923840</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3509,7 +3504,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3519,12 +3514,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3539,22 +3529,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124898191</v>
+        <v>124898290</v>
       </c>
       <c r="B27" t="n">
-        <v>91673</v>
+        <v>57513</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3563,38 +3553,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>599930</v>
+        <v>599911</v>
       </c>
       <c r="R27" t="n">
-        <v>6923840</v>
+        <v>6923836</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3626,7 +3621,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3636,7 +3631,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3651,12 +3651,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -4368,10 +4368,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124897942</v>
+        <v>124899195</v>
       </c>
       <c r="B34" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4384,39 +4384,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>599929</v>
+        <v>599930</v>
       </c>
       <c r="R34" t="n">
-        <v>6923847</v>
+        <v>6923840</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4448,7 +4443,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4458,12 +4453,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4478,22 +4468,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124899195</v>
+        <v>124899341</v>
       </c>
       <c r="B35" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4502,25 +4492,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4530,10 +4520,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>599930</v>
+        <v>599908</v>
       </c>
       <c r="R35" t="n">
-        <v>6923840</v>
+        <v>6923811</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4565,7 +4555,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4575,7 +4565,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4602,10 +4592,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124899341</v>
+        <v>124897942</v>
       </c>
       <c r="B36" t="n">
-        <v>90977</v>
+        <v>57513</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4614,38 +4604,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>599908</v>
+        <v>599929</v>
       </c>
       <c r="R36" t="n">
-        <v>6923811</v>
+        <v>6923847</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4677,7 +4672,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4687,7 +4682,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4702,12 +4702,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -5517,10 +5517,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124901767</v>
+        <v>124900786</v>
       </c>
       <c r="B44" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5529,30 +5529,31 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5561,10 +5562,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>599748</v>
+        <v>599791</v>
       </c>
       <c r="R44" t="n">
-        <v>6923842</v>
+        <v>6923786</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5596,7 +5597,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5606,7 +5607,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5621,22 +5622,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124900786</v>
+        <v>124901767</v>
       </c>
       <c r="B45" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5645,31 +5646,30 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5678,10 +5678,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>599791</v>
+        <v>599748</v>
       </c>
       <c r="R45" t="n">
-        <v>6923786</v>
+        <v>6923842</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5713,7 +5713,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5738,12 +5738,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124899503</v>
+        <v>124899644</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,34 +1381,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599912</v>
+        <v>599898</v>
       </c>
       <c r="R8" t="n">
-        <v>6923800</v>
+        <v>6923799</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,22 +1465,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124899196</v>
+        <v>124902350</v>
       </c>
       <c r="B9" t="n">
-        <v>91457</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,35 +1489,59 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599888</v>
+        <v>599899</v>
       </c>
       <c r="R9" t="n">
         <v>6923798</v>
@@ -1552,7 +1576,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,7 +1586,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett hona födosöker I en gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,12 +1606,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1705,10 +1734,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124898168</v>
+        <v>124899503</v>
       </c>
       <c r="B11" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,34 +1750,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599920</v>
+        <v>599912</v>
       </c>
       <c r="R11" t="n">
-        <v>6923834</v>
+        <v>6923800</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1780,7 +1809,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1790,7 +1819,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,22 +1834,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124899644</v>
+        <v>124899196</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>91457</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1829,25 +1858,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1857,10 +1886,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599898</v>
+        <v>599888</v>
       </c>
       <c r="R12" t="n">
-        <v>6923799</v>
+        <v>6923798</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1892,7 +1921,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1902,7 +1931,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1929,10 +1958,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124900313</v>
+        <v>124898168</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1945,21 +1974,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1969,10 +1998,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599854</v>
+        <v>599920</v>
       </c>
       <c r="R13" t="n">
-        <v>6923776</v>
+        <v>6923834</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2004,7 +2033,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2014,7 +2043,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,10 +2070,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124900018</v>
+        <v>124900313</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2057,34 +2086,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599883</v>
+        <v>599854</v>
       </c>
       <c r="R14" t="n">
-        <v>6923768</v>
+        <v>6923776</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2116,7 +2145,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2126,7 +2155,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2141,22 +2170,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124902350</v>
+        <v>124900018</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2169,58 +2198,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599899</v>
+        <v>599883</v>
       </c>
       <c r="R15" t="n">
-        <v>6923798</v>
+        <v>6923768</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2252,7 +2257,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2262,12 +2267,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:17</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett hona födosöker I en gran.</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2282,22 +2282,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124901131</v>
+        <v>124899839</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2306,38 +2306,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599899</v>
+        <v>599893</v>
       </c>
       <c r="R16" t="n">
-        <v>6923798</v>
+        <v>6923773</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2369,7 +2374,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2379,7 +2384,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2394,22 +2404,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124899421</v>
+        <v>124898995</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>96979</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2418,25 +2428,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2446,10 +2456,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599899</v>
+        <v>599930</v>
       </c>
       <c r="R17" t="n">
-        <v>6923798</v>
+        <v>6923840</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2481,7 +2491,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2491,7 +2501,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2506,22 +2516,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124898995</v>
+        <v>124901131</v>
       </c>
       <c r="B18" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2530,25 +2540,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2558,10 +2568,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599930</v>
+        <v>599899</v>
       </c>
       <c r="R18" t="n">
-        <v>6923840</v>
+        <v>6923798</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2593,7 +2603,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2603,7 +2613,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2618,22 +2628,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124899839</v>
+        <v>124899421</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2646,39 +2656,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599893</v>
+        <v>599899</v>
       </c>
       <c r="R19" t="n">
-        <v>6923773</v>
+        <v>6923798</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2710,7 +2715,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2720,12 +2725,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:35</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2740,12 +2740,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -3429,10 +3429,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124898191</v>
+        <v>124898290</v>
       </c>
       <c r="B26" t="n">
-        <v>91673</v>
+        <v>57513</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3441,38 +3441,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>599930</v>
+        <v>599911</v>
       </c>
       <c r="R26" t="n">
-        <v>6923840</v>
+        <v>6923836</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3504,7 +3509,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3514,7 +3519,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3529,22 +3539,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124898290</v>
+        <v>124898191</v>
       </c>
       <c r="B27" t="n">
-        <v>57513</v>
+        <v>91673</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3553,43 +3563,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>599911</v>
+        <v>599930</v>
       </c>
       <c r="R27" t="n">
-        <v>6923836</v>
+        <v>6923840</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3621,7 +3626,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3631,12 +3636,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3651,12 +3651,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -5283,10 +5283,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124898060</v>
+        <v>124900226</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5299,37 +5299,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>599916</v>
+        <v>599882</v>
       </c>
       <c r="R42" t="n">
-        <v>6923847</v>
+        <v>6923778</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5358,7 +5363,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5368,7 +5373,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Över 20 apothecier</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5383,22 +5393,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124900226</v>
+        <v>124898060</v>
       </c>
       <c r="B43" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5411,42 +5421,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>599882</v>
+        <v>599916</v>
       </c>
       <c r="R43" t="n">
-        <v>6923778</v>
+        <v>6923847</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5475,7 +5480,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5485,12 +5490,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:43</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Över 20 apothecier</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5505,12 +5505,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124900465</v>
+        <v>124900863</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599856</v>
+        <v>599779</v>
       </c>
       <c r="R2" t="n">
-        <v>6923803</v>
+        <v>6923783</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124899616</v>
+        <v>124899564</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599899</v>
+        <v>599910</v>
       </c>
       <c r="R3" t="n">
-        <v>6923765</v>
+        <v>6923786</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124900661</v>
+        <v>124900362</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,38 +911,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599813</v>
+        <v>599864</v>
       </c>
       <c r="R4" t="n">
-        <v>6923781</v>
+        <v>6923786</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,19 +1008,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124900362</v>
+        <v>124901131</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1044,26 +1053,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599864</v>
+        <v>599899</v>
       </c>
       <c r="R5" t="n">
-        <v>6923786</v>
+        <v>6923798</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,19 +1120,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124901624</v>
+        <v>124901634</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1165,26 +1165,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599703</v>
+        <v>599734</v>
       </c>
       <c r="R6" t="n">
-        <v>6923832</v>
+        <v>6923810</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,22 +1232,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124902015</v>
+        <v>124898060</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,37 +1260,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599777</v>
+        <v>599916</v>
       </c>
       <c r="R7" t="n">
-        <v>6923857</v>
+        <v>6923847</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1328,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124899644</v>
+        <v>124901880</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,34 +1372,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599898</v>
+        <v>599771</v>
       </c>
       <c r="R8" t="n">
-        <v>6923799</v>
+        <v>6923841</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,7 +1431,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,7 +1441,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på asp</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124902350</v>
+        <v>124902691</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1493,58 +1489,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599899</v>
+        <v>599798</v>
       </c>
       <c r="R9" t="n">
-        <v>6923798</v>
+        <v>6923975</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1576,7 +1548,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1586,12 +1558,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett hona födosöker I en gran.</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1606,22 +1573,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124900025</v>
+        <v>124898290</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1630,30 +1597,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>12</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1662,10 +1630,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599878</v>
+        <v>599911</v>
       </c>
       <c r="R10" t="n">
-        <v>6923820</v>
+        <v>6923836</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1697,7 +1665,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1707,7 +1675,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1722,22 +1695,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124899503</v>
+        <v>124898995</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>96979</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1746,25 +1719,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1774,10 +1747,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599912</v>
+        <v>599930</v>
       </c>
       <c r="R11" t="n">
-        <v>6923800</v>
+        <v>6923840</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1809,7 +1782,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1819,7 +1792,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1846,10 +1819,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124899196</v>
+        <v>124900786</v>
       </c>
       <c r="B12" t="n">
-        <v>91457</v>
+        <v>57529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1858,38 +1831,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599888</v>
+        <v>599791</v>
       </c>
       <c r="R12" t="n">
-        <v>6923798</v>
+        <v>6923786</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1921,7 +1899,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1931,7 +1909,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1946,22 +1924,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124898168</v>
+        <v>124898096</v>
       </c>
       <c r="B13" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1974,34 +1952,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599920</v>
+        <v>599930</v>
       </c>
       <c r="R13" t="n">
-        <v>6923834</v>
+        <v>6923840</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2033,7 +2011,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2043,7 +2021,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2058,22 +2036,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124900313</v>
+        <v>124898054</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2086,34 +2064,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599854</v>
+        <v>599930</v>
       </c>
       <c r="R14" t="n">
-        <v>6923776</v>
+        <v>6923840</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2145,7 +2123,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2155,7 +2133,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,22 +2153,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124900018</v>
+        <v>124900330</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2198,21 +2181,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2222,10 +2205,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599883</v>
+        <v>599899</v>
       </c>
       <c r="R15" t="n">
-        <v>6923768</v>
+        <v>6923798</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2257,7 +2240,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2267,7 +2250,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2282,22 +2265,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124899839</v>
+        <v>124901767</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2306,43 +2289,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599893</v>
+        <v>599748</v>
       </c>
       <c r="R16" t="n">
-        <v>6923773</v>
+        <v>6923842</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2374,7 +2356,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2384,12 +2366,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:35</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2404,22 +2381,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124898995</v>
+        <v>124897942</v>
       </c>
       <c r="B17" t="n">
-        <v>96979</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2428,38 +2405,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599930</v>
+        <v>599929</v>
       </c>
       <c r="R17" t="n">
-        <v>6923840</v>
+        <v>6923847</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2491,7 +2473,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2501,7 +2483,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2516,19 +2503,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124901131</v>
+        <v>124899798</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2561,17 +2548,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599899</v>
+        <v>599883</v>
       </c>
       <c r="R18" t="n">
-        <v>6923798</v>
+        <v>6923782</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2603,7 +2594,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2613,7 +2604,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2628,22 +2619,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124899421</v>
+        <v>124898191</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>91673</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2652,25 +2643,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2680,10 +2671,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599899</v>
+        <v>599930</v>
       </c>
       <c r="R19" t="n">
-        <v>6923798</v>
+        <v>6923840</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2715,7 +2706,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2725,7 +2716,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2740,12 +2731,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2864,10 +2855,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124902691</v>
+        <v>124902509</v>
       </c>
       <c r="B21" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2880,34 +2871,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599798</v>
+        <v>599754</v>
       </c>
       <c r="R21" t="n">
-        <v>6923975</v>
+        <v>6923921</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2939,7 +2935,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2949,7 +2945,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2976,10 +2977,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124898316</v>
+        <v>124901624</v>
       </c>
       <c r="B22" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2988,38 +2989,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>599918</v>
+        <v>599703</v>
       </c>
       <c r="R22" t="n">
-        <v>6923822</v>
+        <v>6923832</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3051,7 +3061,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3061,7 +3071,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3076,22 +3086,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124900827</v>
+        <v>124898571</v>
       </c>
       <c r="B23" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3104,16 +3114,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3129,14 +3139,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>599787</v>
+        <v>599904</v>
       </c>
       <c r="R23" t="n">
-        <v>6923799</v>
+        <v>6923812</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3168,7 +3178,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3178,7 +3188,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3193,22 +3208,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124900663</v>
+        <v>124899644</v>
       </c>
       <c r="B24" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3221,34 +3236,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>599824</v>
+        <v>599898</v>
       </c>
       <c r="R24" t="n">
-        <v>6923802</v>
+        <v>6923799</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3280,7 +3295,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3290,7 +3305,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3305,22 +3320,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124901634</v>
+        <v>124900226</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3329,38 +3344,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>599734</v>
+        <v>599882</v>
       </c>
       <c r="R25" t="n">
-        <v>6923810</v>
+        <v>6923778</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3392,7 +3412,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3402,7 +3422,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Över 20 apothecier</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3429,10 +3454,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124898290</v>
+        <v>124902015</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3445,39 +3470,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>599911</v>
+        <v>599777</v>
       </c>
       <c r="R26" t="n">
-        <v>6923836</v>
+        <v>6923857</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3509,7 +3529,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3519,12 +3539,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3539,22 +3554,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124898191</v>
+        <v>124900025</v>
       </c>
       <c r="B27" t="n">
-        <v>91673</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3567,34 +3582,38 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>898</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>599930</v>
+        <v>599878</v>
       </c>
       <c r="R27" t="n">
-        <v>6923840</v>
+        <v>6923820</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3626,7 +3645,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3636,7 +3655,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3651,22 +3670,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124899564</v>
+        <v>124902350</v>
       </c>
       <c r="B28" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3679,34 +3698,58 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>599910</v>
+        <v>599899</v>
       </c>
       <c r="R28" t="n">
-        <v>6923786</v>
+        <v>6923798</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3738,7 +3781,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3748,7 +3791,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett hona födosöker I en gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3763,22 +3811,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124898571</v>
+        <v>124899616</v>
       </c>
       <c r="B29" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3791,39 +3839,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>599904</v>
+        <v>599899</v>
       </c>
       <c r="R29" t="n">
-        <v>6923812</v>
+        <v>6923765</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3855,7 +3898,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3865,12 +3908,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:05</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3885,19 +3923,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124901889</v>
+        <v>124901679</v>
       </c>
       <c r="B30" t="n">
         <v>79891</v>
@@ -3933,14 +3971,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>599775</v>
+        <v>599728</v>
       </c>
       <c r="R30" t="n">
-        <v>6923855</v>
+        <v>6923812</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3972,7 +4010,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3982,7 +4020,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3997,22 +4035,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124902509</v>
+        <v>124902765</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4021,31 +4059,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4054,10 +4091,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>599754</v>
+        <v>599800</v>
       </c>
       <c r="R31" t="n">
-        <v>6923921</v>
+        <v>6923959</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4089,7 +4126,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4099,12 +4136,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:29</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4131,10 +4163,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124901922</v>
+        <v>124900465</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4143,42 +4175,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>599783</v>
+        <v>599856</v>
       </c>
       <c r="R32" t="n">
-        <v>6923858</v>
+        <v>6923803</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4210,7 +4238,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4220,7 +4248,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4235,22 +4263,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124901921</v>
+        <v>124899196</v>
       </c>
       <c r="B33" t="n">
-        <v>98101</v>
+        <v>91457</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4263,43 +4291,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>599742</v>
+        <v>599888</v>
       </c>
       <c r="R33" t="n">
-        <v>6923857</v>
+        <v>6923798</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4331,7 +4350,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4341,7 +4360,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4356,22 +4375,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124899195</v>
+        <v>124900661</v>
       </c>
       <c r="B34" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4384,34 +4403,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>599930</v>
+        <v>599813</v>
       </c>
       <c r="R34" t="n">
-        <v>6923840</v>
+        <v>6923781</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4443,7 +4462,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4453,7 +4472,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4468,22 +4487,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124899341</v>
+        <v>124900018</v>
       </c>
       <c r="B35" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4492,25 +4511,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4520,10 +4539,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>599908</v>
+        <v>599883</v>
       </c>
       <c r="R35" t="n">
-        <v>6923811</v>
+        <v>6923768</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4555,7 +4574,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4565,7 +4584,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4592,10 +4611,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124897942</v>
+        <v>124898316</v>
       </c>
       <c r="B36" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4608,39 +4627,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>599929</v>
+        <v>599918</v>
       </c>
       <c r="R36" t="n">
-        <v>6923847</v>
+        <v>6923822</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4672,7 +4686,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4682,12 +4696,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4702,19 +4711,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124901679</v>
+        <v>124901889</v>
       </c>
       <c r="B37" t="n">
         <v>79891</v>
@@ -4750,14 +4759,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>599728</v>
+        <v>599775</v>
       </c>
       <c r="R37" t="n">
-        <v>6923812</v>
+        <v>6923855</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4789,7 +4798,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4799,7 +4808,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4814,19 +4823,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124898054</v>
+        <v>124902839</v>
       </c>
       <c r="B38" t="n">
         <v>78810</v>
@@ -4862,14 +4871,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>599930</v>
+        <v>599810</v>
       </c>
       <c r="R38" t="n">
-        <v>6923840</v>
+        <v>6923980</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4901,7 +4910,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4911,12 +4920,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4931,22 +4935,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124899798</v>
+        <v>124899839</v>
       </c>
       <c r="B39" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4955,30 +4959,31 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4987,10 +4992,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>599883</v>
+        <v>599893</v>
       </c>
       <c r="R39" t="n">
-        <v>6923782</v>
+        <v>6923773</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5022,7 +5027,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5032,7 +5037,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5047,22 +5057,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124902839</v>
+        <v>124901780</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5075,34 +5085,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>599810</v>
+        <v>599756</v>
       </c>
       <c r="R40" t="n">
-        <v>6923980</v>
+        <v>6923823</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5134,7 +5144,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5144,7 +5154,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5159,22 +5169,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124900330</v>
+        <v>124900773</v>
       </c>
       <c r="B41" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5187,34 +5197,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>599899</v>
+        <v>599801</v>
       </c>
       <c r="R41" t="n">
-        <v>6923798</v>
+        <v>6923797</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5246,7 +5256,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5256,7 +5266,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5271,22 +5281,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124900226</v>
+        <v>124901921</v>
       </c>
       <c r="B42" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5295,43 +5305,47 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>599882</v>
+        <v>599742</v>
       </c>
       <c r="R42" t="n">
-        <v>6923778</v>
+        <v>6923857</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5363,7 +5377,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5373,12 +5387,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:43</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Över 20 apothecier</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5393,22 +5402,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124898060</v>
+        <v>124898168</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5421,21 +5430,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5445,13 +5454,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>599916</v>
+        <v>599920</v>
       </c>
       <c r="R43" t="n">
-        <v>6923847</v>
+        <v>6923834</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5480,7 +5489,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5490,7 +5499,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5517,10 +5526,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124900786</v>
+        <v>124899421</v>
       </c>
       <c r="B44" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5533,39 +5542,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>599791</v>
+        <v>599899</v>
       </c>
       <c r="R44" t="n">
-        <v>6923786</v>
+        <v>6923798</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5597,7 +5601,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5607,7 +5611,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5622,22 +5626,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124901767</v>
+        <v>124900827</v>
       </c>
       <c r="B45" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5646,30 +5650,31 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5678,10 +5683,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>599748</v>
+        <v>599787</v>
       </c>
       <c r="R45" t="n">
-        <v>6923842</v>
+        <v>6923799</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5713,7 +5718,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5723,7 +5728,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5750,10 +5755,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124900863</v>
+        <v>124899341</v>
       </c>
       <c r="B46" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5762,38 +5767,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>599779</v>
+        <v>599908</v>
       </c>
       <c r="R46" t="n">
-        <v>6923783</v>
+        <v>6923811</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5825,7 +5830,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5835,7 +5840,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5850,22 +5855,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124900773</v>
+        <v>124900663</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5878,34 +5883,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>599801</v>
+        <v>599824</v>
       </c>
       <c r="R47" t="n">
-        <v>6923797</v>
+        <v>6923802</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5937,7 +5942,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5947,7 +5952,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5962,19 +5967,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124902765</v>
+        <v>124901922</v>
       </c>
       <c r="B48" t="n">
         <v>98101</v>
@@ -6009,7 +6014,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6018,10 +6023,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>599800</v>
+        <v>599783</v>
       </c>
       <c r="R48" t="n">
-        <v>6923959</v>
+        <v>6923858</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6053,7 +6058,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6063,7 +6068,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6090,10 +6095,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124901880</v>
+        <v>124900294</v>
       </c>
       <c r="B49" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6102,38 +6107,47 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>599771</v>
+        <v>599864</v>
       </c>
       <c r="R49" t="n">
-        <v>6923841</v>
+        <v>6923773</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6165,7 +6179,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6175,12 +6189,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:58</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på asp</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6195,22 +6204,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124900294</v>
+        <v>124899503</v>
       </c>
       <c r="B50" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6219,47 +6228,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>599864</v>
+        <v>599912</v>
       </c>
       <c r="R50" t="n">
-        <v>6923773</v>
+        <v>6923800</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6291,7 +6291,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6316,19 +6316,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124901780</v>
+        <v>124900313</v>
       </c>
       <c r="B51" t="n">
         <v>79891</v>
@@ -6364,14 +6364,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>599756</v>
+        <v>599854</v>
       </c>
       <c r="R51" t="n">
-        <v>6923823</v>
+        <v>6923776</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6403,7 +6403,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6428,12 +6428,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124900863</v>
+        <v>124898191</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>91673</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599779</v>
+        <v>599930</v>
       </c>
       <c r="R2" t="n">
-        <v>6923783</v>
+        <v>6923840</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124899564</v>
+        <v>124900313</v>
       </c>
       <c r="B3" t="n">
-        <v>91299</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599910</v>
+        <v>599854</v>
       </c>
       <c r="R3" t="n">
-        <v>6923786</v>
+        <v>6923776</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124900362</v>
+        <v>124900764</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,47 +911,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599864</v>
+        <v>599814</v>
       </c>
       <c r="R4" t="n">
-        <v>6923786</v>
+        <v>6923824</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,22 +999,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124901131</v>
+        <v>124901880</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,38 +1023,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599899</v>
+        <v>599771</v>
       </c>
       <c r="R5" t="n">
-        <v>6923798</v>
+        <v>6923841</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1096,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på asp</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,22 +1116,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124901634</v>
+        <v>124902509</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,38 +1140,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599734</v>
+        <v>599754</v>
       </c>
       <c r="R6" t="n">
-        <v>6923810</v>
+        <v>6923921</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1218,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,22 +1238,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124898060</v>
+        <v>124900226</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,37 +1266,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599916</v>
+        <v>599882</v>
       </c>
       <c r="R7" t="n">
-        <v>6923847</v>
+        <v>6923778</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1319,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1340,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Över 20 apothecier</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,22 +1360,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124901880</v>
+        <v>124899503</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,34 +1388,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599771</v>
+        <v>599912</v>
       </c>
       <c r="R8" t="n">
-        <v>6923841</v>
+        <v>6923800</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1441,12 +1457,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:58</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på asp</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,22 +1472,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124902691</v>
+        <v>124899421</v>
       </c>
       <c r="B9" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,34 +1500,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599798</v>
+        <v>599899</v>
       </c>
       <c r="R9" t="n">
-        <v>6923975</v>
+        <v>6923798</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1558,7 +1569,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1573,22 +1584,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124898290</v>
+        <v>124898995</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,43 +1608,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599911</v>
+        <v>599930</v>
       </c>
       <c r="R10" t="n">
-        <v>6923836</v>
+        <v>6923840</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1675,12 +1681,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,22 +1696,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124898995</v>
+        <v>124900362</v>
       </c>
       <c r="B11" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,38 +1720,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599930</v>
+        <v>599864</v>
       </c>
       <c r="R11" t="n">
-        <v>6923840</v>
+        <v>6923786</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,7 +1792,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1792,7 +1802,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1807,22 +1817,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124900786</v>
+        <v>124900055</v>
       </c>
       <c r="B12" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,43 +1841,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599791</v>
+        <v>599899</v>
       </c>
       <c r="R12" t="n">
-        <v>6923786</v>
+        <v>6923798</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,7 +1904,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1909,7 +1914,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1924,22 +1929,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124898096</v>
+        <v>124899341</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1948,25 +1953,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1976,10 +1981,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599930</v>
+        <v>599908</v>
       </c>
       <c r="R13" t="n">
-        <v>6923840</v>
+        <v>6923811</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2011,7 +2016,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2021,7 +2026,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2048,10 +2053,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124898054</v>
+        <v>124898168</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2064,34 +2069,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599930</v>
+        <v>599920</v>
       </c>
       <c r="R14" t="n">
-        <v>6923840</v>
+        <v>6923834</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2123,7 +2128,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2133,12 +2138,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2153,22 +2153,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124900330</v>
+        <v>124897942</v>
       </c>
       <c r="B15" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2181,34 +2181,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599899</v>
+        <v>599929</v>
       </c>
       <c r="R15" t="n">
-        <v>6923798</v>
+        <v>6923847</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2240,7 +2245,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2250,7 +2255,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2265,22 +2275,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124901767</v>
+        <v>124898571</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2289,42 +2299,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599748</v>
+        <v>599904</v>
       </c>
       <c r="R16" t="n">
-        <v>6923842</v>
+        <v>6923812</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2356,7 +2367,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2366,7 +2377,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2381,19 +2397,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124897942</v>
+        <v>124902350</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2426,22 +2442,41 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599929</v>
+        <v>599899</v>
       </c>
       <c r="R17" t="n">
-        <v>6923847</v>
+        <v>6923798</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2473,7 +2508,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2483,12 +2518,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Tretåig hackspett hona födosöker I en gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2503,12 +2538,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2631,10 +2666,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124898191</v>
+        <v>124900827</v>
       </c>
       <c r="B19" t="n">
-        <v>91673</v>
+        <v>57529</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2643,38 +2678,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>898</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599930</v>
+        <v>599787</v>
       </c>
       <c r="R19" t="n">
-        <v>6923840</v>
+        <v>6923799</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2706,7 +2746,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2716,7 +2756,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2731,19 +2771,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124900764</v>
+        <v>124901679</v>
       </c>
       <c r="B20" t="n">
         <v>79891</v>
@@ -2779,14 +2819,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599814</v>
+        <v>599728</v>
       </c>
       <c r="R20" t="n">
-        <v>6923824</v>
+        <v>6923812</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2818,7 +2858,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2828,7 +2868,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2843,22 +2883,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124902509</v>
+        <v>124900294</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2867,43 +2907,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599754</v>
+        <v>599864</v>
       </c>
       <c r="R21" t="n">
-        <v>6923921</v>
+        <v>6923773</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2935,7 +2979,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2945,12 +2989,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2965,22 +3004,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124901624</v>
+        <v>124900330</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2989,47 +3028,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>599703</v>
+        <v>599899</v>
       </c>
       <c r="R22" t="n">
-        <v>6923832</v>
+        <v>6923798</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3061,7 +3091,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3071,7 +3101,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3086,22 +3116,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124898571</v>
+        <v>124900465</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3114,39 +3144,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>599904</v>
+        <v>599856</v>
       </c>
       <c r="R23" t="n">
-        <v>6923812</v>
+        <v>6923803</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3178,7 +3203,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3188,12 +3213,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:05</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3208,22 +3228,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124899644</v>
+        <v>124902691</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3236,34 +3256,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>599898</v>
+        <v>599798</v>
       </c>
       <c r="R24" t="n">
-        <v>6923799</v>
+        <v>6923975</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3295,7 +3315,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3305,7 +3325,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3332,10 +3352,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124900226</v>
+        <v>124901921</v>
       </c>
       <c r="B25" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3344,43 +3364,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>599882</v>
+        <v>599742</v>
       </c>
       <c r="R25" t="n">
-        <v>6923778</v>
+        <v>6923857</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3412,7 +3436,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3422,12 +3446,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:43</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Över 20 apothecier</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3442,19 +3461,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124902015</v>
+        <v>124899195</v>
       </c>
       <c r="B26" t="n">
         <v>91012</v>
@@ -3490,14 +3509,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>599777</v>
+        <v>599930</v>
       </c>
       <c r="R26" t="n">
-        <v>6923857</v>
+        <v>6923840</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3529,7 +3548,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3539,7 +3558,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3554,22 +3573,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124900025</v>
+        <v>124900863</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3578,42 +3597,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>599878</v>
+        <v>599779</v>
       </c>
       <c r="R27" t="n">
-        <v>6923820</v>
+        <v>6923783</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3645,7 +3660,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3655,7 +3670,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3682,10 +3697,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124902350</v>
+        <v>124901634</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3694,62 +3709,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>599899</v>
+        <v>599734</v>
       </c>
       <c r="R28" t="n">
-        <v>6923798</v>
+        <v>6923810</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3781,7 +3772,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3791,12 +3782,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:17</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett hona födosöker I en gran.</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3811,22 +3797,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124899616</v>
+        <v>124900786</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3839,34 +3825,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>599899</v>
+        <v>599791</v>
       </c>
       <c r="R29" t="n">
-        <v>6923765</v>
+        <v>6923786</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3898,7 +3889,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3908,7 +3899,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3923,22 +3914,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124901679</v>
+        <v>124899616</v>
       </c>
       <c r="B30" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3951,34 +3942,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>599728</v>
+        <v>599899</v>
       </c>
       <c r="R30" t="n">
-        <v>6923812</v>
+        <v>6923765</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4010,7 +4001,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4020,7 +4011,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4035,22 +4026,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124902765</v>
+        <v>124900661</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4059,42 +4050,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>599800</v>
+        <v>599813</v>
       </c>
       <c r="R31" t="n">
-        <v>6923959</v>
+        <v>6923781</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4126,7 +4113,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4136,7 +4123,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4163,7 +4150,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124900465</v>
+        <v>124901889</v>
       </c>
       <c r="B32" t="n">
         <v>79891</v>
@@ -4203,10 +4190,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>599856</v>
+        <v>599775</v>
       </c>
       <c r="R32" t="n">
-        <v>6923803</v>
+        <v>6923855</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4238,7 +4225,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4248,7 +4235,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4275,10 +4262,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124899196</v>
+        <v>124901780</v>
       </c>
       <c r="B33" t="n">
-        <v>91457</v>
+        <v>79891</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4287,38 +4274,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>599888</v>
+        <v>599756</v>
       </c>
       <c r="R33" t="n">
-        <v>6923798</v>
+        <v>6923823</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4350,7 +4337,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4360,7 +4347,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4375,22 +4362,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124900661</v>
+        <v>124901922</v>
       </c>
       <c r="B34" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4399,38 +4386,42 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>599813</v>
+        <v>599783</v>
       </c>
       <c r="R34" t="n">
-        <v>6923781</v>
+        <v>6923858</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4462,7 +4453,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4472,7 +4463,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4499,10 +4490,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124900018</v>
+        <v>124901624</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4511,38 +4502,47 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>599883</v>
+        <v>599703</v>
       </c>
       <c r="R35" t="n">
-        <v>6923768</v>
+        <v>6923832</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4599,22 +4599,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124898316</v>
+        <v>124900025</v>
       </c>
       <c r="B36" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4623,38 +4623,42 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>599918</v>
+        <v>599878</v>
       </c>
       <c r="R36" t="n">
-        <v>6923822</v>
+        <v>6923820</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4686,7 +4690,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4696,7 +4700,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4723,10 +4727,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124901889</v>
+        <v>124899644</v>
       </c>
       <c r="B37" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4739,34 +4743,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>599775</v>
+        <v>599898</v>
       </c>
       <c r="R37" t="n">
-        <v>6923855</v>
+        <v>6923799</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4798,7 +4802,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4808,7 +4812,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4823,22 +4827,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124902839</v>
+        <v>124899839</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4851,34 +4855,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>599810</v>
+        <v>599893</v>
       </c>
       <c r="R38" t="n">
-        <v>6923980</v>
+        <v>6923773</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4910,7 +4919,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4920,7 +4929,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4935,19 +4949,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124899839</v>
+        <v>124898290</v>
       </c>
       <c r="B39" t="n">
         <v>57513</v>
@@ -4992,10 +5006,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>599893</v>
+        <v>599911</v>
       </c>
       <c r="R39" t="n">
-        <v>6923773</v>
+        <v>6923836</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5027,7 +5041,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5037,7 +5051,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5069,10 +5083,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124901780</v>
+        <v>124901767</v>
       </c>
       <c r="B40" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5081,38 +5095,42 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>599756</v>
+        <v>599748</v>
       </c>
       <c r="R40" t="n">
-        <v>6923823</v>
+        <v>6923842</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5144,7 +5162,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5154,7 +5172,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5169,22 +5187,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124900773</v>
+        <v>124898316</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5197,34 +5215,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>599801</v>
+        <v>599918</v>
       </c>
       <c r="R41" t="n">
-        <v>6923797</v>
+        <v>6923822</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5256,7 +5274,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5266,7 +5284,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5293,10 +5311,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124901921</v>
+        <v>124902839</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5305,47 +5323,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>599742</v>
+        <v>599810</v>
       </c>
       <c r="R42" t="n">
-        <v>6923857</v>
+        <v>6923980</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5377,7 +5386,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5387,7 +5396,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5402,22 +5411,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124898168</v>
+        <v>124900663</v>
       </c>
       <c r="B43" t="n">
-        <v>91299</v>
+        <v>79891</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5430,34 +5439,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>599920</v>
+        <v>599824</v>
       </c>
       <c r="R43" t="n">
-        <v>6923834</v>
+        <v>6923802</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5489,7 +5498,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5499,7 +5508,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5514,22 +5523,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124899421</v>
+        <v>124898060</v>
       </c>
       <c r="B44" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5542,37 +5551,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>599899</v>
+        <v>599916</v>
       </c>
       <c r="R44" t="n">
-        <v>6923798</v>
+        <v>6923847</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5601,7 +5610,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5611,7 +5620,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5626,22 +5635,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124900827</v>
+        <v>124898054</v>
       </c>
       <c r="B45" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5654,39 +5663,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>599787</v>
+        <v>599930</v>
       </c>
       <c r="R45" t="n">
-        <v>6923799</v>
+        <v>6923840</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5718,7 +5722,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5728,7 +5732,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5743,22 +5752,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124899341</v>
+        <v>124902765</v>
       </c>
       <c r="B46" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5767,38 +5776,42 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>599908</v>
+        <v>599800</v>
       </c>
       <c r="R46" t="n">
-        <v>6923811</v>
+        <v>6923959</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5830,7 +5843,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5840,7 +5853,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5855,22 +5868,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124900663</v>
+        <v>124900018</v>
       </c>
       <c r="B47" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5883,21 +5896,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5907,10 +5920,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>599824</v>
+        <v>599883</v>
       </c>
       <c r="R47" t="n">
-        <v>6923802</v>
+        <v>6923768</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5942,7 +5955,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5952,7 +5965,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5979,10 +5992,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124901922</v>
+        <v>124900773</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5991,42 +6004,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>599783</v>
+        <v>599801</v>
       </c>
       <c r="R48" t="n">
-        <v>6923858</v>
+        <v>6923797</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6058,7 +6067,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6068,7 +6077,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6095,10 +6104,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124900294</v>
+        <v>124899196</v>
       </c>
       <c r="B49" t="n">
-        <v>98101</v>
+        <v>91457</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6111,43 +6120,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>599864</v>
+        <v>599888</v>
       </c>
       <c r="R49" t="n">
-        <v>6923773</v>
+        <v>6923798</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6204,22 +6204,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124899503</v>
+        <v>124899564</v>
       </c>
       <c r="B50" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6232,21 +6232,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6256,10 +6256,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>599912</v>
+        <v>599910</v>
       </c>
       <c r="R50" t="n">
-        <v>6923800</v>
+        <v>6923786</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6328,10 +6328,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124900313</v>
+        <v>124902015</v>
       </c>
       <c r="B51" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6344,34 +6344,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>599854</v>
+        <v>599777</v>
       </c>
       <c r="R51" t="n">
-        <v>6923776</v>
+        <v>6923857</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6403,7 +6403,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124898191</v>
+        <v>124902691</v>
       </c>
       <c r="B2" t="n">
-        <v>91673</v>
+        <v>91030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>898</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599930</v>
+        <v>599798</v>
       </c>
       <c r="R2" t="n">
-        <v>6923840</v>
+        <v>6923975</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124900313</v>
+        <v>124899839</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599854</v>
+        <v>599893</v>
       </c>
       <c r="R3" t="n">
-        <v>6923776</v>
+        <v>6923773</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,19 +897,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124900764</v>
+        <v>124900313</v>
       </c>
       <c r="B4" t="n">
         <v>79891</v>
@@ -935,14 +945,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599814</v>
+        <v>599854</v>
       </c>
       <c r="R4" t="n">
-        <v>6923824</v>
+        <v>6923776</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,22 +1009,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124901880</v>
+        <v>124899616</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1037,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599771</v>
+        <v>599899</v>
       </c>
       <c r="R5" t="n">
-        <v>6923841</v>
+        <v>6923765</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,12 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:58</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på asp</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,22 +1121,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124902509</v>
+        <v>124900362</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,43 +1145,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599754</v>
+        <v>599864</v>
       </c>
       <c r="R6" t="n">
-        <v>6923921</v>
+        <v>6923786</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,12 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,22 +1242,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124900226</v>
+        <v>124898995</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>96979</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,43 +1266,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599882</v>
+        <v>599930</v>
       </c>
       <c r="R7" t="n">
-        <v>6923778</v>
+        <v>6923840</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,12 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:43</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Över 20 apothecier</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,10 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124899503</v>
+        <v>124900661</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,34 +1382,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599912</v>
+        <v>599813</v>
       </c>
       <c r="R8" t="n">
-        <v>6923800</v>
+        <v>6923781</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,22 +1466,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124899421</v>
+        <v>124900330</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,21 +1494,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1559,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,7 +1563,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1596,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124898995</v>
+        <v>124901767</v>
       </c>
       <c r="B10" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,38 +1602,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599930</v>
+        <v>599748</v>
       </c>
       <c r="R10" t="n">
-        <v>6923840</v>
+        <v>6923842</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,22 +1694,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124900362</v>
+        <v>124901679</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1720,47 +1718,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599864</v>
+        <v>599728</v>
       </c>
       <c r="R11" t="n">
-        <v>6923786</v>
+        <v>6923812</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,7 +1781,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1802,7 +1791,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1817,19 +1806,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124900055</v>
+        <v>124901921</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1862,17 +1851,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599899</v>
+        <v>599742</v>
       </c>
       <c r="R12" t="n">
-        <v>6923798</v>
+        <v>6923857</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1904,7 +1902,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1914,7 +1912,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1929,22 +1927,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124899341</v>
+        <v>124901780</v>
       </c>
       <c r="B13" t="n">
-        <v>90977</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1953,25 +1951,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1981,10 +1979,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599908</v>
+        <v>599756</v>
       </c>
       <c r="R13" t="n">
-        <v>6923811</v>
+        <v>6923823</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2016,7 +2014,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2026,7 +2024,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2053,10 +2051,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124898168</v>
+        <v>124901624</v>
       </c>
       <c r="B14" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2065,38 +2063,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599920</v>
+        <v>599703</v>
       </c>
       <c r="R14" t="n">
-        <v>6923834</v>
+        <v>6923832</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2128,7 +2135,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2138,7 +2145,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2153,22 +2160,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124897942</v>
+        <v>124900055</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2177,43 +2184,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599929</v>
+        <v>599899</v>
       </c>
       <c r="R15" t="n">
-        <v>6923847</v>
+        <v>6923798</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2245,7 +2247,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2255,12 +2257,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2275,12 +2272,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2409,10 +2406,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124902350</v>
+        <v>124899195</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2425,58 +2422,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599899</v>
+        <v>599930</v>
       </c>
       <c r="R17" t="n">
-        <v>6923798</v>
+        <v>6923840</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2508,7 +2481,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2518,12 +2491,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:17</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett hona födosöker I en gran.</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2538,22 +2506,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124899798</v>
+        <v>124900786</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2562,42 +2530,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599883</v>
+        <v>599791</v>
       </c>
       <c r="R18" t="n">
-        <v>6923782</v>
+        <v>6923786</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2629,7 +2598,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2639,7 +2608,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2654,22 +2623,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124900827</v>
+        <v>124900226</v>
       </c>
       <c r="B19" t="n">
-        <v>57529</v>
+        <v>79891</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2682,39 +2651,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599787</v>
+        <v>599882</v>
       </c>
       <c r="R19" t="n">
-        <v>6923799</v>
+        <v>6923778</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2746,7 +2715,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2756,7 +2725,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Över 20 apothecier</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2771,22 +2745,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124901679</v>
+        <v>124899341</v>
       </c>
       <c r="B20" t="n">
-        <v>79891</v>
+        <v>90977</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2795,38 +2769,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599728</v>
+        <v>599908</v>
       </c>
       <c r="R20" t="n">
-        <v>6923812</v>
+        <v>6923811</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2858,7 +2832,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2868,7 +2842,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2883,22 +2857,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124900294</v>
+        <v>124898316</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2907,47 +2881,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599864</v>
+        <v>599918</v>
       </c>
       <c r="R21" t="n">
-        <v>6923773</v>
+        <v>6923822</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2979,7 +2944,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2989,7 +2954,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3004,22 +2969,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124900330</v>
+        <v>124901634</v>
       </c>
       <c r="B22" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3028,25 +2993,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3056,10 +3021,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>599899</v>
+        <v>599734</v>
       </c>
       <c r="R22" t="n">
-        <v>6923798</v>
+        <v>6923810</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3091,7 +3056,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3101,7 +3066,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3116,22 +3081,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124900465</v>
+        <v>124898191</v>
       </c>
       <c r="B23" t="n">
-        <v>79891</v>
+        <v>91673</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3140,25 +3105,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>898</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3168,10 +3133,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>599856</v>
+        <v>599930</v>
       </c>
       <c r="R23" t="n">
-        <v>6923803</v>
+        <v>6923840</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3203,7 +3168,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3213,7 +3178,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3240,10 +3205,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124902691</v>
+        <v>124900663</v>
       </c>
       <c r="B24" t="n">
-        <v>91030</v>
+        <v>79891</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3256,34 +3221,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>599798</v>
+        <v>599824</v>
       </c>
       <c r="R24" t="n">
-        <v>6923975</v>
+        <v>6923802</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3315,7 +3280,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3325,7 +3290,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3340,22 +3305,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124901921</v>
+        <v>124900827</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3364,35 +3329,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3401,10 +3362,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>599742</v>
+        <v>599787</v>
       </c>
       <c r="R25" t="n">
-        <v>6923857</v>
+        <v>6923799</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3436,7 +3397,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3446,7 +3407,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3461,22 +3422,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124899195</v>
+        <v>124897942</v>
       </c>
       <c r="B26" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3489,34 +3450,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>599930</v>
+        <v>599929</v>
       </c>
       <c r="R26" t="n">
-        <v>6923840</v>
+        <v>6923847</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3548,7 +3514,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3558,7 +3524,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3573,22 +3544,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124900863</v>
+        <v>124900294</v>
       </c>
       <c r="B27" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3597,38 +3568,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>599779</v>
+        <v>599864</v>
       </c>
       <c r="R27" t="n">
-        <v>6923783</v>
+        <v>6923773</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3660,7 +3640,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3670,7 +3650,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3685,22 +3665,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124901634</v>
+        <v>124899503</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3709,25 +3689,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3737,10 +3717,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>599734</v>
+        <v>599912</v>
       </c>
       <c r="R28" t="n">
-        <v>6923810</v>
+        <v>6923800</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3772,7 +3752,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3782,7 +3762,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3809,10 +3789,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124900786</v>
+        <v>124899421</v>
       </c>
       <c r="B29" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3825,39 +3805,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>599791</v>
+        <v>599899</v>
       </c>
       <c r="R29" t="n">
-        <v>6923786</v>
+        <v>6923798</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3889,7 +3864,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3899,7 +3874,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3914,22 +3889,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124899616</v>
+        <v>124900764</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3942,21 +3917,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3966,10 +3941,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>599899</v>
+        <v>599814</v>
       </c>
       <c r="R30" t="n">
-        <v>6923765</v>
+        <v>6923824</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4001,7 +3976,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4011,7 +3986,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4038,10 +4013,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124900661</v>
+        <v>124898168</v>
       </c>
       <c r="B31" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4054,34 +4029,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>599813</v>
+        <v>599920</v>
       </c>
       <c r="R31" t="n">
-        <v>6923781</v>
+        <v>6923834</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4113,7 +4088,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4123,7 +4098,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4150,10 +4125,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124901889</v>
+        <v>124902015</v>
       </c>
       <c r="B32" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4166,34 +4141,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>599775</v>
+        <v>599777</v>
       </c>
       <c r="R32" t="n">
-        <v>6923855</v>
+        <v>6923857</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4225,7 +4200,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4235,7 +4210,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4250,19 +4225,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124901780</v>
+        <v>124900465</v>
       </c>
       <c r="B33" t="n">
         <v>79891</v>
@@ -4302,10 +4277,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>599756</v>
+        <v>599856</v>
       </c>
       <c r="R33" t="n">
-        <v>6923823</v>
+        <v>6923803</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4337,7 +4312,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4347,7 +4322,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4374,10 +4349,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124901922</v>
+        <v>124900773</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4386,42 +4361,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>599783</v>
+        <v>599801</v>
       </c>
       <c r="R34" t="n">
-        <v>6923858</v>
+        <v>6923797</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4453,7 +4424,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4463,7 +4434,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4490,10 +4461,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124901624</v>
+        <v>124902509</v>
       </c>
       <c r="B35" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4502,35 +4473,31 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4539,10 +4506,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>599703</v>
+        <v>599754</v>
       </c>
       <c r="R35" t="n">
-        <v>6923832</v>
+        <v>6923921</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4574,7 +4541,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4584,7 +4551,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:29</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4599,22 +4571,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124900025</v>
+        <v>124902350</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4623,42 +4595,62 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>599878</v>
+        <v>599899</v>
       </c>
       <c r="R36" t="n">
-        <v>6923820</v>
+        <v>6923798</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4690,7 +4682,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4700,7 +4692,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett hona födosöker I en gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4715,22 +4712,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124899644</v>
+        <v>124899798</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4739,38 +4736,42 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>599898</v>
+        <v>599883</v>
       </c>
       <c r="R37" t="n">
-        <v>6923799</v>
+        <v>6923782</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4802,7 +4803,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4812,7 +4813,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4839,10 +4840,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124899839</v>
+        <v>124901880</v>
       </c>
       <c r="B38" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4855,39 +4856,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>599893</v>
+        <v>599771</v>
       </c>
       <c r="R38" t="n">
-        <v>6923773</v>
+        <v>6923841</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4919,7 +4915,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4929,12 +4925,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Rikligt med lunglav på asp</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4949,22 +4945,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124898290</v>
+        <v>124898060</v>
       </c>
       <c r="B39" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4977,42 +4973,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>599911</v>
+        <v>599916</v>
       </c>
       <c r="R39" t="n">
-        <v>6923836</v>
+        <v>6923847</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5041,7 +5032,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5051,12 +5042,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5071,22 +5057,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124901767</v>
+        <v>124899644</v>
       </c>
       <c r="B40" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5095,42 +5081,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>599748</v>
+        <v>599898</v>
       </c>
       <c r="R40" t="n">
-        <v>6923842</v>
+        <v>6923799</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5162,7 +5144,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5172,7 +5154,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5199,10 +5181,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124898316</v>
+        <v>124902839</v>
       </c>
       <c r="B41" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5215,34 +5197,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>599918</v>
+        <v>599810</v>
       </c>
       <c r="R41" t="n">
-        <v>6923822</v>
+        <v>6923980</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5274,7 +5256,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5284,7 +5266,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5311,7 +5293,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124902839</v>
+        <v>124898054</v>
       </c>
       <c r="B42" t="n">
         <v>78810</v>
@@ -5347,14 +5329,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>599810</v>
+        <v>599930</v>
       </c>
       <c r="R42" t="n">
-        <v>6923980</v>
+        <v>6923840</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5386,7 +5368,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5396,7 +5378,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5411,22 +5398,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124900663</v>
+        <v>124900025</v>
       </c>
       <c r="B43" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5435,38 +5422,42 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>599824</v>
+        <v>599878</v>
       </c>
       <c r="R43" t="n">
-        <v>6923802</v>
+        <v>6923820</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5498,7 +5489,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5508,7 +5499,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5523,22 +5514,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124898060</v>
+        <v>124901889</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5551,37 +5542,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>599916</v>
+        <v>599775</v>
       </c>
       <c r="R44" t="n">
-        <v>6923847</v>
+        <v>6923855</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5610,7 +5601,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5620,7 +5611,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5635,22 +5626,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124898054</v>
+        <v>124901922</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5659,38 +5650,42 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>599930</v>
+        <v>599783</v>
       </c>
       <c r="R45" t="n">
-        <v>6923840</v>
+        <v>6923858</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5722,7 +5717,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5732,12 +5727,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5752,22 +5742,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124902765</v>
+        <v>124899196</v>
       </c>
       <c r="B46" t="n">
-        <v>98101</v>
+        <v>91457</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5780,38 +5770,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>599800</v>
+        <v>599888</v>
       </c>
       <c r="R46" t="n">
-        <v>6923959</v>
+        <v>6923798</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5843,7 +5829,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5853,7 +5839,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5880,10 +5866,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124900018</v>
+        <v>124900863</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5896,34 +5882,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>599883</v>
+        <v>599779</v>
       </c>
       <c r="R47" t="n">
-        <v>6923768</v>
+        <v>6923783</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5955,7 +5941,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5965,7 +5951,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5980,22 +5966,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124900773</v>
+        <v>124899564</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6008,34 +5994,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>599801</v>
+        <v>599910</v>
       </c>
       <c r="R48" t="n">
-        <v>6923797</v>
+        <v>6923786</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6067,7 +6053,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6077,7 +6063,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6092,22 +6078,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124899196</v>
+        <v>124900018</v>
       </c>
       <c r="B49" t="n">
-        <v>91457</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6116,38 +6102,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>599888</v>
+        <v>599883</v>
       </c>
       <c r="R49" t="n">
-        <v>6923798</v>
+        <v>6923768</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6179,7 +6165,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6189,7 +6175,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6204,22 +6190,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124899564</v>
+        <v>124898290</v>
       </c>
       <c r="B50" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6232,34 +6218,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>599910</v>
+        <v>599911</v>
       </c>
       <c r="R50" t="n">
-        <v>6923786</v>
+        <v>6923836</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6291,7 +6282,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6301,7 +6292,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6316,22 +6312,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124902015</v>
+        <v>124902765</v>
       </c>
       <c r="B51" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6340,38 +6336,42 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>599777</v>
+        <v>599800</v>
       </c>
       <c r="R51" t="n">
-        <v>6923857</v>
+        <v>6923959</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6403,7 +6403,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -2284,10 +2284,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124898571</v>
+        <v>124899195</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2300,39 +2300,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599904</v>
+        <v>599930</v>
       </c>
       <c r="R16" t="n">
-        <v>6923812</v>
+        <v>6923840</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2364,7 +2359,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2374,12 +2369,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:05</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2394,22 +2384,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124899195</v>
+        <v>124898571</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2422,34 +2412,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599930</v>
+        <v>599904</v>
       </c>
       <c r="R17" t="n">
-        <v>6923840</v>
+        <v>6923812</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2481,7 +2476,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2491,7 +2486,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2506,22 +2506,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124900786</v>
+        <v>124900226</v>
       </c>
       <c r="B18" t="n">
-        <v>57529</v>
+        <v>79891</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2534,39 +2534,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599791</v>
+        <v>599882</v>
       </c>
       <c r="R18" t="n">
-        <v>6923786</v>
+        <v>6923778</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2608,7 +2608,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Över 20 apothecier</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2623,22 +2628,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124900226</v>
+        <v>124900786</v>
       </c>
       <c r="B19" t="n">
-        <v>79891</v>
+        <v>57529</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2651,39 +2656,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599882</v>
+        <v>599791</v>
       </c>
       <c r="R19" t="n">
-        <v>6923778</v>
+        <v>6923786</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2715,7 +2720,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2725,12 +2730,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:43</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Över 20 apothecier</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2745,22 +2745,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124899341</v>
+        <v>124898316</v>
       </c>
       <c r="B20" t="n">
-        <v>90977</v>
+        <v>91299</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2769,38 +2769,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599908</v>
+        <v>599918</v>
       </c>
       <c r="R20" t="n">
-        <v>6923811</v>
+        <v>6923822</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2857,22 +2857,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124898316</v>
+        <v>124899341</v>
       </c>
       <c r="B21" t="n">
-        <v>91299</v>
+        <v>90977</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2881,38 +2881,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599918</v>
+        <v>599908</v>
       </c>
       <c r="R21" t="n">
-        <v>6923822</v>
+        <v>6923811</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2969,12 +2969,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3317,10 +3317,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124900827</v>
+        <v>124897942</v>
       </c>
       <c r="B25" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3333,16 +3333,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3353,19 +3353,19 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>599787</v>
+        <v>599929</v>
       </c>
       <c r="R25" t="n">
-        <v>6923799</v>
+        <v>6923847</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3407,7 +3407,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3422,22 +3427,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124897942</v>
+        <v>124900827</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3450,16 +3455,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3470,19 +3475,19 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>599929</v>
+        <v>599787</v>
       </c>
       <c r="R26" t="n">
-        <v>6923847</v>
+        <v>6923799</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3514,7 +3519,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3524,12 +3529,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3544,22 +3544,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124900294</v>
+        <v>124899503</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3568,47 +3568,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>599864</v>
+        <v>599912</v>
       </c>
       <c r="R27" t="n">
-        <v>6923773</v>
+        <v>6923800</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3640,7 +3631,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3650,7 +3641,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3665,19 +3656,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124899503</v>
+        <v>124899421</v>
       </c>
       <c r="B28" t="n">
         <v>91012</v>
@@ -3717,10 +3708,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>599912</v>
+        <v>599899</v>
       </c>
       <c r="R28" t="n">
-        <v>6923800</v>
+        <v>6923798</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3752,7 +3743,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3762,7 +3753,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3777,22 +3768,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124899421</v>
+        <v>124900764</v>
       </c>
       <c r="B29" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3805,21 +3796,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3829,10 +3820,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>599899</v>
+        <v>599814</v>
       </c>
       <c r="R29" t="n">
-        <v>6923798</v>
+        <v>6923824</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3864,7 +3855,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3874,7 +3865,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3889,22 +3880,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124900764</v>
+        <v>124900294</v>
       </c>
       <c r="B30" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3913,38 +3904,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>599814</v>
+        <v>599864</v>
       </c>
       <c r="R30" t="n">
-        <v>6923824</v>
+        <v>6923773</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3976,7 +3976,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4001,12 +4001,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124902691</v>
+        <v>124898054</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599798</v>
+        <v>599930</v>
       </c>
       <c r="R2" t="n">
-        <v>6923975</v>
+        <v>6923840</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124899839</v>
+        <v>124899503</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599893</v>
+        <v>599912</v>
       </c>
       <c r="R3" t="n">
-        <v>6923773</v>
+        <v>6923800</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:35</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +892,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124900313</v>
+        <v>124898096</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,34 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599854</v>
+        <v>599930</v>
       </c>
       <c r="R4" t="n">
-        <v>6923776</v>
+        <v>6923840</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,22 +1004,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124899616</v>
+        <v>124897942</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,34 +1032,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599899</v>
+        <v>599929</v>
       </c>
       <c r="R5" t="n">
-        <v>6923765</v>
+        <v>6923847</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,19 +1126,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124900362</v>
+        <v>124901584</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1166,26 +1171,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599864</v>
+        <v>599899</v>
       </c>
       <c r="R6" t="n">
-        <v>6923786</v>
+        <v>6923798</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,22 +1238,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124898995</v>
+        <v>124898060</v>
       </c>
       <c r="B7" t="n">
-        <v>96979</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,41 +1262,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599930</v>
+        <v>599916</v>
       </c>
       <c r="R7" t="n">
-        <v>6923840</v>
+        <v>6923847</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1329,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,22 +1350,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124900661</v>
+        <v>124902839</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,21 +1378,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1406,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599813</v>
+        <v>599810</v>
       </c>
       <c r="R8" t="n">
-        <v>6923781</v>
+        <v>6923980</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124900330</v>
+        <v>124899644</v>
       </c>
       <c r="B9" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,34 +1490,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599899</v>
+        <v>599898</v>
       </c>
       <c r="R9" t="n">
-        <v>6923798</v>
+        <v>6923799</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,7 +1559,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,22 +1574,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124901767</v>
+        <v>124900018</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,42 +1598,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599748</v>
+        <v>599883</v>
       </c>
       <c r="R10" t="n">
-        <v>6923842</v>
+        <v>6923768</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1671,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1694,22 +1686,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124901679</v>
+        <v>124902015</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,21 +1714,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1746,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599728</v>
+        <v>599777</v>
       </c>
       <c r="R11" t="n">
-        <v>6923812</v>
+        <v>6923857</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1781,7 +1773,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1791,7 +1783,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124901921</v>
+        <v>124902350</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1830,47 +1822,62 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599742</v>
+        <v>599899</v>
       </c>
       <c r="R12" t="n">
-        <v>6923857</v>
+        <v>6923798</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,7 +1909,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1912,7 +1919,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett hona födosöker I en gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,22 +1939,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124901780</v>
+        <v>124900025</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1951,38 +1963,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599756</v>
+        <v>599878</v>
       </c>
       <c r="R13" t="n">
-        <v>6923823</v>
+        <v>6923820</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2014,7 +2030,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2024,7 +2040,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2039,22 +2055,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124901624</v>
+        <v>124900764</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2063,47 +2079,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599703</v>
+        <v>599814</v>
       </c>
       <c r="R14" t="n">
-        <v>6923832</v>
+        <v>6923824</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2135,7 +2142,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2145,7 +2152,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2160,22 +2167,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124900055</v>
+        <v>124899421</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2184,25 +2191,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2247,7 +2254,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2257,7 +2264,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2284,10 +2291,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124899195</v>
+        <v>124901634</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2296,25 +2303,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2324,10 +2331,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599930</v>
+        <v>599734</v>
       </c>
       <c r="R16" t="n">
-        <v>6923840</v>
+        <v>6923810</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2359,7 +2366,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2369,7 +2376,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2396,10 +2403,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124898571</v>
+        <v>124900863</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2412,39 +2419,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599904</v>
+        <v>599779</v>
       </c>
       <c r="R17" t="n">
-        <v>6923812</v>
+        <v>6923783</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2476,7 +2478,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2486,12 +2488,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:05</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2506,19 +2503,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124900226</v>
+        <v>124901880</v>
       </c>
       <c r="B18" t="n">
         <v>79891</v>
@@ -2552,21 +2549,16 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599882</v>
+        <v>599771</v>
       </c>
       <c r="R18" t="n">
-        <v>6923778</v>
+        <v>6923841</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2598,7 +2590,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2608,12 +2600,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Över 20 apothecier</t>
+          <t>Rikligt med lunglav på asp</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2628,22 +2620,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124900786</v>
+        <v>124900663</v>
       </c>
       <c r="B19" t="n">
-        <v>57529</v>
+        <v>79891</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2656,39 +2648,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599791</v>
+        <v>599824</v>
       </c>
       <c r="R19" t="n">
-        <v>6923786</v>
+        <v>6923802</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2720,7 +2707,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2730,7 +2717,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2745,19 +2732,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124898316</v>
+        <v>124899564</v>
       </c>
       <c r="B20" t="n">
         <v>91299</v>
@@ -2793,14 +2780,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599918</v>
+        <v>599910</v>
       </c>
       <c r="R20" t="n">
-        <v>6923822</v>
+        <v>6923786</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2832,7 +2819,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2842,7 +2829,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2857,22 +2844,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124899341</v>
+        <v>124898168</v>
       </c>
       <c r="B21" t="n">
-        <v>90977</v>
+        <v>91299</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2881,38 +2868,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599908</v>
+        <v>599920</v>
       </c>
       <c r="R21" t="n">
-        <v>6923811</v>
+        <v>6923834</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2944,7 +2931,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2954,7 +2941,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2969,22 +2956,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124901634</v>
+        <v>124899839</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2993,38 +2980,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>599734</v>
+        <v>599893</v>
       </c>
       <c r="R22" t="n">
-        <v>6923810</v>
+        <v>6923773</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3056,7 +3048,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3066,7 +3058,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3081,22 +3078,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124898191</v>
+        <v>124898290</v>
       </c>
       <c r="B23" t="n">
-        <v>91673</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3105,38 +3102,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>599930</v>
+        <v>599911</v>
       </c>
       <c r="R23" t="n">
-        <v>6923840</v>
+        <v>6923836</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3168,7 +3170,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3178,7 +3180,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3193,19 +3200,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124900663</v>
+        <v>124900226</v>
       </c>
       <c r="B24" t="n">
         <v>79891</v>
@@ -3239,16 +3246,21 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>599824</v>
+        <v>599882</v>
       </c>
       <c r="R24" t="n">
-        <v>6923802</v>
+        <v>6923778</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3280,7 +3292,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3290,7 +3302,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Över 20 apothecier</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3317,10 +3334,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124897942</v>
+        <v>124900773</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3333,39 +3350,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>599929</v>
+        <v>599801</v>
       </c>
       <c r="R25" t="n">
-        <v>6923847</v>
+        <v>6923797</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3397,7 +3409,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3407,12 +3419,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3427,22 +3434,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124900827</v>
+        <v>124900330</v>
       </c>
       <c r="B26" t="n">
-        <v>57529</v>
+        <v>91299</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3455,39 +3462,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>599787</v>
+        <v>599899</v>
       </c>
       <c r="R26" t="n">
-        <v>6923799</v>
+        <v>6923798</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3519,7 +3521,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3529,7 +3531,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3544,22 +3546,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124899503</v>
+        <v>124901922</v>
       </c>
       <c r="B27" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3568,38 +3570,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>599912</v>
+        <v>599783</v>
       </c>
       <c r="R27" t="n">
-        <v>6923800</v>
+        <v>6923858</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3631,7 +3637,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3641,7 +3647,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3656,22 +3662,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124899421</v>
+        <v>124898995</v>
       </c>
       <c r="B28" t="n">
-        <v>91012</v>
+        <v>96979</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3680,25 +3686,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3708,10 +3714,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>599899</v>
+        <v>599930</v>
       </c>
       <c r="R28" t="n">
-        <v>6923798</v>
+        <v>6923840</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3743,7 +3749,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3753,7 +3759,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3768,22 +3774,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124900764</v>
+        <v>124899341</v>
       </c>
       <c r="B29" t="n">
-        <v>79891</v>
+        <v>90977</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3792,25 +3798,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3820,10 +3826,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>599814</v>
+        <v>599908</v>
       </c>
       <c r="R29" t="n">
-        <v>6923824</v>
+        <v>6923811</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3855,7 +3861,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3865,7 +3871,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3892,10 +3898,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124900294</v>
+        <v>124900786</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3904,47 +3910,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>599864</v>
+        <v>599791</v>
       </c>
       <c r="R30" t="n">
-        <v>6923773</v>
+        <v>6923786</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3976,7 +3978,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3986,7 +3988,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4013,10 +4015,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124898168</v>
+        <v>124901767</v>
       </c>
       <c r="B31" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4025,38 +4027,42 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>599920</v>
+        <v>599748</v>
       </c>
       <c r="R31" t="n">
-        <v>6923834</v>
+        <v>6923842</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4088,7 +4094,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4098,7 +4104,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4125,10 +4131,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124902015</v>
+        <v>124900294</v>
       </c>
       <c r="B32" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4137,38 +4143,47 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>599777</v>
+        <v>599864</v>
       </c>
       <c r="R32" t="n">
-        <v>6923857</v>
+        <v>6923773</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4200,7 +4215,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4210,7 +4225,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4225,22 +4240,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124900465</v>
+        <v>124899798</v>
       </c>
       <c r="B33" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4249,38 +4264,42 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>599856</v>
+        <v>599883</v>
       </c>
       <c r="R33" t="n">
-        <v>6923803</v>
+        <v>6923782</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4312,7 +4331,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4322,7 +4341,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4337,22 +4356,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124900773</v>
+        <v>124900313</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4365,34 +4384,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>599801</v>
+        <v>599854</v>
       </c>
       <c r="R34" t="n">
-        <v>6923797</v>
+        <v>6923776</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4424,7 +4443,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4434,7 +4453,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4461,10 +4480,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124902509</v>
+        <v>124901624</v>
       </c>
       <c r="B35" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4473,31 +4492,35 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4506,10 +4529,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>599754</v>
+        <v>599703</v>
       </c>
       <c r="R35" t="n">
-        <v>6923921</v>
+        <v>6923832</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4541,7 +4564,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4551,12 +4574,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>18:29</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4571,22 +4589,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124902350</v>
+        <v>124899196</v>
       </c>
       <c r="B36" t="n">
-        <v>57513</v>
+        <v>91457</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4595,59 +4613,35 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>599899</v>
+        <v>599888</v>
       </c>
       <c r="R36" t="n">
         <v>6923798</v>
@@ -4682,7 +4676,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4692,12 +4686,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>18:17</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett hona födosöker I en gran.</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4712,22 +4701,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124899798</v>
+        <v>124901679</v>
       </c>
       <c r="B37" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4736,42 +4725,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>599883</v>
+        <v>599728</v>
       </c>
       <c r="R37" t="n">
-        <v>6923782</v>
+        <v>6923812</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4803,7 +4788,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4813,7 +4798,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4840,10 +4825,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124901880</v>
+        <v>124899616</v>
       </c>
       <c r="B38" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4856,34 +4841,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>599771</v>
+        <v>599899</v>
       </c>
       <c r="R38" t="n">
-        <v>6923841</v>
+        <v>6923765</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4915,7 +4900,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4925,12 +4910,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:58</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på asp</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4945,22 +4925,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124898060</v>
+        <v>124898571</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4973,37 +4953,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>599916</v>
+        <v>599904</v>
       </c>
       <c r="R39" t="n">
-        <v>6923847</v>
+        <v>6923812</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5032,7 +5017,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5042,7 +5027,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5057,22 +5047,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124899644</v>
+        <v>124900465</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5085,34 +5075,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>599898</v>
+        <v>599856</v>
       </c>
       <c r="R40" t="n">
-        <v>6923799</v>
+        <v>6923803</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5144,7 +5134,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5154,7 +5144,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5169,22 +5159,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124902839</v>
+        <v>124902509</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5197,34 +5187,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>599810</v>
+        <v>599754</v>
       </c>
       <c r="R41" t="n">
-        <v>6923980</v>
+        <v>6923921</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5256,7 +5251,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5266,7 +5261,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:29</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5293,10 +5293,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124898054</v>
+        <v>124902765</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5305,38 +5305,42 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>599930</v>
+        <v>599800</v>
       </c>
       <c r="R42" t="n">
-        <v>6923840</v>
+        <v>6923959</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5368,7 +5372,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5378,12 +5382,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5398,22 +5397,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124900025</v>
+        <v>124900827</v>
       </c>
       <c r="B43" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5422,42 +5421,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>12</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>599878</v>
+        <v>599787</v>
       </c>
       <c r="R43" t="n">
-        <v>6923820</v>
+        <v>6923799</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5489,7 +5489,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5526,7 +5526,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124901889</v>
+        <v>124900661</v>
       </c>
       <c r="B44" t="n">
         <v>79891</v>
@@ -5562,14 +5562,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>599775</v>
+        <v>599813</v>
       </c>
       <c r="R44" t="n">
-        <v>6923855</v>
+        <v>6923781</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5601,7 +5601,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5626,22 +5626,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124901922</v>
+        <v>124898191</v>
       </c>
       <c r="B45" t="n">
-        <v>98101</v>
+        <v>91673</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5654,38 +5654,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>898</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>599783</v>
+        <v>599930</v>
       </c>
       <c r="R45" t="n">
-        <v>6923858</v>
+        <v>6923840</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5717,7 +5713,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5727,7 +5723,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5742,22 +5738,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124899196</v>
+        <v>124901780</v>
       </c>
       <c r="B46" t="n">
-        <v>91457</v>
+        <v>79891</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5766,38 +5762,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>599888</v>
+        <v>599756</v>
       </c>
       <c r="R46" t="n">
-        <v>6923798</v>
+        <v>6923823</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5829,7 +5825,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5839,7 +5835,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5854,22 +5850,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124900863</v>
+        <v>124900362</v>
       </c>
       <c r="B47" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5878,38 +5874,47 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>599779</v>
+        <v>599864</v>
       </c>
       <c r="R47" t="n">
-        <v>6923783</v>
+        <v>6923786</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5941,7 +5946,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5951,7 +5956,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5966,22 +5971,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124899564</v>
+        <v>124901889</v>
       </c>
       <c r="B48" t="n">
-        <v>91299</v>
+        <v>79891</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5994,21 +5999,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6018,10 +6023,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>599910</v>
+        <v>599775</v>
       </c>
       <c r="R48" t="n">
-        <v>6923786</v>
+        <v>6923855</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6053,7 +6058,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6063,7 +6068,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6090,10 +6095,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124900018</v>
+        <v>124902691</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6106,34 +6111,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>599883</v>
+        <v>599798</v>
       </c>
       <c r="R49" t="n">
-        <v>6923768</v>
+        <v>6923975</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6165,7 +6170,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6175,7 +6180,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6190,22 +6195,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124898290</v>
+        <v>124898316</v>
       </c>
       <c r="B50" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6218,39 +6223,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>599911</v>
+        <v>599918</v>
       </c>
       <c r="R50" t="n">
-        <v>6923836</v>
+        <v>6923822</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6292,12 +6292,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6312,19 +6307,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124902765</v>
+        <v>124901921</v>
       </c>
       <c r="B51" t="n">
         <v>98101</v>
@@ -6362,16 +6357,21 @@
           <t>10</t>
         </is>
       </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>599800</v>
+        <v>599742</v>
       </c>
       <c r="R51" t="n">
-        <v>6923959</v>
+        <v>6923857</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6403,7 +6403,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6428,12 +6428,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -4252,10 +4252,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124899798</v>
+        <v>124900313</v>
       </c>
       <c r="B33" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4264,42 +4264,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>599883</v>
+        <v>599854</v>
       </c>
       <c r="R33" t="n">
-        <v>6923782</v>
+        <v>6923776</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4331,7 +4327,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4341,7 +4337,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4368,10 +4364,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124900313</v>
+        <v>124899798</v>
       </c>
       <c r="B34" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4380,38 +4376,42 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>599854</v>
+        <v>599883</v>
       </c>
       <c r="R34" t="n">
-        <v>6923776</v>
+        <v>6923782</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5983,10 +5983,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124901889</v>
+        <v>124898316</v>
       </c>
       <c r="B48" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5999,34 +5999,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>599775</v>
+        <v>599918</v>
       </c>
       <c r="R48" t="n">
-        <v>6923855</v>
+        <v>6923822</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6083,22 +6083,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124902691</v>
+        <v>124901889</v>
       </c>
       <c r="B49" t="n">
-        <v>91030</v>
+        <v>79891</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6111,34 +6111,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>599798</v>
+        <v>599775</v>
       </c>
       <c r="R49" t="n">
-        <v>6923975</v>
+        <v>6923855</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6195,22 +6195,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124898316</v>
+        <v>124902691</v>
       </c>
       <c r="B50" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6223,34 +6223,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>599918</v>
+        <v>599798</v>
       </c>
       <c r="R50" t="n">
-        <v>6923822</v>
+        <v>6923975</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124898054</v>
+        <v>124902839</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599930</v>
+        <v>599810</v>
       </c>
       <c r="R2" t="n">
-        <v>6923840</v>
+        <v>6923980</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124899503</v>
+        <v>124899341</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599912</v>
+        <v>599908</v>
       </c>
       <c r="R3" t="n">
-        <v>6923800</v>
+        <v>6923811</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124898096</v>
+        <v>124899839</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599930</v>
+        <v>599893</v>
       </c>
       <c r="R4" t="n">
-        <v>6923840</v>
+        <v>6923773</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,22 +1009,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124897942</v>
+        <v>124900330</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,39 +1037,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599929</v>
+        <v>599899</v>
       </c>
       <c r="R5" t="n">
-        <v>6923847</v>
+        <v>6923798</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,12 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,22 +1121,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124901584</v>
+        <v>124898060</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,41 +1145,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599899</v>
+        <v>599916</v>
       </c>
       <c r="R6" t="n">
-        <v>6923798</v>
+        <v>6923847</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1213,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,22 +1233,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124898060</v>
+        <v>124900573</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,41 +1257,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599916</v>
+        <v>599899</v>
       </c>
       <c r="R7" t="n">
-        <v>6923847</v>
+        <v>6923798</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1325,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,22 +1349,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124902839</v>
+        <v>124898316</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,34 +1377,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599810</v>
+        <v>599918</v>
       </c>
       <c r="R8" t="n">
-        <v>6923980</v>
+        <v>6923822</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124899644</v>
+        <v>124899195</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,34 +1489,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599898</v>
+        <v>599930</v>
       </c>
       <c r="R9" t="n">
-        <v>6923799</v>
+        <v>6923840</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1549,7 +1548,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1558,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,22 +1573,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124900018</v>
+        <v>124900465</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,21 +1601,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1626,10 +1625,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599883</v>
+        <v>599856</v>
       </c>
       <c r="R10" t="n">
-        <v>6923768</v>
+        <v>6923803</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1661,7 +1660,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,7 +1670,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,10 +1697,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124902015</v>
+        <v>124900786</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,34 +1713,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599777</v>
+        <v>599791</v>
       </c>
       <c r="R11" t="n">
-        <v>6923857</v>
+        <v>6923786</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1773,7 +1777,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,7 +1787,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1798,19 +1802,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124902350</v>
+        <v>124902509</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1843,41 +1847,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599899</v>
+        <v>599754</v>
       </c>
       <c r="R12" t="n">
-        <v>6923798</v>
+        <v>6923921</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1909,7 +1894,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1919,12 +1904,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett hona födosöker I en gran.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1939,22 +1924,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124900025</v>
+        <v>124900663</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1963,42 +1948,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599878</v>
+        <v>599824</v>
       </c>
       <c r="R13" t="n">
-        <v>6923820</v>
+        <v>6923802</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2030,7 +2011,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2040,7 +2021,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2055,22 +2036,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124900764</v>
+        <v>124901921</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2079,38 +2060,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599814</v>
+        <v>599742</v>
       </c>
       <c r="R14" t="n">
-        <v>6923824</v>
+        <v>6923857</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2142,7 +2132,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2152,7 +2142,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2167,22 +2157,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124899421</v>
+        <v>124900764</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2195,21 +2185,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2219,10 +2209,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599899</v>
+        <v>599814</v>
       </c>
       <c r="R15" t="n">
-        <v>6923798</v>
+        <v>6923824</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2254,7 +2244,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2264,7 +2254,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2279,22 +2269,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124901634</v>
+        <v>124901780</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2303,25 +2293,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2331,10 +2321,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599734</v>
+        <v>599756</v>
       </c>
       <c r="R16" t="n">
-        <v>6923810</v>
+        <v>6923823</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2366,7 +2356,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2376,7 +2366,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2403,10 +2393,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124900863</v>
+        <v>124900827</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2419,34 +2409,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599779</v>
+        <v>599787</v>
       </c>
       <c r="R17" t="n">
-        <v>6923783</v>
+        <v>6923799</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2478,7 +2473,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2488,7 +2483,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2515,10 +2510,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124901880</v>
+        <v>124902350</v>
       </c>
       <c r="B18" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2531,34 +2526,58 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599771</v>
+        <v>599899</v>
       </c>
       <c r="R18" t="n">
-        <v>6923841</v>
+        <v>6923798</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2590,7 +2609,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2600,12 +2619,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på asp</t>
+          <t>Tretåig hackspett hona födosöker I en gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2620,22 +2639,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124900663</v>
+        <v>124899421</v>
       </c>
       <c r="B19" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2648,21 +2667,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2672,10 +2691,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599824</v>
+        <v>599899</v>
       </c>
       <c r="R19" t="n">
-        <v>6923802</v>
+        <v>6923798</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2707,7 +2726,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2717,7 +2736,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2732,22 +2751,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124899564</v>
+        <v>124899644</v>
       </c>
       <c r="B20" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2760,34 +2779,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599910</v>
+        <v>599898</v>
       </c>
       <c r="R20" t="n">
-        <v>6923786</v>
+        <v>6923799</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2819,7 +2838,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2829,7 +2848,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2844,22 +2863,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124898168</v>
+        <v>124900226</v>
       </c>
       <c r="B21" t="n">
-        <v>91299</v>
+        <v>79891</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2872,34 +2891,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599920</v>
+        <v>599882</v>
       </c>
       <c r="R21" t="n">
-        <v>6923834</v>
+        <v>6923778</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2931,7 +2955,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2941,7 +2965,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Över 20 apothecier</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2956,22 +2985,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124899839</v>
+        <v>124900773</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2984,39 +3013,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>599893</v>
+        <v>599801</v>
       </c>
       <c r="R22" t="n">
-        <v>6923773</v>
+        <v>6923797</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3048,7 +3072,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3058,12 +3082,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:35</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3078,22 +3097,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124898290</v>
+        <v>124901922</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3102,43 +3121,42 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>599911</v>
+        <v>599783</v>
       </c>
       <c r="R23" t="n">
-        <v>6923836</v>
+        <v>6923858</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3170,7 +3188,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3180,12 +3198,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3200,22 +3213,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124900226</v>
+        <v>124901767</v>
       </c>
       <c r="B24" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3224,43 +3237,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>599882</v>
+        <v>599748</v>
       </c>
       <c r="R24" t="n">
-        <v>6923778</v>
+        <v>6923842</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3292,7 +3304,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3302,12 +3314,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:43</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Över 20 apothecier</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3322,22 +3329,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124900773</v>
+        <v>124898191</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>91673</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3346,38 +3353,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>898</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>599801</v>
+        <v>599930</v>
       </c>
       <c r="R25" t="n">
-        <v>6923797</v>
+        <v>6923840</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3409,7 +3416,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3419,7 +3426,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3434,22 +3441,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124900330</v>
+        <v>124902691</v>
       </c>
       <c r="B26" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3462,34 +3469,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>599899</v>
+        <v>599798</v>
       </c>
       <c r="R26" t="n">
-        <v>6923798</v>
+        <v>6923975</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3521,7 +3528,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3531,7 +3538,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3546,22 +3553,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124901922</v>
+        <v>124902015</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3570,42 +3577,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>599783</v>
+        <v>599777</v>
       </c>
       <c r="R27" t="n">
-        <v>6923858</v>
+        <v>6923857</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3637,7 +3640,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3647,7 +3650,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3674,10 +3677,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124898995</v>
+        <v>124900863</v>
       </c>
       <c r="B28" t="n">
-        <v>96979</v>
+        <v>91012</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3686,38 +3689,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>599930</v>
+        <v>599779</v>
       </c>
       <c r="R28" t="n">
-        <v>6923840</v>
+        <v>6923783</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3749,7 +3752,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3759,7 +3762,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3774,22 +3777,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124899341</v>
+        <v>124900661</v>
       </c>
       <c r="B29" t="n">
-        <v>90977</v>
+        <v>79891</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3798,38 +3801,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>599908</v>
+        <v>599813</v>
       </c>
       <c r="R29" t="n">
-        <v>6923811</v>
+        <v>6923781</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3861,7 +3864,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3871,7 +3874,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3886,22 +3889,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124900786</v>
+        <v>124898168</v>
       </c>
       <c r="B30" t="n">
-        <v>57529</v>
+        <v>91299</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3914,39 +3917,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>599791</v>
+        <v>599920</v>
       </c>
       <c r="R30" t="n">
-        <v>6923786</v>
+        <v>6923834</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3978,7 +3976,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3988,7 +3986,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4003,19 +4001,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124901767</v>
+        <v>124900362</v>
       </c>
       <c r="B31" t="n">
         <v>98101</v>
@@ -4050,19 +4048,24 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>599748</v>
+        <v>599864</v>
       </c>
       <c r="R31" t="n">
-        <v>6923842</v>
+        <v>6923786</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4094,7 +4097,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4104,7 +4107,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4119,22 +4122,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124900294</v>
+        <v>124901889</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4143,47 +4146,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>599864</v>
+        <v>599775</v>
       </c>
       <c r="R32" t="n">
-        <v>6923773</v>
+        <v>6923855</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4215,7 +4209,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4225,7 +4219,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4240,22 +4234,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124900313</v>
+        <v>124900018</v>
       </c>
       <c r="B33" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4268,34 +4262,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>599854</v>
+        <v>599883</v>
       </c>
       <c r="R33" t="n">
-        <v>6923776</v>
+        <v>6923768</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4327,7 +4321,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4337,7 +4331,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4352,22 +4346,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124899798</v>
+        <v>124899196</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>91457</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4380,38 +4374,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>599883</v>
+        <v>599888</v>
       </c>
       <c r="R34" t="n">
-        <v>6923782</v>
+        <v>6923798</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4443,7 +4433,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4453,7 +4443,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4480,10 +4470,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124901624</v>
+        <v>124898995</v>
       </c>
       <c r="B35" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4492,47 +4482,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>599703</v>
+        <v>599930</v>
       </c>
       <c r="R35" t="n">
-        <v>6923832</v>
+        <v>6923840</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4564,7 +4545,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4574,7 +4555,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4589,22 +4570,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124899196</v>
+        <v>124900313</v>
       </c>
       <c r="B36" t="n">
-        <v>91457</v>
+        <v>79891</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4613,25 +4594,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4641,10 +4622,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>599888</v>
+        <v>599854</v>
       </c>
       <c r="R36" t="n">
-        <v>6923798</v>
+        <v>6923776</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4676,7 +4657,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4686,7 +4667,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4713,7 +4694,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124901679</v>
+        <v>124901880</v>
       </c>
       <c r="B37" t="n">
         <v>79891</v>
@@ -4753,10 +4734,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>599728</v>
+        <v>599771</v>
       </c>
       <c r="R37" t="n">
-        <v>6923812</v>
+        <v>6923841</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4788,7 +4769,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4798,7 +4779,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på asp</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4825,10 +4811,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124899616</v>
+        <v>124899503</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4841,21 +4827,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4865,10 +4851,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>599899</v>
+        <v>599912</v>
       </c>
       <c r="R38" t="n">
-        <v>6923765</v>
+        <v>6923800</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4900,7 +4886,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4910,7 +4896,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4937,10 +4923,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124898571</v>
+        <v>124899564</v>
       </c>
       <c r="B39" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4953,39 +4939,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>599904</v>
+        <v>599910</v>
       </c>
       <c r="R39" t="n">
-        <v>6923812</v>
+        <v>6923786</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5017,7 +4998,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5027,12 +5008,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:05</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5047,22 +5023,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124900465</v>
+        <v>124898290</v>
       </c>
       <c r="B40" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5075,34 +5051,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>599856</v>
+        <v>599911</v>
       </c>
       <c r="R40" t="n">
-        <v>6923803</v>
+        <v>6923836</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5134,7 +5115,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5144,7 +5125,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5159,22 +5145,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124902509</v>
+        <v>124900025</v>
       </c>
       <c r="B41" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5183,43 +5169,42 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>599754</v>
+        <v>599878</v>
       </c>
       <c r="R41" t="n">
-        <v>6923921</v>
+        <v>6923820</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5251,7 +5236,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5261,12 +5246,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>18:29</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5293,7 +5273,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124902765</v>
+        <v>124901634</v>
       </c>
       <c r="B42" t="n">
         <v>98101</v>
@@ -5326,21 +5306,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>599800</v>
+        <v>599734</v>
       </c>
       <c r="R42" t="n">
-        <v>6923959</v>
+        <v>6923810</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5372,7 +5348,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5382,7 +5358,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5397,22 +5373,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124900827</v>
+        <v>124899616</v>
       </c>
       <c r="B43" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5425,39 +5401,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>599787</v>
+        <v>599899</v>
       </c>
       <c r="R43" t="n">
-        <v>6923799</v>
+        <v>6923765</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5489,7 +5460,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5499,7 +5470,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5514,22 +5485,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124900661</v>
+        <v>124900294</v>
       </c>
       <c r="B44" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5538,38 +5509,47 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>599813</v>
+        <v>599864</v>
       </c>
       <c r="R44" t="n">
-        <v>6923781</v>
+        <v>6923773</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5601,7 +5581,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5611,7 +5591,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5626,22 +5606,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124898191</v>
+        <v>124897942</v>
       </c>
       <c r="B45" t="n">
-        <v>91673</v>
+        <v>57513</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5650,38 +5630,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>599930</v>
+        <v>599929</v>
       </c>
       <c r="R45" t="n">
-        <v>6923840</v>
+        <v>6923847</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5713,7 +5698,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5723,7 +5708,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5738,22 +5728,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124901780</v>
+        <v>124898571</v>
       </c>
       <c r="B46" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5766,34 +5756,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>599756</v>
+        <v>599904</v>
       </c>
       <c r="R46" t="n">
-        <v>6923823</v>
+        <v>6923812</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5825,7 +5820,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5835,7 +5830,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5850,22 +5850,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124900362</v>
+        <v>124898054</v>
       </c>
       <c r="B47" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5874,47 +5874,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>599864</v>
+        <v>599930</v>
       </c>
       <c r="R47" t="n">
-        <v>6923786</v>
+        <v>6923840</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5946,7 +5937,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5956,7 +5947,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5971,22 +5967,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124898316</v>
+        <v>124899798</v>
       </c>
       <c r="B48" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5995,38 +5991,42 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>599918</v>
+        <v>599883</v>
       </c>
       <c r="R48" t="n">
-        <v>6923822</v>
+        <v>6923782</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6095,10 +6095,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124901889</v>
+        <v>124901624</v>
       </c>
       <c r="B49" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6107,38 +6107,47 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>599775</v>
+        <v>599703</v>
       </c>
       <c r="R49" t="n">
-        <v>6923855</v>
+        <v>6923832</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6170,7 +6179,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6180,7 +6189,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6195,22 +6204,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124902691</v>
+        <v>124901679</v>
       </c>
       <c r="B50" t="n">
-        <v>91030</v>
+        <v>79891</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6223,21 +6232,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6247,10 +6256,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>599798</v>
+        <v>599728</v>
       </c>
       <c r="R50" t="n">
-        <v>6923975</v>
+        <v>6923812</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6282,7 +6291,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6292,7 +6301,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6319,7 +6328,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124901921</v>
+        <v>124902765</v>
       </c>
       <c r="B51" t="n">
         <v>98101</v>
@@ -6357,21 +6366,16 @@
           <t>10</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>599742</v>
+        <v>599800</v>
       </c>
       <c r="R51" t="n">
-        <v>6923857</v>
+        <v>6923959</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6403,7 +6407,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6413,7 +6417,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6428,12 +6432,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124902839</v>
+        <v>124898191</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>91833</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>898</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599810</v>
+        <v>599930</v>
       </c>
       <c r="R2" t="n">
-        <v>6923980</v>
+        <v>6923840</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124899341</v>
+        <v>124902509</v>
       </c>
       <c r="B3" t="n">
-        <v>90977</v>
+        <v>57635</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +799,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599908</v>
+        <v>599754</v>
       </c>
       <c r="R3" t="n">
-        <v>6923811</v>
+        <v>6923921</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>18:29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124899839</v>
+        <v>124901131</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>98269</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,43 +921,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599893</v>
+        <v>599899</v>
       </c>
       <c r="R4" t="n">
-        <v>6923773</v>
+        <v>6923798</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:35</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,22 +1009,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124900330</v>
+        <v>124897942</v>
       </c>
       <c r="B5" t="n">
-        <v>91299</v>
+        <v>57635</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,34 +1037,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599899</v>
+        <v>599929</v>
       </c>
       <c r="R5" t="n">
-        <v>6923798</v>
+        <v>6923847</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1111,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,22 +1131,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124898060</v>
+        <v>124898096</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>91166</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,37 +1159,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599916</v>
+        <v>599930</v>
       </c>
       <c r="R6" t="n">
-        <v>6923847</v>
+        <v>6923840</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,22 +1243,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124900573</v>
+        <v>124899798</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,19 +1290,19 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599899</v>
+        <v>599883</v>
       </c>
       <c r="R7" t="n">
-        <v>6923798</v>
+        <v>6923782</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,22 +1359,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124898316</v>
+        <v>124901921</v>
       </c>
       <c r="B8" t="n">
-        <v>91299</v>
+        <v>98269</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,38 +1383,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599918</v>
+        <v>599742</v>
       </c>
       <c r="R8" t="n">
-        <v>6923822</v>
+        <v>6923857</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,7 +1455,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1465,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,22 +1480,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124899195</v>
+        <v>124900663</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>80028</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,21 +1508,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1513,10 +1532,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599930</v>
+        <v>599824</v>
       </c>
       <c r="R9" t="n">
-        <v>6923840</v>
+        <v>6923802</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,7 +1567,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1558,7 +1577,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1588,7 +1607,7 @@
         <v>124900465</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>80028</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1697,10 +1716,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124900786</v>
+        <v>124900330</v>
       </c>
       <c r="B11" t="n">
-        <v>57529</v>
+        <v>91459</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1713,39 +1732,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599791</v>
+        <v>599899</v>
       </c>
       <c r="R11" t="n">
-        <v>6923786</v>
+        <v>6923798</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1777,7 +1791,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1787,7 +1801,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1802,22 +1816,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124902509</v>
+        <v>124901767</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>98269</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,31 +1840,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1859,10 +1872,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599754</v>
+        <v>599748</v>
       </c>
       <c r="R12" t="n">
-        <v>6923921</v>
+        <v>6923842</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1894,7 +1907,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1904,12 +1917,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:29</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1936,10 +1944,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124900663</v>
+        <v>124900773</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>78947</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1952,34 +1960,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599824</v>
+        <v>599801</v>
       </c>
       <c r="R13" t="n">
-        <v>6923802</v>
+        <v>6923797</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2011,7 +2019,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2021,7 +2029,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2036,22 +2044,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124901921</v>
+        <v>124899341</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>91131</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2060,47 +2068,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599742</v>
+        <v>599908</v>
       </c>
       <c r="R14" t="n">
-        <v>6923857</v>
+        <v>6923811</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2132,7 +2131,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2142,7 +2141,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2157,22 +2156,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124900764</v>
+        <v>124901679</v>
       </c>
       <c r="B15" t="n">
-        <v>79891</v>
+        <v>80028</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2205,14 +2204,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599814</v>
+        <v>599728</v>
       </c>
       <c r="R15" t="n">
-        <v>6923824</v>
+        <v>6923812</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2244,7 +2243,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2254,7 +2253,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2269,22 +2268,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124901780</v>
+        <v>124899421</v>
       </c>
       <c r="B16" t="n">
-        <v>79891</v>
+        <v>91166</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2297,21 +2296,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2321,10 +2320,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599756</v>
+        <v>599899</v>
       </c>
       <c r="R16" t="n">
-        <v>6923823</v>
+        <v>6923798</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2356,7 +2355,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2366,7 +2365,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2381,22 +2380,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124900827</v>
+        <v>124902350</v>
       </c>
       <c r="B17" t="n">
-        <v>57529</v>
+        <v>57635</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2409,16 +2408,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2426,22 +2425,41 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599787</v>
+        <v>599899</v>
       </c>
       <c r="R17" t="n">
-        <v>6923799</v>
+        <v>6923798</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2473,7 +2491,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2483,7 +2501,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett hona födosöker I en gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2498,22 +2521,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124902350</v>
+        <v>124900313</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>80028</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2526,58 +2549,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599899</v>
+        <v>599854</v>
       </c>
       <c r="R18" t="n">
-        <v>6923798</v>
+        <v>6923776</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2609,7 +2608,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2619,12 +2618,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:17</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett hona födosöker I en gran.</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2639,22 +2633,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124899421</v>
+        <v>124899564</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>91459</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2667,21 +2661,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2691,10 +2685,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599899</v>
+        <v>599910</v>
       </c>
       <c r="R19" t="n">
-        <v>6923798</v>
+        <v>6923786</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2726,7 +2720,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2736,7 +2730,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2751,22 +2745,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124899644</v>
+        <v>124898168</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>91459</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2779,21 +2773,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2803,10 +2797,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599898</v>
+        <v>599920</v>
       </c>
       <c r="R20" t="n">
-        <v>6923799</v>
+        <v>6923834</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2838,7 +2832,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2848,7 +2842,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2875,10 +2869,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124900226</v>
+        <v>124900827</v>
       </c>
       <c r="B21" t="n">
-        <v>79891</v>
+        <v>57632</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2891,39 +2885,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599882</v>
+        <v>599787</v>
       </c>
       <c r="R21" t="n">
-        <v>6923778</v>
+        <v>6923799</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2955,7 +2949,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2965,12 +2959,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:43</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Över 20 apothecier</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2985,22 +2974,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124900773</v>
+        <v>124901889</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>80028</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3013,34 +3002,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>599801</v>
+        <v>599775</v>
       </c>
       <c r="R22" t="n">
-        <v>6923797</v>
+        <v>6923855</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3072,7 +3061,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3082,7 +3071,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3097,22 +3086,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124901922</v>
+        <v>124902839</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>78947</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3121,42 +3110,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>599783</v>
+        <v>599810</v>
       </c>
       <c r="R23" t="n">
-        <v>6923858</v>
+        <v>6923980</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3188,7 +3173,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3198,7 +3183,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3225,10 +3210,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124901767</v>
+        <v>124900018</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>78947</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3237,42 +3222,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>599748</v>
+        <v>599883</v>
       </c>
       <c r="R24" t="n">
-        <v>6923842</v>
+        <v>6923768</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3304,7 +3285,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3314,7 +3295,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3329,22 +3310,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124898191</v>
+        <v>124898054</v>
       </c>
       <c r="B25" t="n">
-        <v>91673</v>
+        <v>78947</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3353,25 +3334,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>898</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3416,7 +3397,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3426,7 +3407,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3453,10 +3439,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124902691</v>
+        <v>124898995</v>
       </c>
       <c r="B26" t="n">
-        <v>91030</v>
+        <v>97147</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3465,38 +3451,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>599798</v>
+        <v>599930</v>
       </c>
       <c r="R26" t="n">
-        <v>6923975</v>
+        <v>6923840</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3528,7 +3514,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3538,7 +3524,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3553,22 +3539,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124902015</v>
+        <v>124899503</v>
       </c>
       <c r="B27" t="n">
-        <v>91012</v>
+        <v>91166</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3601,14 +3587,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>599777</v>
+        <v>599912</v>
       </c>
       <c r="R27" t="n">
-        <v>6923857</v>
+        <v>6923800</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3640,7 +3626,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3650,7 +3636,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3665,22 +3651,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124900863</v>
+        <v>124899839</v>
       </c>
       <c r="B28" t="n">
-        <v>91012</v>
+        <v>57635</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3693,34 +3679,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>599779</v>
+        <v>599893</v>
       </c>
       <c r="R28" t="n">
-        <v>6923783</v>
+        <v>6923773</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3752,7 +3743,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3762,7 +3753,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3777,22 +3773,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124900661</v>
+        <v>124898290</v>
       </c>
       <c r="B29" t="n">
-        <v>79891</v>
+        <v>57635</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3805,34 +3801,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>599813</v>
+        <v>599911</v>
       </c>
       <c r="R29" t="n">
-        <v>6923781</v>
+        <v>6923836</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3864,7 +3865,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3874,7 +3875,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3889,22 +3895,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124898168</v>
+        <v>124898316</v>
       </c>
       <c r="B30" t="n">
-        <v>91299</v>
+        <v>91459</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3941,10 +3947,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>599920</v>
+        <v>599918</v>
       </c>
       <c r="R30" t="n">
-        <v>6923834</v>
+        <v>6923822</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3976,7 +3982,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3986,7 +3992,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4013,10 +4019,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124900362</v>
+        <v>124899644</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>78947</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4025,47 +4031,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>599864</v>
+        <v>599898</v>
       </c>
       <c r="R31" t="n">
-        <v>6923786</v>
+        <v>6923799</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4097,7 +4094,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4107,7 +4104,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4122,22 +4119,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124901889</v>
+        <v>124902015</v>
       </c>
       <c r="B32" t="n">
-        <v>79891</v>
+        <v>91166</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4150,34 +4147,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>599775</v>
+        <v>599777</v>
       </c>
       <c r="R32" t="n">
-        <v>6923855</v>
+        <v>6923857</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4209,7 +4206,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4219,7 +4216,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4234,22 +4231,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124900018</v>
+        <v>124899616</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4286,10 +4283,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>599883</v>
+        <v>599899</v>
       </c>
       <c r="R33" t="n">
-        <v>6923768</v>
+        <v>6923765</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4321,7 +4318,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4331,7 +4328,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4358,10 +4355,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124899196</v>
+        <v>124900661</v>
       </c>
       <c r="B34" t="n">
-        <v>91457</v>
+        <v>80028</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4370,38 +4367,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>599888</v>
+        <v>599813</v>
       </c>
       <c r="R34" t="n">
-        <v>6923798</v>
+        <v>6923781</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4433,7 +4430,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4443,7 +4440,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4470,10 +4467,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124898995</v>
+        <v>124901922</v>
       </c>
       <c r="B35" t="n">
-        <v>96979</v>
+        <v>98269</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4482,38 +4479,42 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>599930</v>
+        <v>599783</v>
       </c>
       <c r="R35" t="n">
-        <v>6923840</v>
+        <v>6923858</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4545,7 +4546,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4555,7 +4556,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4570,22 +4571,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124900313</v>
+        <v>124901634</v>
       </c>
       <c r="B36" t="n">
-        <v>79891</v>
+        <v>98269</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4594,38 +4595,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>599854</v>
+        <v>599734</v>
       </c>
       <c r="R36" t="n">
-        <v>6923776</v>
+        <v>6923810</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4657,7 +4658,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4667,7 +4668,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4682,22 +4683,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124901880</v>
+        <v>124900025</v>
       </c>
       <c r="B37" t="n">
-        <v>79891</v>
+        <v>98269</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4706,38 +4707,42 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>599771</v>
+        <v>599878</v>
       </c>
       <c r="R37" t="n">
-        <v>6923841</v>
+        <v>6923820</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4769,7 +4774,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4779,12 +4784,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:58</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på asp</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4811,10 +4811,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124899503</v>
+        <v>124900226</v>
       </c>
       <c r="B38" t="n">
-        <v>91012</v>
+        <v>80028</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4827,34 +4827,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>599912</v>
+        <v>599882</v>
       </c>
       <c r="R38" t="n">
-        <v>6923800</v>
+        <v>6923778</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4886,7 +4891,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4896,7 +4901,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Över 20 apothecier</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4923,10 +4933,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124899564</v>
+        <v>124900786</v>
       </c>
       <c r="B39" t="n">
-        <v>91299</v>
+        <v>57632</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4939,31 +4949,36 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>599910</v>
+        <v>599791</v>
       </c>
       <c r="R39" t="n">
         <v>6923786</v>
@@ -4998,7 +5013,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5008,7 +5023,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5023,22 +5038,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124898290</v>
+        <v>124900863</v>
       </c>
       <c r="B40" t="n">
-        <v>57513</v>
+        <v>91166</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5051,39 +5066,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>599911</v>
+        <v>599779</v>
       </c>
       <c r="R40" t="n">
-        <v>6923836</v>
+        <v>6923783</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5115,7 +5125,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5125,12 +5135,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5145,22 +5150,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124900025</v>
+        <v>124900764</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
+        <v>80028</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5169,42 +5174,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>599878</v>
+        <v>599814</v>
       </c>
       <c r="R41" t="n">
-        <v>6923820</v>
+        <v>6923824</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5236,7 +5237,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5246,7 +5247,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5261,22 +5262,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124901634</v>
+        <v>124898060</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
+        <v>78947</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5285,41 +5286,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>599734</v>
+        <v>599916</v>
       </c>
       <c r="R42" t="n">
-        <v>6923810</v>
+        <v>6923847</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5348,7 +5349,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5358,7 +5359,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5373,22 +5374,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124899616</v>
+        <v>124901624</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>98269</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5397,38 +5398,47 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>599899</v>
+        <v>599703</v>
       </c>
       <c r="R43" t="n">
-        <v>6923765</v>
+        <v>6923832</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5460,7 +5470,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5470,7 +5480,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5485,22 +5495,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124900294</v>
+        <v>124898571</v>
       </c>
       <c r="B44" t="n">
-        <v>98101</v>
+        <v>57635</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5509,35 +5519,31 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5546,10 +5552,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>599864</v>
+        <v>599904</v>
       </c>
       <c r="R44" t="n">
-        <v>6923773</v>
+        <v>6923812</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5581,7 +5587,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5591,7 +5597,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5618,10 +5629,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124897942</v>
+        <v>124900362</v>
       </c>
       <c r="B45" t="n">
-        <v>57513</v>
+        <v>98269</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5630,31 +5641,35 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5663,10 +5678,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>599929</v>
+        <v>599864</v>
       </c>
       <c r="R45" t="n">
-        <v>6923847</v>
+        <v>6923786</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5698,7 +5713,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5708,12 +5723,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5740,10 +5750,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124898571</v>
+        <v>124902765</v>
       </c>
       <c r="B46" t="n">
-        <v>57513</v>
+        <v>98269</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5752,43 +5762,42 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>599904</v>
+        <v>599800</v>
       </c>
       <c r="R46" t="n">
-        <v>6923812</v>
+        <v>6923959</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5820,7 +5829,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5830,12 +5839,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:05</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5850,22 +5854,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124898054</v>
+        <v>124900294</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>98269</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5874,38 +5878,47 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>599930</v>
+        <v>599864</v>
       </c>
       <c r="R47" t="n">
-        <v>6923840</v>
+        <v>6923773</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5937,7 +5950,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5947,12 +5960,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5967,22 +5975,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124899798</v>
+        <v>124901880</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>80028</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5991,42 +5999,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>599883</v>
+        <v>599771</v>
       </c>
       <c r="R48" t="n">
-        <v>6923782</v>
+        <v>6923841</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6058,7 +6062,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6068,7 +6072,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på asp</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6095,10 +6104,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124901624</v>
+        <v>124901780</v>
       </c>
       <c r="B49" t="n">
-        <v>98101</v>
+        <v>80028</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6107,47 +6116,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>599703</v>
+        <v>599756</v>
       </c>
       <c r="R49" t="n">
-        <v>6923832</v>
+        <v>6923823</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6204,22 +6204,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124901679</v>
+        <v>124902691</v>
       </c>
       <c r="B50" t="n">
-        <v>79891</v>
+        <v>91184</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6232,21 +6232,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6256,10 +6256,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>599728</v>
+        <v>599798</v>
       </c>
       <c r="R50" t="n">
-        <v>6923812</v>
+        <v>6923975</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6291,7 +6291,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6328,10 +6328,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124902765</v>
+        <v>124899196</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
+        <v>91617</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6344,38 +6344,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>599800</v>
+        <v>599888</v>
       </c>
       <c r="R51" t="n">
-        <v>6923959</v>
+        <v>6923798</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6407,7 +6403,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6417,7 +6413,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -2533,10 +2533,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124900313</v>
+        <v>124899564</v>
       </c>
       <c r="B18" t="n">
-        <v>80028</v>
+        <v>91459</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2549,34 +2549,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599854</v>
+        <v>599910</v>
       </c>
       <c r="R18" t="n">
-        <v>6923776</v>
+        <v>6923786</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,19 +2633,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124899564</v>
+        <v>124898168</v>
       </c>
       <c r="B19" t="n">
         <v>91459</v>
@@ -2681,14 +2681,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599910</v>
+        <v>599920</v>
       </c>
       <c r="R19" t="n">
-        <v>6923786</v>
+        <v>6923834</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2745,22 +2745,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124898168</v>
+        <v>124900313</v>
       </c>
       <c r="B20" t="n">
-        <v>91459</v>
+        <v>80028</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2773,21 +2773,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2797,10 +2797,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599920</v>
+        <v>599854</v>
       </c>
       <c r="R20" t="n">
-        <v>6923834</v>
+        <v>6923776</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2869,10 +2869,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124900827</v>
+        <v>124899503</v>
       </c>
       <c r="B21" t="n">
-        <v>57632</v>
+        <v>91166</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2885,39 +2885,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599787</v>
+        <v>599912</v>
       </c>
       <c r="R21" t="n">
-        <v>6923799</v>
+        <v>6923800</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2949,7 +2944,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2959,7 +2954,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2974,22 +2969,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124901889</v>
+        <v>124900827</v>
       </c>
       <c r="B22" t="n">
-        <v>80028</v>
+        <v>57632</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3002,34 +2997,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>599775</v>
+        <v>599787</v>
       </c>
       <c r="R22" t="n">
-        <v>6923855</v>
+        <v>6923799</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3086,22 +3086,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124902839</v>
+        <v>124901889</v>
       </c>
       <c r="B23" t="n">
-        <v>78947</v>
+        <v>80028</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3114,34 +3114,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>599810</v>
+        <v>599775</v>
       </c>
       <c r="R23" t="n">
-        <v>6923980</v>
+        <v>6923855</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3198,19 +3198,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124900018</v>
+        <v>124902839</v>
       </c>
       <c r="B24" t="n">
         <v>78947</v>
@@ -3246,14 +3246,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>599883</v>
+        <v>599810</v>
       </c>
       <c r="R24" t="n">
-        <v>6923768</v>
+        <v>6923980</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3310,19 +3310,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124898054</v>
+        <v>124900018</v>
       </c>
       <c r="B25" t="n">
         <v>78947</v>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>599930</v>
+        <v>599883</v>
       </c>
       <c r="R25" t="n">
-        <v>6923840</v>
+        <v>6923768</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3407,12 +3407,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3439,10 +3434,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124898995</v>
+        <v>124898054</v>
       </c>
       <c r="B26" t="n">
-        <v>97147</v>
+        <v>78947</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3451,25 +3446,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3514,7 +3509,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3524,7 +3519,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3551,10 +3551,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124899503</v>
+        <v>124898995</v>
       </c>
       <c r="B27" t="n">
-        <v>91166</v>
+        <v>97147</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3563,25 +3563,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3591,10 +3591,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>599912</v>
+        <v>599930</v>
       </c>
       <c r="R27" t="n">
-        <v>6923800</v>
+        <v>6923840</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3663,10 +3663,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124899839</v>
+        <v>124902015</v>
       </c>
       <c r="B28" t="n">
-        <v>57635</v>
+        <v>91166</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3679,39 +3679,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>599893</v>
+        <v>599777</v>
       </c>
       <c r="R28" t="n">
-        <v>6923773</v>
+        <v>6923857</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3743,7 +3738,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3753,12 +3748,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:35</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3773,22 +3763,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124898290</v>
+        <v>124898316</v>
       </c>
       <c r="B29" t="n">
-        <v>57635</v>
+        <v>91459</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3801,39 +3791,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>599911</v>
+        <v>599918</v>
       </c>
       <c r="R29" t="n">
-        <v>6923836</v>
+        <v>6923822</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3865,7 +3850,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3875,12 +3860,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3895,22 +3875,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124898316</v>
+        <v>124899839</v>
       </c>
       <c r="B30" t="n">
-        <v>91459</v>
+        <v>57635</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3923,34 +3903,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>599918</v>
+        <v>599893</v>
       </c>
       <c r="R30" t="n">
-        <v>6923822</v>
+        <v>6923773</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3982,7 +3967,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3992,7 +3977,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4007,22 +3997,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124899644</v>
+        <v>124898290</v>
       </c>
       <c r="B31" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4035,34 +4025,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>599898</v>
+        <v>599911</v>
       </c>
       <c r="R31" t="n">
-        <v>6923799</v>
+        <v>6923836</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4094,7 +4089,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4104,7 +4099,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4119,22 +4119,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124902015</v>
+        <v>124899644</v>
       </c>
       <c r="B32" t="n">
-        <v>91166</v>
+        <v>78947</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4147,34 +4147,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>599777</v>
+        <v>599898</v>
       </c>
       <c r="R32" t="n">
-        <v>6923857</v>
+        <v>6923799</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4583,10 +4583,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124901634</v>
+        <v>124900226</v>
       </c>
       <c r="B36" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4595,38 +4595,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>599734</v>
+        <v>599882</v>
       </c>
       <c r="R36" t="n">
-        <v>6923810</v>
+        <v>6923778</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4658,7 +4663,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4668,7 +4673,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Över 20 apothecier</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4695,10 +4705,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124900025</v>
+        <v>124900786</v>
       </c>
       <c r="B37" t="n">
-        <v>98269</v>
+        <v>57632</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4707,42 +4717,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>12</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>599878</v>
+        <v>599791</v>
       </c>
       <c r="R37" t="n">
-        <v>6923820</v>
+        <v>6923786</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4774,7 +4785,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4784,7 +4795,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4799,22 +4810,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124900226</v>
+        <v>124901634</v>
       </c>
       <c r="B38" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4823,43 +4834,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>599882</v>
+        <v>599734</v>
       </c>
       <c r="R38" t="n">
-        <v>6923778</v>
+        <v>6923810</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4891,7 +4897,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4901,12 +4907,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:43</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Över 20 apothecier</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4933,10 +4934,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124900786</v>
+        <v>124900025</v>
       </c>
       <c r="B39" t="n">
-        <v>57632</v>
+        <v>98269</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4945,43 +4946,42 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>599791</v>
+        <v>599878</v>
       </c>
       <c r="R39" t="n">
-        <v>6923786</v>
+        <v>6923820</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5013,7 +5013,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5038,12 +5038,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124898191</v>
+        <v>124900786</v>
       </c>
       <c r="B2" t="n">
-        <v>91833</v>
+        <v>57632</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>898</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599930</v>
+        <v>599791</v>
       </c>
       <c r="R2" t="n">
-        <v>6923840</v>
+        <v>6923786</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124902509</v>
+        <v>124900663</v>
       </c>
       <c r="B3" t="n">
-        <v>57635</v>
+        <v>80028</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599754</v>
+        <v>599824</v>
       </c>
       <c r="R3" t="n">
-        <v>6923921</v>
+        <v>6923802</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,19 +892,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124901131</v>
+        <v>124901624</v>
       </c>
       <c r="B4" t="n">
         <v>98269</v>
@@ -942,17 +937,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599899</v>
+        <v>599703</v>
       </c>
       <c r="R4" t="n">
-        <v>6923798</v>
+        <v>6923832</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,22 +1013,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124897942</v>
+        <v>124901679</v>
       </c>
       <c r="B5" t="n">
-        <v>57635</v>
+        <v>80028</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,39 +1041,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599929</v>
+        <v>599728</v>
       </c>
       <c r="R5" t="n">
-        <v>6923847</v>
+        <v>6923812</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,22 +1125,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124898096</v>
+        <v>124900226</v>
       </c>
       <c r="B6" t="n">
-        <v>91166</v>
+        <v>80028</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,34 +1153,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599930</v>
+        <v>599882</v>
       </c>
       <c r="R6" t="n">
-        <v>6923840</v>
+        <v>6923778</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1227,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Över 20 apothecier</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124899798</v>
+        <v>124902015</v>
       </c>
       <c r="B7" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,42 +1271,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599883</v>
+        <v>599777</v>
       </c>
       <c r="R7" t="n">
-        <v>6923782</v>
+        <v>6923857</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124901921</v>
+        <v>124897942</v>
       </c>
       <c r="B8" t="n">
-        <v>98269</v>
+        <v>57635</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,47 +1383,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599742</v>
+        <v>599929</v>
       </c>
       <c r="R8" t="n">
-        <v>6923857</v>
+        <v>6923847</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1465,7 +1461,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,10 +1493,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124900663</v>
+        <v>124898290</v>
       </c>
       <c r="B9" t="n">
-        <v>80028</v>
+        <v>57635</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1508,34 +1509,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599824</v>
+        <v>599911</v>
       </c>
       <c r="R9" t="n">
-        <v>6923802</v>
+        <v>6923836</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,7 +1573,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1577,7 +1583,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1592,22 +1603,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124900465</v>
+        <v>124899341</v>
       </c>
       <c r="B10" t="n">
-        <v>80028</v>
+        <v>91131</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,25 +1627,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1644,10 +1655,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599856</v>
+        <v>599908</v>
       </c>
       <c r="R10" t="n">
-        <v>6923803</v>
+        <v>6923811</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,7 +1690,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1689,7 +1700,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1716,10 +1727,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124900330</v>
+        <v>124899644</v>
       </c>
       <c r="B11" t="n">
-        <v>91459</v>
+        <v>78947</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1732,34 +1743,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599899</v>
+        <v>599898</v>
       </c>
       <c r="R11" t="n">
-        <v>6923798</v>
+        <v>6923799</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,7 +1802,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1801,7 +1812,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,22 +1827,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124901767</v>
+        <v>124900018</v>
       </c>
       <c r="B12" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1840,42 +1851,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599748</v>
+        <v>599883</v>
       </c>
       <c r="R12" t="n">
-        <v>6923842</v>
+        <v>6923768</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,7 +1914,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1917,7 +1924,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,22 +1939,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124900773</v>
+        <v>124901922</v>
       </c>
       <c r="B13" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,38 +1963,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599801</v>
+        <v>599783</v>
       </c>
       <c r="R13" t="n">
-        <v>6923797</v>
+        <v>6923858</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,7 +2030,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2029,7 +2040,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2056,10 +2067,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124899341</v>
+        <v>124900573</v>
       </c>
       <c r="B14" t="n">
-        <v>91131</v>
+        <v>98269</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2068,38 +2079,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599908</v>
+        <v>599899</v>
       </c>
       <c r="R14" t="n">
-        <v>6923811</v>
+        <v>6923798</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2131,7 +2146,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2141,7 +2156,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2156,22 +2171,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124901679</v>
+        <v>124898096</v>
       </c>
       <c r="B15" t="n">
-        <v>80028</v>
+        <v>91166</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2184,34 +2199,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599728</v>
+        <v>599930</v>
       </c>
       <c r="R15" t="n">
-        <v>6923812</v>
+        <v>6923840</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2243,7 +2258,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2253,7 +2268,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,19 +2283,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124899421</v>
+        <v>124900863</v>
       </c>
       <c r="B16" t="n">
         <v>91166</v>
@@ -2316,14 +2331,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599899</v>
+        <v>599779</v>
       </c>
       <c r="R16" t="n">
-        <v>6923798</v>
+        <v>6923783</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2355,7 +2370,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2365,7 +2380,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,22 +2395,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124902350</v>
+        <v>124899503</v>
       </c>
       <c r="B17" t="n">
-        <v>57635</v>
+        <v>91166</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2408,58 +2423,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599899</v>
+        <v>599912</v>
       </c>
       <c r="R17" t="n">
-        <v>6923798</v>
+        <v>6923800</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2491,7 +2482,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2501,12 +2492,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:17</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett hona födosöker I en gran.</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2521,19 +2507,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124899564</v>
+        <v>124898168</v>
       </c>
       <c r="B18" t="n">
         <v>91459</v>
@@ -2569,14 +2555,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599910</v>
+        <v>599920</v>
       </c>
       <c r="R18" t="n">
-        <v>6923786</v>
+        <v>6923834</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2608,7 +2594,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2618,7 +2604,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,19 +2619,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124898168</v>
+        <v>124898316</v>
       </c>
       <c r="B19" t="n">
         <v>91459</v>
@@ -2685,10 +2671,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599920</v>
+        <v>599918</v>
       </c>
       <c r="R19" t="n">
-        <v>6923834</v>
+        <v>6923822</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2720,7 +2706,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2730,7 +2716,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2757,7 +2743,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124900313</v>
+        <v>124900764</v>
       </c>
       <c r="B20" t="n">
         <v>80028</v>
@@ -2793,14 +2779,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599854</v>
+        <v>599814</v>
       </c>
       <c r="R20" t="n">
-        <v>6923776</v>
+        <v>6923824</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2832,7 +2818,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2842,7 +2828,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2857,22 +2843,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124899503</v>
+        <v>124900362</v>
       </c>
       <c r="B21" t="n">
-        <v>91166</v>
+        <v>98269</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2881,38 +2867,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599912</v>
+        <v>599864</v>
       </c>
       <c r="R21" t="n">
-        <v>6923800</v>
+        <v>6923786</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2944,7 +2939,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2954,7 +2949,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2969,22 +2964,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124900827</v>
+        <v>124901889</v>
       </c>
       <c r="B22" t="n">
-        <v>57632</v>
+        <v>80028</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2997,39 +2992,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>599787</v>
+        <v>599775</v>
       </c>
       <c r="R22" t="n">
-        <v>6923799</v>
+        <v>6923855</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3061,7 +3051,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3071,7 +3061,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3086,22 +3076,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124901889</v>
+        <v>124899798</v>
       </c>
       <c r="B23" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3110,38 +3100,42 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>599775</v>
+        <v>599883</v>
       </c>
       <c r="R23" t="n">
-        <v>6923855</v>
+        <v>6923782</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3173,7 +3167,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3183,7 +3177,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3198,22 +3192,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124902839</v>
+        <v>124901634</v>
       </c>
       <c r="B24" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3222,38 +3216,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>599810</v>
+        <v>599734</v>
       </c>
       <c r="R24" t="n">
-        <v>6923980</v>
+        <v>6923810</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3285,7 +3279,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3295,7 +3289,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3310,22 +3304,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124900018</v>
+        <v>124901880</v>
       </c>
       <c r="B25" t="n">
-        <v>78947</v>
+        <v>80028</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3338,34 +3332,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>599883</v>
+        <v>599771</v>
       </c>
       <c r="R25" t="n">
-        <v>6923768</v>
+        <v>6923841</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3397,7 +3391,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3407,7 +3401,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på asp</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3422,22 +3421,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124898054</v>
+        <v>124900465</v>
       </c>
       <c r="B26" t="n">
-        <v>78947</v>
+        <v>80028</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3450,21 +3449,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3474,10 +3473,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>599930</v>
+        <v>599856</v>
       </c>
       <c r="R26" t="n">
-        <v>6923840</v>
+        <v>6923803</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3509,7 +3508,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3519,12 +3518,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3551,10 +3545,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124898995</v>
+        <v>124900313</v>
       </c>
       <c r="B27" t="n">
-        <v>97147</v>
+        <v>80028</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3563,38 +3557,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>599930</v>
+        <v>599854</v>
       </c>
       <c r="R27" t="n">
-        <v>6923840</v>
+        <v>6923776</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3626,7 +3620,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3636,7 +3630,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3651,22 +3645,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124902015</v>
+        <v>124899616</v>
       </c>
       <c r="B28" t="n">
-        <v>91166</v>
+        <v>78947</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3679,34 +3673,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>599777</v>
+        <v>599899</v>
       </c>
       <c r="R28" t="n">
-        <v>6923857</v>
+        <v>6923765</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3738,7 +3732,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3748,7 +3742,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3763,22 +3757,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124898316</v>
+        <v>124898191</v>
       </c>
       <c r="B29" t="n">
-        <v>91459</v>
+        <v>91833</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3787,38 +3781,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>898</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>599918</v>
+        <v>599930</v>
       </c>
       <c r="R29" t="n">
-        <v>6923822</v>
+        <v>6923840</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3850,7 +3844,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3860,7 +3854,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3875,22 +3869,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124899839</v>
+        <v>124901780</v>
       </c>
       <c r="B30" t="n">
-        <v>57635</v>
+        <v>80028</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3903,39 +3897,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>599893</v>
+        <v>599756</v>
       </c>
       <c r="R30" t="n">
-        <v>6923773</v>
+        <v>6923823</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3967,7 +3956,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3977,12 +3966,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:35</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3997,22 +3981,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124898290</v>
+        <v>124900773</v>
       </c>
       <c r="B31" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4025,39 +4009,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>599911</v>
+        <v>599801</v>
       </c>
       <c r="R31" t="n">
-        <v>6923836</v>
+        <v>6923797</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4089,7 +4068,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4099,12 +4078,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4119,22 +4093,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124899644</v>
+        <v>124902509</v>
       </c>
       <c r="B32" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4147,34 +4121,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>599898</v>
+        <v>599754</v>
       </c>
       <c r="R32" t="n">
-        <v>6923799</v>
+        <v>6923921</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4206,7 +4185,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4216,7 +4195,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>18:29</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4243,10 +4227,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124899616</v>
+        <v>124901767</v>
       </c>
       <c r="B33" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4255,38 +4239,42 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>599899</v>
+        <v>599748</v>
       </c>
       <c r="R33" t="n">
-        <v>6923765</v>
+        <v>6923842</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4318,7 +4306,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4328,7 +4316,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4343,22 +4331,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124900661</v>
+        <v>124898571</v>
       </c>
       <c r="B34" t="n">
-        <v>80028</v>
+        <v>57635</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4371,34 +4359,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>599813</v>
+        <v>599904</v>
       </c>
       <c r="R34" t="n">
-        <v>6923781</v>
+        <v>6923812</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4430,7 +4423,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4440,7 +4433,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4455,22 +4453,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124901922</v>
+        <v>124899196</v>
       </c>
       <c r="B35" t="n">
-        <v>98269</v>
+        <v>91617</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4483,38 +4481,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>599783</v>
+        <v>599888</v>
       </c>
       <c r="R35" t="n">
-        <v>6923858</v>
+        <v>6923798</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4546,7 +4540,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4556,7 +4550,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4583,7 +4577,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124900226</v>
+        <v>124900661</v>
       </c>
       <c r="B36" t="n">
         <v>80028</v>
@@ -4617,21 +4611,16 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>599882</v>
+        <v>599813</v>
       </c>
       <c r="R36" t="n">
-        <v>6923778</v>
+        <v>6923781</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4663,7 +4652,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4673,12 +4662,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:43</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Över 20 apothecier</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4693,19 +4677,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124900786</v>
+        <v>124900827</v>
       </c>
       <c r="B37" t="n">
         <v>57632</v>
@@ -4741,7 +4725,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4750,10 +4734,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>599791</v>
+        <v>599787</v>
       </c>
       <c r="R37" t="n">
-        <v>6923786</v>
+        <v>6923799</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4785,7 +4769,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4795,7 +4779,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4810,22 +4794,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124901634</v>
+        <v>124902691</v>
       </c>
       <c r="B38" t="n">
-        <v>98269</v>
+        <v>91184</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4834,38 +4818,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>599734</v>
+        <v>599798</v>
       </c>
       <c r="R38" t="n">
-        <v>6923810</v>
+        <v>6923975</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4897,7 +4881,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4907,7 +4891,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4922,19 +4906,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124900025</v>
+        <v>124902765</v>
       </c>
       <c r="B39" t="n">
         <v>98269</v>
@@ -4969,19 +4953,19 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>599878</v>
+        <v>599800</v>
       </c>
       <c r="R39" t="n">
-        <v>6923820</v>
+        <v>6923959</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5013,7 +4997,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5023,7 +5007,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5050,10 +5034,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124900863</v>
+        <v>124899564</v>
       </c>
       <c r="B40" t="n">
-        <v>91166</v>
+        <v>91459</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5066,34 +5050,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>599779</v>
+        <v>599910</v>
       </c>
       <c r="R40" t="n">
-        <v>6923783</v>
+        <v>6923786</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5125,7 +5109,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5135,7 +5119,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5150,22 +5134,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124900764</v>
+        <v>124902839</v>
       </c>
       <c r="B41" t="n">
-        <v>80028</v>
+        <v>78947</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5178,34 +5162,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>599814</v>
+        <v>599810</v>
       </c>
       <c r="R41" t="n">
-        <v>6923824</v>
+        <v>6923980</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5237,7 +5221,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5247,7 +5231,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5262,22 +5246,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124898060</v>
+        <v>124902350</v>
       </c>
       <c r="B42" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5290,37 +5274,61 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>599916</v>
+        <v>599899</v>
       </c>
       <c r="R42" t="n">
-        <v>6923847</v>
+        <v>6923798</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5349,7 +5357,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5359,7 +5367,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett hona födosöker I en gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5374,19 +5387,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124901624</v>
+        <v>124900294</v>
       </c>
       <c r="B43" t="n">
         <v>98269</v>
@@ -5421,7 +5434,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5431,14 +5444,14 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>599703</v>
+        <v>599864</v>
       </c>
       <c r="R43" t="n">
-        <v>6923832</v>
+        <v>6923773</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5470,7 +5483,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5480,7 +5493,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5507,10 +5520,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124898571</v>
+        <v>124901921</v>
       </c>
       <c r="B44" t="n">
-        <v>57635</v>
+        <v>98269</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5519,43 +5532,47 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>599904</v>
+        <v>599742</v>
       </c>
       <c r="R44" t="n">
-        <v>6923812</v>
+        <v>6923857</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5587,7 +5604,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5597,12 +5614,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:05</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5629,7 +5641,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124900362</v>
+        <v>124900025</v>
       </c>
       <c r="B45" t="n">
         <v>98269</v>
@@ -5664,12 +5676,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5678,10 +5685,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>599864</v>
+        <v>599878</v>
       </c>
       <c r="R45" t="n">
-        <v>6923786</v>
+        <v>6923820</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5713,7 +5720,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5723,7 +5730,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5738,22 +5745,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124902765</v>
+        <v>124898054</v>
       </c>
       <c r="B46" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5762,42 +5769,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>599800</v>
+        <v>599930</v>
       </c>
       <c r="R46" t="n">
-        <v>6923959</v>
+        <v>6923840</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5829,7 +5832,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5839,7 +5842,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5854,22 +5862,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124900294</v>
+        <v>124898995</v>
       </c>
       <c r="B47" t="n">
-        <v>98269</v>
+        <v>97147</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5878,47 +5886,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>599864</v>
+        <v>599930</v>
       </c>
       <c r="R47" t="n">
-        <v>6923773</v>
+        <v>6923840</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5950,7 +5949,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5960,7 +5959,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5975,22 +5974,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124901880</v>
+        <v>124900330</v>
       </c>
       <c r="B48" t="n">
-        <v>80028</v>
+        <v>91459</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6003,34 +6002,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>599771</v>
+        <v>599899</v>
       </c>
       <c r="R48" t="n">
-        <v>6923841</v>
+        <v>6923798</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6062,7 +6061,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6072,12 +6071,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:58</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på asp</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6092,22 +6086,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124901780</v>
+        <v>124899421</v>
       </c>
       <c r="B49" t="n">
-        <v>80028</v>
+        <v>91166</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6120,21 +6114,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6144,10 +6138,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>599756</v>
+        <v>599899</v>
       </c>
       <c r="R49" t="n">
-        <v>6923823</v>
+        <v>6923798</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6179,7 +6173,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6189,7 +6183,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6204,22 +6198,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124902691</v>
+        <v>124898060</v>
       </c>
       <c r="B50" t="n">
-        <v>91184</v>
+        <v>78947</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6232,37 +6226,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>599798</v>
+        <v>599916</v>
       </c>
       <c r="R50" t="n">
-        <v>6923975</v>
+        <v>6923847</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6291,7 +6285,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6301,7 +6295,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6328,10 +6322,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124899196</v>
+        <v>124899839</v>
       </c>
       <c r="B51" t="n">
-        <v>91617</v>
+        <v>57635</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6340,38 +6334,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>599888</v>
+        <v>599893</v>
       </c>
       <c r="R51" t="n">
-        <v>6923798</v>
+        <v>6923773</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6403,7 +6402,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6413,7 +6412,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6428,12 +6432,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -2183,7 +2183,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124898096</v>
+        <v>124900863</v>
       </c>
       <c r="B15" t="n">
         <v>91166</v>
@@ -2219,14 +2219,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599930</v>
+        <v>599779</v>
       </c>
       <c r="R15" t="n">
-        <v>6923840</v>
+        <v>6923783</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2283,19 +2283,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124900863</v>
+        <v>124898096</v>
       </c>
       <c r="B16" t="n">
         <v>91166</v>
@@ -2331,14 +2331,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599779</v>
+        <v>599930</v>
       </c>
       <c r="R16" t="n">
-        <v>6923783</v>
+        <v>6923840</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2395,22 +2395,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124899503</v>
+        <v>124900764</v>
       </c>
       <c r="B17" t="n">
-        <v>91166</v>
+        <v>80028</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2423,21 +2423,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599912</v>
+        <v>599814</v>
       </c>
       <c r="R17" t="n">
-        <v>6923800</v>
+        <v>6923824</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2743,10 +2743,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124900764</v>
+        <v>124900362</v>
       </c>
       <c r="B20" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2755,38 +2755,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599814</v>
+        <v>599864</v>
       </c>
       <c r="R20" t="n">
-        <v>6923824</v>
+        <v>6923786</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2818,7 +2827,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2828,7 +2837,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2843,22 +2852,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124900362</v>
+        <v>124899503</v>
       </c>
       <c r="B21" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2867,47 +2876,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599864</v>
+        <v>599912</v>
       </c>
       <c r="R21" t="n">
-        <v>6923786</v>
+        <v>6923800</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2939,7 +2939,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2964,12 +2964,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3088,7 +3088,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124899798</v>
+        <v>124901634</v>
       </c>
       <c r="B23" t="n">
         <v>98269</v>
@@ -3121,21 +3121,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>599883</v>
+        <v>599734</v>
       </c>
       <c r="R23" t="n">
-        <v>6923782</v>
+        <v>6923810</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3167,7 +3163,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3177,7 +3173,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3192,19 +3188,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124901634</v>
+        <v>124899798</v>
       </c>
       <c r="B24" t="n">
         <v>98269</v>
@@ -3237,17 +3233,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>599734</v>
+        <v>599883</v>
       </c>
       <c r="R24" t="n">
-        <v>6923810</v>
+        <v>6923782</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3304,12 +3304,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3881,10 +3881,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124901780</v>
+        <v>124901767</v>
       </c>
       <c r="B30" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3893,38 +3893,42 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>599756</v>
+        <v>599748</v>
       </c>
       <c r="R30" t="n">
-        <v>6923823</v>
+        <v>6923842</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3956,7 +3960,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3966,7 +3970,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3981,12 +3985,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4227,10 +4231,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124901767</v>
+        <v>124901780</v>
       </c>
       <c r="B33" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4239,42 +4243,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>599748</v>
+        <v>599756</v>
       </c>
       <c r="R33" t="n">
-        <v>6923842</v>
+        <v>6923823</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4331,12 +4331,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AY59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2183,7 +2183,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124900863</v>
+        <v>124898096</v>
       </c>
       <c r="B15" t="n">
         <v>91166</v>
@@ -2219,14 +2219,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599779</v>
+        <v>599930</v>
       </c>
       <c r="R15" t="n">
-        <v>6923783</v>
+        <v>6923840</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2283,19 +2283,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124898096</v>
+        <v>124900863</v>
       </c>
       <c r="B16" t="n">
         <v>91166</v>
@@ -2331,14 +2331,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599930</v>
+        <v>599779</v>
       </c>
       <c r="R16" t="n">
-        <v>6923840</v>
+        <v>6923783</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2395,12 +2395,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -4343,10 +4343,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124898571</v>
+        <v>124899196</v>
       </c>
       <c r="B34" t="n">
-        <v>57635</v>
+        <v>91617</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4355,43 +4355,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>599904</v>
+        <v>599888</v>
       </c>
       <c r="R34" t="n">
-        <v>6923812</v>
+        <v>6923798</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4423,7 +4418,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4433,12 +4428,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:05</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4453,22 +4443,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124899196</v>
+        <v>124898571</v>
       </c>
       <c r="B35" t="n">
-        <v>91617</v>
+        <v>57635</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4477,38 +4467,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>599888</v>
+        <v>599904</v>
       </c>
       <c r="R35" t="n">
-        <v>6923798</v>
+        <v>6923812</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4540,7 +4535,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4550,7 +4545,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4565,12 +4565,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -6442,6 +6442,830 @@
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>125686610</v>
+      </c>
+      <c r="B52" t="n">
+        <v>91177</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>1205</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Stor aspticka</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Phellinus populicola</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>599815</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6923786</v>
+      </c>
+      <c r="S52" t="n">
+        <v>15</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>125685582</v>
+      </c>
+      <c r="B53" t="n">
+        <v>80028</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>599906</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6923816</v>
+      </c>
+      <c r="S53" t="n">
+        <v>15</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>125685122</v>
+      </c>
+      <c r="B54" t="n">
+        <v>91166</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>600013</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6923741</v>
+      </c>
+      <c r="S54" t="n">
+        <v>15</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>125685866</v>
+      </c>
+      <c r="B55" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>599803</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6923868</v>
+      </c>
+      <c r="S55" t="n">
+        <v>15</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>125685331</v>
+      </c>
+      <c r="B56" t="n">
+        <v>88512</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>510</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>599910</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6923817</v>
+      </c>
+      <c r="S56" t="n">
+        <v>15</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>125685127</v>
+      </c>
+      <c r="B57" t="n">
+        <v>91131</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>600027</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6923772</v>
+      </c>
+      <c r="S57" t="n">
+        <v>15</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>125685402</v>
+      </c>
+      <c r="B58" t="n">
+        <v>91459</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>658</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>599900</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6923788</v>
+      </c>
+      <c r="S58" t="n">
+        <v>15</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>125686642</v>
+      </c>
+      <c r="B59" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>599816</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6923786</v>
+      </c>
+      <c r="S59" t="n">
+        <v>15</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124900786</v>
+        <v>124901679</v>
       </c>
       <c r="B2" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599791</v>
+        <v>599728</v>
       </c>
       <c r="R2" t="n">
-        <v>6923786</v>
+        <v>6923812</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,27 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124900663</v>
+        <v>124898054</v>
       </c>
       <c r="B3" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599824</v>
+        <v>599930</v>
       </c>
       <c r="R3" t="n">
-        <v>6923802</v>
+        <v>6923840</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +862,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,59 +894,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124901624</v>
+        <v>124899616</v>
       </c>
       <c r="B4" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599703</v>
+        <v>599899</v>
       </c>
       <c r="R4" t="n">
-        <v>6923832</v>
+        <v>6923765</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,28 +989,23 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124901679</v>
+        <v>124901880</v>
       </c>
       <c r="B5" t="n">
         <v>80028</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1065,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599728</v>
+        <v>599771</v>
       </c>
       <c r="R5" t="n">
-        <v>6923812</v>
+        <v>6923841</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1081,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på asp</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,15 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124900226</v>
+        <v>124902839</v>
       </c>
       <c r="B6" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,39 +1124,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599882</v>
+        <v>599810</v>
       </c>
       <c r="R6" t="n">
-        <v>6923778</v>
+        <v>6923980</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,12 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:43</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Över 20 apothecier</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,62 +1208,66 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124902015</v>
+        <v>124900294</v>
       </c>
       <c r="B7" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599777</v>
+        <v>599864</v>
       </c>
       <c r="R7" t="n">
-        <v>6923857</v>
+        <v>6923773</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,67 +1324,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124897942</v>
+        <v>124898995</v>
       </c>
       <c r="B8" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97147</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599929</v>
+        <v>599930</v>
       </c>
       <c r="R8" t="n">
-        <v>6923847</v>
+        <v>6923840</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,7 +1406,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,12 +1416,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,27 +1431,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124898290</v>
+        <v>124899644</v>
       </c>
       <c r="B9" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,39 +1454,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599911</v>
+        <v>599898</v>
       </c>
       <c r="R9" t="n">
-        <v>6923836</v>
+        <v>6923799</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,7 +1513,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,12 +1523,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,49 +1538,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124899341</v>
+        <v>124900764</v>
       </c>
       <c r="B10" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1655,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599908</v>
+        <v>599814</v>
       </c>
       <c r="R10" t="n">
-        <v>6923811</v>
+        <v>6923824</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1690,7 +1620,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1700,7 +1630,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1727,15 +1657,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124899644</v>
+        <v>124901889</v>
       </c>
       <c r="B11" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,34 +1668,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599898</v>
+        <v>599775</v>
       </c>
       <c r="R11" t="n">
-        <v>6923799</v>
+        <v>6923855</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1802,7 +1727,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1812,7 +1737,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,12 +1752,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1844,11 +1769,6 @@
       <c r="B12" t="n">
         <v>78947</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1951,54 +1871,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124901922</v>
+        <v>124900773</v>
       </c>
       <c r="B13" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599783</v>
+        <v>599801</v>
       </c>
       <c r="R13" t="n">
-        <v>6923858</v>
+        <v>6923797</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2030,7 +1941,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2040,7 +1951,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2067,57 +1978,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124900573</v>
+        <v>124898060</v>
       </c>
       <c r="B14" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599899</v>
+        <v>599916</v>
       </c>
       <c r="R14" t="n">
-        <v>6923798</v>
+        <v>6923847</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2146,7 +2048,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2156,7 +2058,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2171,27 +2073,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124898096</v>
+        <v>124898571</v>
       </c>
       <c r="B15" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,34 +2096,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599930</v>
+        <v>599904</v>
       </c>
       <c r="R15" t="n">
-        <v>6923840</v>
+        <v>6923812</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2258,7 +2160,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2268,7 +2170,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2283,27 +2190,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124900863</v>
+        <v>124898290</v>
       </c>
       <c r="B16" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2311,34 +2213,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599779</v>
+        <v>599911</v>
       </c>
       <c r="R16" t="n">
-        <v>6923783</v>
+        <v>6923836</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2370,7 +2277,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2380,7 +2287,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2395,27 +2307,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124900764</v>
+        <v>124900330</v>
       </c>
       <c r="B17" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91459</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2423,21 +2330,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2447,10 +2354,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599814</v>
+        <v>599899</v>
       </c>
       <c r="R17" t="n">
-        <v>6923824</v>
+        <v>6923798</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2482,7 +2389,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2492,7 +2399,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2507,62 +2414,57 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124898168</v>
+        <v>124901584</v>
       </c>
       <c r="B18" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599920</v>
+        <v>599899</v>
       </c>
       <c r="R18" t="n">
-        <v>6923834</v>
+        <v>6923798</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2594,7 +2496,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2604,7 +2506,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2619,27 +2521,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124898316</v>
+        <v>124899503</v>
       </c>
       <c r="B19" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91166</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2647,34 +2544,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599918</v>
+        <v>599912</v>
       </c>
       <c r="R19" t="n">
-        <v>6923822</v>
+        <v>6923800</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2706,7 +2603,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2716,7 +2613,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2731,28 +2628,23 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124900362</v>
+        <v>124901624</v>
       </c>
       <c r="B20" t="n">
         <v>98269</v>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>VU</t>
@@ -2778,24 +2670,24 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599864</v>
+        <v>599703</v>
       </c>
       <c r="R20" t="n">
-        <v>6923786</v>
+        <v>6923832</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2827,7 +2719,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2837,7 +2729,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2864,50 +2756,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124899503</v>
+        <v>124901922</v>
       </c>
       <c r="B21" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599912</v>
+        <v>599783</v>
       </c>
       <c r="R21" t="n">
-        <v>6923800</v>
+        <v>6923858</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2939,7 +2830,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2949,7 +2840,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2964,27 +2855,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124901889</v>
+        <v>124900786</v>
       </c>
       <c r="B22" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57632</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2992,34 +2878,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>599775</v>
+        <v>599791</v>
       </c>
       <c r="R22" t="n">
-        <v>6923855</v>
+        <v>6923786</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3051,7 +2942,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3061,7 +2952,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3076,62 +2967,81 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124901634</v>
+        <v>124902350</v>
       </c>
       <c r="B23" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>599734</v>
+        <v>599899</v>
       </c>
       <c r="R23" t="n">
-        <v>6923810</v>
+        <v>6923798</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3163,7 +3073,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3173,7 +3083,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett hona födosöker I en gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3188,66 +3103,62 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124899798</v>
+        <v>124900827</v>
       </c>
       <c r="B24" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57632</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>599883</v>
+        <v>599787</v>
       </c>
       <c r="R24" t="n">
-        <v>6923782</v>
+        <v>6923799</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3279,7 +3190,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3289,7 +3200,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3316,15 +3227,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124901880</v>
+        <v>124899839</v>
       </c>
       <c r="B25" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3332,34 +3238,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>599771</v>
+        <v>599893</v>
       </c>
       <c r="R25" t="n">
-        <v>6923841</v>
+        <v>6923773</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3391,7 +3302,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3401,12 +3312,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på asp</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3421,49 +3332,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124900465</v>
+        <v>124901634</v>
       </c>
       <c r="B26" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3473,10 +3379,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>599856</v>
+        <v>599734</v>
       </c>
       <c r="R26" t="n">
-        <v>6923803</v>
+        <v>6923810</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3508,7 +3414,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3518,7 +3424,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3545,50 +3451,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124900313</v>
+        <v>124901921</v>
       </c>
       <c r="B27" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>599854</v>
+        <v>599742</v>
       </c>
       <c r="R27" t="n">
-        <v>6923776</v>
+        <v>6923857</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3620,7 +3530,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3630,7 +3540,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3645,27 +3555,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124899616</v>
+        <v>124899564</v>
       </c>
       <c r="B28" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91459</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3673,21 +3578,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3697,10 +3602,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>599899</v>
+        <v>599910</v>
       </c>
       <c r="R28" t="n">
-        <v>6923765</v>
+        <v>6923786</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3732,7 +3637,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3742,7 +3647,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3769,37 +3674,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124898191</v>
+        <v>124901780</v>
       </c>
       <c r="B29" t="n">
-        <v>91833</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>898</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3809,10 +3709,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>599930</v>
+        <v>599756</v>
       </c>
       <c r="R29" t="n">
-        <v>6923840</v>
+        <v>6923823</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3844,7 +3744,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3854,7 +3754,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3886,11 +3786,6 @@
       <c r="B30" t="n">
         <v>98269</v>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>VU</t>
@@ -3997,15 +3892,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124900773</v>
+        <v>124900661</v>
       </c>
       <c r="B31" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4013,21 +3903,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4037,10 +3927,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>599801</v>
+        <v>599813</v>
       </c>
       <c r="R31" t="n">
-        <v>6923797</v>
+        <v>6923781</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4072,7 +3962,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4082,7 +3972,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4109,15 +3999,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124902509</v>
+        <v>124900663</v>
       </c>
       <c r="B32" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4125,39 +4010,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>599754</v>
+        <v>599824</v>
       </c>
       <c r="R32" t="n">
-        <v>6923921</v>
+        <v>6923802</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4189,7 +4069,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4199,12 +4079,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>18:29</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4219,28 +4094,23 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124901780</v>
+        <v>124900465</v>
       </c>
       <c r="B33" t="n">
         <v>80028</v>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D33" t="inlineStr">
         <is>
           <t>NT</t>
@@ -4271,10 +4141,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>599756</v>
+        <v>599856</v>
       </c>
       <c r="R33" t="n">
-        <v>6923823</v>
+        <v>6923803</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4306,7 +4176,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4316,7 +4186,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4343,50 +4213,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124899196</v>
+        <v>124900863</v>
       </c>
       <c r="B34" t="n">
-        <v>91617</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91166</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>599888</v>
+        <v>599779</v>
       </c>
       <c r="R34" t="n">
-        <v>6923798</v>
+        <v>6923783</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4418,7 +4283,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4428,7 +4293,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4455,15 +4320,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124898571</v>
+        <v>124899195</v>
       </c>
       <c r="B35" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91166</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4471,39 +4331,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>599904</v>
+        <v>599930</v>
       </c>
       <c r="R35" t="n">
-        <v>6923812</v>
+        <v>6923840</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4535,7 +4390,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4545,12 +4400,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:05</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4565,62 +4415,57 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124900661</v>
+        <v>124898191</v>
       </c>
       <c r="B36" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91833</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>898</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>599813</v>
+        <v>599930</v>
       </c>
       <c r="R36" t="n">
-        <v>6923781</v>
+        <v>6923840</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4652,7 +4497,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4662,7 +4507,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4677,27 +4522,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124900827</v>
+        <v>124897942</v>
       </c>
       <c r="B37" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57635</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4705,16 +4545,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4725,19 +4565,19 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>599787</v>
+        <v>599929</v>
       </c>
       <c r="R37" t="n">
-        <v>6923799</v>
+        <v>6923847</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4769,7 +4609,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4779,7 +4619,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4794,62 +4639,57 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124902691</v>
+        <v>124899341</v>
       </c>
       <c r="B38" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91131</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>599798</v>
+        <v>599908</v>
       </c>
       <c r="R38" t="n">
-        <v>6923975</v>
+        <v>6923811</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4881,7 +4721,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4891,7 +4731,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4906,66 +4746,57 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124902765</v>
+        <v>124902015</v>
       </c>
       <c r="B39" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91166</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>599800</v>
+        <v>599777</v>
       </c>
       <c r="R39" t="n">
-        <v>6923959</v>
+        <v>6923857</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4997,7 +4828,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5007,7 +4838,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5034,16 +4865,11 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124899564</v>
+        <v>124898316</v>
       </c>
       <c r="B40" t="n">
         <v>91459</v>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D40" t="inlineStr">
         <is>
           <t>NT</t>
@@ -5070,14 +4896,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>599910</v>
+        <v>599918</v>
       </c>
       <c r="R40" t="n">
-        <v>6923786</v>
+        <v>6923822</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5109,7 +4935,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5119,7 +4945,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5134,27 +4960,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124902839</v>
+        <v>124899421</v>
       </c>
       <c r="B41" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91166</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5162,34 +4983,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>599810</v>
+        <v>599899</v>
       </c>
       <c r="R41" t="n">
-        <v>6923980</v>
+        <v>6923798</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5221,7 +5042,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5231,7 +5052,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5246,28 +5067,23 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124902350</v>
+        <v>124902509</v>
       </c>
       <c r="B42" t="n">
         <v>57635</v>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D42" t="inlineStr">
         <is>
           <t>NT</t>
@@ -5291,41 +5107,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>599899</v>
+        <v>599754</v>
       </c>
       <c r="R42" t="n">
-        <v>6923798</v>
+        <v>6923921</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5357,7 +5154,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5367,12 +5164,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett hona födosöker I en gran.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5387,28 +5184,23 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124900294</v>
+        <v>124902765</v>
       </c>
       <c r="B43" t="n">
         <v>98269</v>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D43" t="inlineStr">
         <is>
           <t>VU</t>
@@ -5434,24 +5226,19 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>599864</v>
+        <v>599800</v>
       </c>
       <c r="R43" t="n">
-        <v>6923773</v>
+        <v>6923959</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5483,7 +5270,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5493,7 +5280,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5508,71 +5295,57 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124901921</v>
+        <v>124902691</v>
       </c>
       <c r="B44" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91184</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>599742</v>
+        <v>599798</v>
       </c>
       <c r="R44" t="n">
-        <v>6923857</v>
+        <v>6923975</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5604,7 +5377,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5614,7 +5387,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5629,66 +5402,57 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124900025</v>
+        <v>124898168</v>
       </c>
       <c r="B45" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91459</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>599878</v>
+        <v>599920</v>
       </c>
       <c r="R45" t="n">
-        <v>6923820</v>
+        <v>6923834</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5720,7 +5484,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5730,7 +5494,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5757,50 +5521,49 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124898054</v>
+        <v>124899798</v>
       </c>
       <c r="B46" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>599930</v>
+        <v>599883</v>
       </c>
       <c r="R46" t="n">
-        <v>6923840</v>
+        <v>6923782</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5832,7 +5595,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5842,12 +5605,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5862,62 +5620,57 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124898995</v>
+        <v>124900313</v>
       </c>
       <c r="B47" t="n">
-        <v>97147</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>599930</v>
+        <v>599854</v>
       </c>
       <c r="R47" t="n">
-        <v>6923840</v>
+        <v>6923776</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5949,7 +5702,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5959,7 +5712,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5974,27 +5727,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124900330</v>
+        <v>124900226</v>
       </c>
       <c r="B48" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6002,34 +5750,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>599899</v>
+        <v>599882</v>
       </c>
       <c r="R48" t="n">
-        <v>6923798</v>
+        <v>6923778</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6061,7 +5814,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6071,7 +5824,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Över 20 apothecier</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6086,59 +5844,54 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124899421</v>
+        <v>124899196</v>
       </c>
       <c r="B49" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91617</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>599899</v>
+        <v>599888</v>
       </c>
       <c r="R49" t="n">
         <v>6923798</v>
@@ -6173,7 +5926,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6183,7 +5936,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6198,65 +5951,64 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124898060</v>
+        <v>124900025</v>
       </c>
       <c r="B50" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>599916</v>
+        <v>599878</v>
       </c>
       <c r="R50" t="n">
-        <v>6923847</v>
+        <v>6923820</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6285,7 +6037,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6295,7 +6047,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6322,43 +6074,42 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124899839</v>
+        <v>124900362</v>
       </c>
       <c r="B51" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6367,10 +6118,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>599893</v>
+        <v>599864</v>
       </c>
       <c r="R51" t="n">
-        <v>6923773</v>
+        <v>6923786</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6402,7 +6153,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6412,12 +6163,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:35</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6444,50 +6190,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125686610</v>
+        <v>125685122</v>
       </c>
       <c r="B52" t="n">
-        <v>91177</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>599815</v>
+        <v>600013</v>
       </c>
       <c r="R52" t="n">
-        <v>6923786</v>
+        <v>6923741</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6546,37 +6287,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125685582</v>
+        <v>125685127</v>
       </c>
       <c r="B53" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91185</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6586,10 +6322,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>599906</v>
+        <v>600027</v>
       </c>
       <c r="R53" t="n">
-        <v>6923816</v>
+        <v>6923772</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6648,50 +6384,49 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125685122</v>
+        <v>125685866</v>
       </c>
       <c r="B54" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>600013</v>
+        <v>599803</v>
       </c>
       <c r="R54" t="n">
-        <v>6923741</v>
+        <v>6923868</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6750,54 +6485,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125685866</v>
+        <v>125685582</v>
       </c>
       <c r="B55" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>599803</v>
+        <v>599906</v>
       </c>
       <c r="R55" t="n">
-        <v>6923868</v>
+        <v>6923816</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6859,12 +6585,7 @@
         <v>125685331</v>
       </c>
       <c r="B56" t="n">
-        <v>88512</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88626</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6958,37 +6679,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125685127</v>
+        <v>125685402</v>
       </c>
       <c r="B57" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91513</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6998,10 +6714,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>600027</v>
+        <v>599900</v>
       </c>
       <c r="R57" t="n">
-        <v>6923772</v>
+        <v>6923788</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -7060,50 +6776,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125685402</v>
+        <v>125686610</v>
       </c>
       <c r="B58" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91231</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>1205</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>599900</v>
+        <v>599815</v>
       </c>
       <c r="R58" t="n">
-        <v>6923788</v>
+        <v>6923786</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -7165,12 +6876,7 @@
         <v>125686642</v>
       </c>
       <c r="B59" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -6384,49 +6384,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125685866</v>
+        <v>125685582</v>
       </c>
       <c r="B54" t="n">
-        <v>98324</v>
+        <v>80070</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>599803</v>
+        <v>599906</v>
       </c>
       <c r="R54" t="n">
-        <v>6923868</v>
+        <v>6923816</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6485,45 +6481,49 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125685582</v>
+        <v>125685866</v>
       </c>
       <c r="B55" t="n">
-        <v>80070</v>
+        <v>98324</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>599906</v>
+        <v>599803</v>
       </c>
       <c r="R55" t="n">
-        <v>6923816</v>
+        <v>6923868</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6776,42 +6776,46 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125686610</v>
+        <v>125686642</v>
       </c>
       <c r="B58" t="n">
-        <v>91231</v>
+        <v>98324</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1205</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>599815</v>
+        <v>599816</v>
       </c>
       <c r="R58" t="n">
         <v>6923786</v>
@@ -6873,46 +6877,42 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125686642</v>
+        <v>125686610</v>
       </c>
       <c r="B59" t="n">
-        <v>98324</v>
+        <v>91231</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>599816</v>
+        <v>599815</v>
       </c>
       <c r="R59" t="n">
         <v>6923786</v>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -6193,7 +6193,7 @@
         <v>125685122</v>
       </c>
       <c r="B52" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6287,32 +6287,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125685127</v>
+        <v>125685582</v>
       </c>
       <c r="B53" t="n">
-        <v>91185</v>
+        <v>80070</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6322,10 +6322,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>600027</v>
+        <v>599906</v>
       </c>
       <c r="R53" t="n">
-        <v>6923772</v>
+        <v>6923816</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6384,32 +6384,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125685582</v>
+        <v>125685127</v>
       </c>
       <c r="B54" t="n">
-        <v>80070</v>
+        <v>91192</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6419,10 +6419,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>599906</v>
+        <v>600027</v>
       </c>
       <c r="R54" t="n">
-        <v>6923816</v>
+        <v>6923772</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6484,7 +6484,7 @@
         <v>125685866</v>
       </c>
       <c r="B55" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6582,10 +6582,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125685331</v>
+        <v>125685402</v>
       </c>
       <c r="B56" t="n">
-        <v>88626</v>
+        <v>91520</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6593,21 +6593,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6617,10 +6617,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>599910</v>
+        <v>599900</v>
       </c>
       <c r="R56" t="n">
-        <v>6923817</v>
+        <v>6923788</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6679,10 +6679,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125685402</v>
+        <v>125685331</v>
       </c>
       <c r="B57" t="n">
-        <v>91513</v>
+        <v>88633</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6690,21 +6690,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6714,10 +6714,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>599900</v>
+        <v>599910</v>
       </c>
       <c r="R57" t="n">
-        <v>6923788</v>
+        <v>6923817</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6776,46 +6776,42 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125686642</v>
+        <v>125686610</v>
       </c>
       <c r="B58" t="n">
-        <v>98324</v>
+        <v>91238</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>599816</v>
+        <v>599815</v>
       </c>
       <c r="R58" t="n">
         <v>6923786</v>
@@ -6877,42 +6873,46 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125686610</v>
+        <v>125686642</v>
       </c>
       <c r="B59" t="n">
-        <v>91231</v>
+        <v>98331</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1205</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>599815</v>
+        <v>599816</v>
       </c>
       <c r="R59" t="n">
         <v>6923786</v>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -6776,42 +6776,46 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125686610</v>
+        <v>125686642</v>
       </c>
       <c r="B58" t="n">
-        <v>91238</v>
+        <v>98331</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1205</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>599815</v>
+        <v>599816</v>
       </c>
       <c r="R58" t="n">
         <v>6923786</v>
@@ -6873,46 +6877,42 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125686642</v>
+        <v>125686610</v>
       </c>
       <c r="B59" t="n">
-        <v>98331</v>
+        <v>91238</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>599816</v>
+        <v>599815</v>
       </c>
       <c r="R59" t="n">
         <v>6923786</v>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -6193,7 +6193,7 @@
         <v>125685122</v>
       </c>
       <c r="B52" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         <v>125685582</v>
       </c>
       <c r="B53" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6384,45 +6384,49 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125685127</v>
+        <v>125685866</v>
       </c>
       <c r="B54" t="n">
-        <v>91192</v>
+        <v>98334</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>600027</v>
+        <v>599803</v>
       </c>
       <c r="R54" t="n">
-        <v>6923772</v>
+        <v>6923868</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6481,49 +6485,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125685866</v>
+        <v>125685127</v>
       </c>
       <c r="B55" t="n">
-        <v>98331</v>
+        <v>91193</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>599803</v>
+        <v>600027</v>
       </c>
       <c r="R55" t="n">
-        <v>6923868</v>
+        <v>6923772</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6585,7 +6585,7 @@
         <v>125685402</v>
       </c>
       <c r="B56" t="n">
-        <v>91520</v>
+        <v>91524</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>125685331</v>
       </c>
       <c r="B57" t="n">
-        <v>88633</v>
+        <v>88637</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6776,46 +6776,42 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125686642</v>
+        <v>125686610</v>
       </c>
       <c r="B58" t="n">
-        <v>98331</v>
+        <v>91239</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>599816</v>
+        <v>599815</v>
       </c>
       <c r="R58" t="n">
         <v>6923786</v>
@@ -6877,42 +6873,46 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125686610</v>
+        <v>125686642</v>
       </c>
       <c r="B59" t="n">
-        <v>91238</v>
+        <v>98334</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1205</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>599815</v>
+        <v>599816</v>
       </c>
       <c r="R59" t="n">
         <v>6923786</v>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -6287,32 +6287,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125685582</v>
+        <v>125685127</v>
       </c>
       <c r="B53" t="n">
-        <v>80071</v>
+        <v>91193</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6322,10 +6322,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>599906</v>
+        <v>600027</v>
       </c>
       <c r="R53" t="n">
-        <v>6923816</v>
+        <v>6923772</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6384,49 +6384,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125685866</v>
+        <v>125685582</v>
       </c>
       <c r="B54" t="n">
-        <v>98334</v>
+        <v>80071</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>599803</v>
+        <v>599906</v>
       </c>
       <c r="R54" t="n">
-        <v>6923868</v>
+        <v>6923816</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6485,45 +6481,49 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125685127</v>
+        <v>125685866</v>
       </c>
       <c r="B55" t="n">
-        <v>91193</v>
+        <v>98334</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>600027</v>
+        <v>599803</v>
       </c>
       <c r="R55" t="n">
-        <v>6923772</v>
+        <v>6923868</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -6193,7 +6193,7 @@
         <v>125685122</v>
       </c>
       <c r="B52" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6287,32 +6287,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125685127</v>
+        <v>125685582</v>
       </c>
       <c r="B53" t="n">
-        <v>91193</v>
+        <v>80075</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6322,10 +6322,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>600027</v>
+        <v>599906</v>
       </c>
       <c r="R53" t="n">
-        <v>6923772</v>
+        <v>6923816</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6384,45 +6384,49 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125685582</v>
+        <v>125685866</v>
       </c>
       <c r="B54" t="n">
-        <v>80071</v>
+        <v>98338</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>599906</v>
+        <v>599803</v>
       </c>
       <c r="R54" t="n">
-        <v>6923816</v>
+        <v>6923868</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6481,49 +6485,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125685866</v>
+        <v>125685127</v>
       </c>
       <c r="B55" t="n">
-        <v>98334</v>
+        <v>91197</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>599803</v>
+        <v>600027</v>
       </c>
       <c r="R55" t="n">
-        <v>6923868</v>
+        <v>6923772</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6585,7 +6585,7 @@
         <v>125685402</v>
       </c>
       <c r="B56" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>125685331</v>
       </c>
       <c r="B57" t="n">
-        <v>88637</v>
+        <v>88641</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>125686610</v>
       </c>
       <c r="B58" t="n">
-        <v>91239</v>
+        <v>91243</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>125686642</v>
       </c>
       <c r="B59" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -6384,49 +6384,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125685866</v>
+        <v>125685127</v>
       </c>
       <c r="B54" t="n">
-        <v>98338</v>
+        <v>91197</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>599803</v>
+        <v>600027</v>
       </c>
       <c r="R54" t="n">
-        <v>6923868</v>
+        <v>6923772</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6485,45 +6481,49 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125685127</v>
+        <v>125685866</v>
       </c>
       <c r="B55" t="n">
-        <v>91197</v>
+        <v>98338</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>600027</v>
+        <v>599803</v>
       </c>
       <c r="R55" t="n">
-        <v>6923772</v>
+        <v>6923868</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -6287,45 +6287,49 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125685582</v>
+        <v>125685866</v>
       </c>
       <c r="B53" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>599906</v>
+        <v>599803</v>
       </c>
       <c r="R53" t="n">
-        <v>6923816</v>
+        <v>6923868</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6481,49 +6485,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125685866</v>
+        <v>125685582</v>
       </c>
       <c r="B55" t="n">
-        <v>98338</v>
+        <v>80075</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>599803</v>
+        <v>599906</v>
       </c>
       <c r="R55" t="n">
-        <v>6923868</v>
+        <v>6923816</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6876,7 +6876,7 @@
         <v>125686642</v>
       </c>
       <c r="B59" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -6287,49 +6287,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125685866</v>
+        <v>125685127</v>
       </c>
       <c r="B53" t="n">
-        <v>98339</v>
+        <v>91197</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>599803</v>
+        <v>600027</v>
       </c>
       <c r="R53" t="n">
-        <v>6923868</v>
+        <v>6923772</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6388,32 +6384,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125685127</v>
+        <v>125685582</v>
       </c>
       <c r="B54" t="n">
-        <v>91197</v>
+        <v>80075</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6423,10 +6419,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>600027</v>
+        <v>599906</v>
       </c>
       <c r="R54" t="n">
-        <v>6923772</v>
+        <v>6923816</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6485,45 +6481,49 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125685582</v>
+        <v>125685866</v>
       </c>
       <c r="B55" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>599906</v>
+        <v>599803</v>
       </c>
       <c r="R55" t="n">
-        <v>6923816</v>
+        <v>6923868</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -6193,7 +6193,7 @@
         <v>125685122</v>
       </c>
       <c r="B52" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6287,32 +6287,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125685127</v>
+        <v>125685582</v>
       </c>
       <c r="B53" t="n">
-        <v>91197</v>
+        <v>80076</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6322,10 +6322,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>600027</v>
+        <v>599906</v>
       </c>
       <c r="R53" t="n">
-        <v>6923772</v>
+        <v>6923816</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6384,32 +6384,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125685582</v>
+        <v>125685127</v>
       </c>
       <c r="B54" t="n">
-        <v>80075</v>
+        <v>91199</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6419,10 +6419,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>599906</v>
+        <v>600027</v>
       </c>
       <c r="R54" t="n">
-        <v>6923816</v>
+        <v>6923772</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6484,7 +6484,7 @@
         <v>125685866</v>
       </c>
       <c r="B55" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>125685402</v>
       </c>
       <c r="B56" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>125685331</v>
       </c>
       <c r="B57" t="n">
-        <v>88641</v>
+        <v>88643</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>125686610</v>
       </c>
       <c r="B58" t="n">
-        <v>91243</v>
+        <v>91245</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>125686642</v>
       </c>
       <c r="B59" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -6193,7 +6193,7 @@
         <v>125685122</v>
       </c>
       <c r="B52" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6287,45 +6287,49 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125685582</v>
+        <v>125685866</v>
       </c>
       <c r="B53" t="n">
-        <v>80076</v>
+        <v>98343</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>599906</v>
+        <v>599803</v>
       </c>
       <c r="R53" t="n">
-        <v>6923816</v>
+        <v>6923868</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6384,32 +6388,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125685127</v>
+        <v>125685582</v>
       </c>
       <c r="B54" t="n">
-        <v>91199</v>
+        <v>80076</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6419,10 +6423,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>600027</v>
+        <v>599906</v>
       </c>
       <c r="R54" t="n">
-        <v>6923772</v>
+        <v>6923816</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6481,49 +6485,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125685866</v>
+        <v>125685127</v>
       </c>
       <c r="B55" t="n">
-        <v>98341</v>
+        <v>91201</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>599803</v>
+        <v>600027</v>
       </c>
       <c r="R55" t="n">
-        <v>6923868</v>
+        <v>6923772</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6585,7 +6585,7 @@
         <v>125685402</v>
       </c>
       <c r="B56" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>125685331</v>
       </c>
       <c r="B57" t="n">
-        <v>88643</v>
+        <v>88645</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>125686610</v>
       </c>
       <c r="B58" t="n">
-        <v>91245</v>
+        <v>91247</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>125686642</v>
       </c>
       <c r="B59" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -6287,49 +6287,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125685866</v>
+        <v>125685582</v>
       </c>
       <c r="B53" t="n">
-        <v>98343</v>
+        <v>80076</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>599803</v>
+        <v>599906</v>
       </c>
       <c r="R53" t="n">
-        <v>6923868</v>
+        <v>6923816</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6388,32 +6384,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125685582</v>
+        <v>125685127</v>
       </c>
       <c r="B54" t="n">
-        <v>80076</v>
+        <v>91201</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6423,10 +6419,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>599906</v>
+        <v>600027</v>
       </c>
       <c r="R54" t="n">
-        <v>6923816</v>
+        <v>6923772</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6485,45 +6481,49 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125685127</v>
+        <v>125685866</v>
       </c>
       <c r="B55" t="n">
-        <v>91201</v>
+        <v>98343</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>600027</v>
+        <v>599803</v>
       </c>
       <c r="R55" t="n">
-        <v>6923772</v>
+        <v>6923868</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -6193,7 +6193,7 @@
         <v>125685122</v>
       </c>
       <c r="B52" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>125685127</v>
       </c>
       <c r="B54" t="n">
-        <v>91201</v>
+        <v>91203</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>125685866</v>
       </c>
       <c r="B55" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>125685402</v>
       </c>
       <c r="B56" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>125685331</v>
       </c>
       <c r="B57" t="n">
-        <v>88645</v>
+        <v>88647</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6776,42 +6776,46 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125686610</v>
+        <v>125686642</v>
       </c>
       <c r="B58" t="n">
-        <v>91247</v>
+        <v>98345</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1205</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>599815</v>
+        <v>599816</v>
       </c>
       <c r="R58" t="n">
         <v>6923786</v>
@@ -6873,46 +6877,42 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125686642</v>
+        <v>125686610</v>
       </c>
       <c r="B59" t="n">
-        <v>98343</v>
+        <v>91249</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>599816</v>
+        <v>599815</v>
       </c>
       <c r="R59" t="n">
         <v>6923786</v>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -6776,46 +6776,42 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125686642</v>
+        <v>125686610</v>
       </c>
       <c r="B58" t="n">
-        <v>98345</v>
+        <v>91249</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>599816</v>
+        <v>599815</v>
       </c>
       <c r="R58" t="n">
         <v>6923786</v>
@@ -6877,42 +6873,46 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125686610</v>
+        <v>125686642</v>
       </c>
       <c r="B59" t="n">
-        <v>91249</v>
+        <v>98345</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1205</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>599815</v>
+        <v>599816</v>
       </c>
       <c r="R59" t="n">
         <v>6923786</v>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -6193,7 +6193,7 @@
         <v>125685122</v>
       </c>
       <c r="B52" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6287,45 +6287,49 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125685582</v>
+        <v>125685866</v>
       </c>
       <c r="B53" t="n">
-        <v>80076</v>
+        <v>98349</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>599906</v>
+        <v>599803</v>
       </c>
       <c r="R53" t="n">
-        <v>6923816</v>
+        <v>6923868</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6384,32 +6388,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125685127</v>
+        <v>125685582</v>
       </c>
       <c r="B54" t="n">
-        <v>91203</v>
+        <v>80080</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6419,10 +6423,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>600027</v>
+        <v>599906</v>
       </c>
       <c r="R54" t="n">
-        <v>6923772</v>
+        <v>6923816</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6481,49 +6485,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125685866</v>
+        <v>125685127</v>
       </c>
       <c r="B55" t="n">
-        <v>98345</v>
+        <v>91207</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>599803</v>
+        <v>600027</v>
       </c>
       <c r="R55" t="n">
-        <v>6923868</v>
+        <v>6923772</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6585,7 +6585,7 @@
         <v>125685402</v>
       </c>
       <c r="B56" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>125685331</v>
       </c>
       <c r="B57" t="n">
-        <v>88647</v>
+        <v>88651</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>125686610</v>
       </c>
       <c r="B58" t="n">
-        <v>91249</v>
+        <v>91253</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>125686642</v>
       </c>
       <c r="B59" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -6287,49 +6287,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125685866</v>
+        <v>125685582</v>
       </c>
       <c r="B53" t="n">
-        <v>98349</v>
+        <v>80080</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>599803</v>
+        <v>599906</v>
       </c>
       <c r="R53" t="n">
-        <v>6923868</v>
+        <v>6923816</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6388,32 +6384,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125685582</v>
+        <v>125685127</v>
       </c>
       <c r="B54" t="n">
-        <v>80080</v>
+        <v>91207</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6423,10 +6419,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>599906</v>
+        <v>600027</v>
       </c>
       <c r="R54" t="n">
-        <v>6923816</v>
+        <v>6923772</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6485,45 +6481,49 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125685127</v>
+        <v>125685866</v>
       </c>
       <c r="B55" t="n">
-        <v>91207</v>
+        <v>98352</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>600027</v>
+        <v>599803</v>
       </c>
       <c r="R55" t="n">
-        <v>6923772</v>
+        <v>6923868</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6876,7 +6876,7 @@
         <v>125686642</v>
       </c>
       <c r="B59" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -6977,7 +6977,7 @@
         <v>126717319</v>
       </c>
       <c r="B60" t="n">
-        <v>91541</v>
+        <v>91615</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>126717749</v>
       </c>
       <c r="B61" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -6977,7 +6977,7 @@
         <v>126717319</v>
       </c>
       <c r="B60" t="n">
-        <v>91615</v>
+        <v>91621</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>126717749</v>
       </c>
       <c r="B61" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -6977,7 +6977,7 @@
         <v>126717319</v>
       </c>
       <c r="B60" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -2870,7 +2870,7 @@
         <v>124900786</v>
       </c>
       <c r="B22" t="n">
-        <v>57632</v>
+        <v>57658</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>124900827</v>
       </c>
       <c r="B24" t="n">
-        <v>57632</v>
+        <v>57658</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -2870,7 +2870,7 @@
         <v>124900786</v>
       </c>
       <c r="B22" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>124900827</v>
       </c>
       <c r="B24" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AY66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7272,6 +7272,374 @@
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>127945802</v>
+      </c>
+      <c r="B63" t="n">
+        <v>80083</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Backtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>599734</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6923810</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>127946712</v>
+      </c>
+      <c r="B64" t="n">
+        <v>88741</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>510</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Backtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>599788</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6923908</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>127944705</v>
+      </c>
+      <c r="B65" t="n">
+        <v>80083</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Söderlundsintaget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>599970</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6923843</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>127939731</v>
+      </c>
+      <c r="B66" t="n">
+        <v>97333</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Söderlundsintaget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>599970</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6923843</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AY66" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -2870,7 +2870,7 @@
         <v>124900786</v>
       </c>
       <c r="B22" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>124900827</v>
       </c>
       <c r="B24" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>127945802</v>
       </c>
       <c r="B63" t="n">
-        <v>80083</v>
+        <v>80086</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>127946712</v>
       </c>
       <c r="B64" t="n">
-        <v>88741</v>
+        <v>88744</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7471,7 +7471,7 @@
         <v>127944705</v>
       </c>
       <c r="B65" t="n">
-        <v>80083</v>
+        <v>80086</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7551,6 +7551,16 @@
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Kevin Huss</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Kevin Huss</t>
+        </is>
+      </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
@@ -7558,7 +7568,7 @@
         <v>127939731</v>
       </c>
       <c r="B66" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7638,6 +7648,16 @@
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Kevin Huss</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Kevin Huss</t>
+        </is>
+      </c>
       <c r="AY66" t="inlineStr"/>
     </row>
   </sheetData>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -2870,7 +2870,7 @@
         <v>124900786</v>
       </c>
       <c r="B22" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>124900827</v>
       </c>
       <c r="B24" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>127945802</v>
       </c>
       <c r="B63" t="n">
-        <v>80086</v>
+        <v>80092</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>127946712</v>
       </c>
       <c r="B64" t="n">
-        <v>88744</v>
+        <v>88752</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7471,7 +7471,7 @@
         <v>127944705</v>
       </c>
       <c r="B65" t="n">
-        <v>80086</v>
+        <v>80092</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>127939731</v>
       </c>
       <c r="B66" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -7374,7 +7374,7 @@
         <v>127946712</v>
       </c>
       <c r="B64" t="n">
-        <v>88752</v>
+        <v>88753</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>127939731</v>
       </c>
       <c r="B66" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -7374,7 +7374,7 @@
         <v>127946712</v>
       </c>
       <c r="B64" t="n">
-        <v>88753</v>
+        <v>88754</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>127939731</v>
       </c>
       <c r="B66" t="n">
-        <v>97345</v>
+        <v>97346</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -7374,7 +7374,7 @@
         <v>127946712</v>
       </c>
       <c r="B64" t="n">
-        <v>88754</v>
+        <v>88755</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>127939731</v>
       </c>
       <c r="B66" t="n">
-        <v>97346</v>
+        <v>97347</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -2870,7 +2870,7 @@
         <v>124900786</v>
       </c>
       <c r="B22" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>124900827</v>
       </c>
       <c r="B24" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>127945802</v>
       </c>
       <c r="B63" t="n">
-        <v>80092</v>
+        <v>80095</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>127946712</v>
       </c>
       <c r="B64" t="n">
-        <v>88755</v>
+        <v>88761</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7471,7 +7471,7 @@
         <v>127944705</v>
       </c>
       <c r="B65" t="n">
-        <v>80092</v>
+        <v>80095</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>127939731</v>
       </c>
       <c r="B66" t="n">
-        <v>97347</v>
+        <v>97355</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -2870,7 +2870,7 @@
         <v>124900786</v>
       </c>
       <c r="B22" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>124900827</v>
       </c>
       <c r="B24" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>127945802</v>
       </c>
       <c r="B63" t="n">
-        <v>80095</v>
+        <v>80148</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>127946712</v>
       </c>
       <c r="B64" t="n">
-        <v>88761</v>
+        <v>88853</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7471,7 +7471,7 @@
         <v>127944705</v>
       </c>
       <c r="B65" t="n">
-        <v>80095</v>
+        <v>80148</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>127939731</v>
       </c>
       <c r="B66" t="n">
-        <v>97355</v>
+        <v>97448</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -7277,7 +7277,7 @@
         <v>127945802</v>
       </c>
       <c r="B63" t="n">
-        <v>80148</v>
+        <v>80152</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>127946712</v>
       </c>
       <c r="B64" t="n">
-        <v>88853</v>
+        <v>88865</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7471,7 +7471,7 @@
         <v>127944705</v>
       </c>
       <c r="B65" t="n">
-        <v>80148</v>
+        <v>80152</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>127939731</v>
       </c>
       <c r="B66" t="n">
-        <v>97448</v>
+        <v>97460</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -2088,7 +2088,7 @@
         <v>124898571</v>
       </c>
       <c r="B15" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>124898290</v>
       </c>
       <c r="B16" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>124899839</v>
       </c>
       <c r="B25" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>124897942</v>
       </c>
       <c r="B37" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>124902509</v>
       </c>
       <c r="B42" t="n">
-        <v>57635</v>
+        <v>57736</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -2088,7 +2088,7 @@
         <v>124898571</v>
       </c>
       <c r="B15" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>124898290</v>
       </c>
       <c r="B16" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>124899839</v>
       </c>
       <c r="B25" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>124897942</v>
       </c>
       <c r="B37" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>124902509</v>
       </c>
       <c r="B42" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -6977,7 +6977,7 @@
         <v>126717319</v>
       </c>
       <c r="B60" t="n">
-        <v>91622</v>
+        <v>91615</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>126717749</v>
       </c>
       <c r="B61" t="n">
-        <v>80146</v>
+        <v>80143</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY66"/>
+  <dimension ref="A1:AY67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124901679</v>
+        <v>125685331</v>
       </c>
       <c r="B2" t="n">
-        <v>80028</v>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599728</v>
+        <v>599910</v>
       </c>
       <c r="R2" t="n">
-        <v>6923812</v>
+        <v>6923817</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>17:50</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>17:50</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124898054</v>
+        <v>127946712</v>
       </c>
       <c r="B3" t="n">
-        <v>78947</v>
+        <v>89292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599930</v>
+        <v>599788</v>
       </c>
       <c r="R3" t="n">
-        <v>6923840</v>
+        <v>6923908</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,27 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:46</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124899616</v>
+        <v>124898168</v>
       </c>
       <c r="B4" t="n">
-        <v>78947</v>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599899</v>
+        <v>599920</v>
       </c>
       <c r="R4" t="n">
-        <v>6923765</v>
+        <v>6923834</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +939,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +949,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,22 +964,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124901880</v>
+        <v>124898316</v>
       </c>
       <c r="B5" t="n">
-        <v>80028</v>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,34 +987,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599771</v>
+        <v>599918</v>
       </c>
       <c r="R5" t="n">
-        <v>6923841</v>
+        <v>6923822</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1046,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,12 +1056,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:58</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt med lunglav på asp</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124902839</v>
+        <v>124899564</v>
       </c>
       <c r="B6" t="n">
-        <v>78947</v>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,34 +1094,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599810</v>
+        <v>599910</v>
       </c>
       <c r="R6" t="n">
-        <v>6923980</v>
+        <v>6923786</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1153,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1163,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,66 +1178,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124900294</v>
+        <v>124900330</v>
       </c>
       <c r="B7" t="n">
-        <v>98269</v>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599864</v>
+        <v>599899</v>
       </c>
       <c r="R7" t="n">
-        <v>6923773</v>
+        <v>6923798</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,7 +1260,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1270,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,60 +1285,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124898995</v>
+        <v>125685402</v>
       </c>
       <c r="B8" t="n">
-        <v>97147</v>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599930</v>
+        <v>599900</v>
       </c>
       <c r="R8" t="n">
-        <v>6923840</v>
+        <v>6923788</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1401,22 +1362,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>16:17</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>16:17</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1431,22 +1382,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124899644</v>
+        <v>126717319</v>
       </c>
       <c r="B9" t="n">
-        <v>78947</v>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,34 +1405,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599898</v>
+        <v>599876</v>
       </c>
       <c r="R9" t="n">
-        <v>6923799</v>
+        <v>6923905</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1508,22 +1459,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>16:36</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>16:36</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1538,44 +1479,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124900764</v>
+        <v>124898191</v>
       </c>
       <c r="B10" t="n">
-        <v>80028</v>
+        <v>92605</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>898</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1585,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599814</v>
+        <v>599930</v>
       </c>
       <c r="R10" t="n">
-        <v>6923824</v>
+        <v>6923840</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1620,7 +1561,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1630,7 +1571,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1657,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124901889</v>
+        <v>124898096</v>
       </c>
       <c r="B11" t="n">
-        <v>80028</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1692,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599775</v>
+        <v>599930</v>
       </c>
       <c r="R11" t="n">
-        <v>6923855</v>
+        <v>6923840</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1727,7 +1668,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1737,7 +1678,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1764,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124900018</v>
+        <v>124899421</v>
       </c>
       <c r="B12" t="n">
-        <v>78947</v>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1775,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1799,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599883</v>
+        <v>599899</v>
       </c>
       <c r="R12" t="n">
-        <v>6923768</v>
+        <v>6923798</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1834,7 +1775,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1844,7 +1785,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1859,22 +1800,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124900773</v>
+        <v>124899503</v>
       </c>
       <c r="B13" t="n">
-        <v>78947</v>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,34 +1823,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599801</v>
+        <v>599912</v>
       </c>
       <c r="R13" t="n">
-        <v>6923797</v>
+        <v>6923800</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1941,7 +1882,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1951,7 +1892,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1966,22 +1907,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124898060</v>
+        <v>124900863</v>
       </c>
       <c r="B14" t="n">
-        <v>78947</v>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,37 +1930,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599916</v>
+        <v>599779</v>
       </c>
       <c r="R14" t="n">
-        <v>6923847</v>
+        <v>6923783</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2048,7 +1989,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2058,7 +1999,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2085,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124898571</v>
+        <v>124902015</v>
       </c>
       <c r="B15" t="n">
-        <v>57741</v>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2096,39 +2037,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599904</v>
+        <v>599777</v>
       </c>
       <c r="R15" t="n">
-        <v>6923812</v>
+        <v>6923857</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2160,7 +2096,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2170,12 +2106,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:05</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2190,22 +2121,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124898290</v>
+        <v>125685122</v>
       </c>
       <c r="B16" t="n">
-        <v>57741</v>
+        <v>91909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,42 +2144,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599911</v>
+        <v>600013</v>
       </c>
       <c r="R16" t="n">
-        <v>6923836</v>
+        <v>6923741</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2272,27 +2198,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:55</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2307,60 +2218,60 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124900330</v>
+        <v>125686610</v>
       </c>
       <c r="B17" t="n">
-        <v>91459</v>
+        <v>91920</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>1205</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599899</v>
+        <v>599815</v>
       </c>
       <c r="R17" t="n">
-        <v>6923798</v>
+        <v>6923786</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2384,22 +2295,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>16:49</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>16:49</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2414,54 +2315,54 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124901584</v>
+        <v>124899196</v>
       </c>
       <c r="B18" t="n">
-        <v>98269</v>
+        <v>92369</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599899</v>
+        <v>599888</v>
       </c>
       <c r="R18" t="n">
         <v>6923798</v>
@@ -2496,7 +2397,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2506,7 +2407,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2521,44 +2422,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124899503</v>
+        <v>124899341</v>
       </c>
       <c r="B19" t="n">
-        <v>91166</v>
+        <v>91872</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2568,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599912</v>
+        <v>599908</v>
       </c>
       <c r="R19" t="n">
-        <v>6923800</v>
+        <v>6923811</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2603,7 +2504,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2613,7 +2514,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2640,57 +2541,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124901624</v>
+        <v>125685127</v>
       </c>
       <c r="B20" t="n">
-        <v>98269</v>
+        <v>91872</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599703</v>
+        <v>600027</v>
       </c>
       <c r="R20" t="n">
-        <v>6923832</v>
+        <v>6923772</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2714,22 +2606,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>17:43</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>17:43</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2744,22 +2626,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124901922</v>
+        <v>124898054</v>
       </c>
       <c r="B21" t="n">
-        <v>98269</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2767,38 +2649,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599783</v>
+        <v>599930</v>
       </c>
       <c r="R21" t="n">
-        <v>6923858</v>
+        <v>6923840</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2830,7 +2708,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2840,7 +2718,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2855,65 +2738,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124900786</v>
+        <v>124898060</v>
       </c>
       <c r="B22" t="n">
-        <v>57681</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>599791</v>
+        <v>599916</v>
       </c>
       <c r="R22" t="n">
-        <v>6923786</v>
+        <v>6923847</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2942,7 +2820,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2952,7 +2830,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2967,71 +2845,47 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124902350</v>
+        <v>124899616</v>
       </c>
       <c r="B23" t="n">
-        <v>57635</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Backtjärnen, Mpd</t>
@@ -3041,7 +2895,7 @@
         <v>599899</v>
       </c>
       <c r="R23" t="n">
-        <v>6923798</v>
+        <v>6923765</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3073,7 +2927,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3083,12 +2937,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:17</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett hona födosöker I en gran.</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3103,59 +2952,54 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124900827</v>
+        <v>124899644</v>
       </c>
       <c r="B24" t="n">
-        <v>57681</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>599787</v>
+        <v>599898</v>
       </c>
       <c r="R24" t="n">
         <v>6923799</v>
@@ -3190,7 +3034,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3200,7 +3044,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3227,50 +3071,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124899839</v>
+        <v>124900018</v>
       </c>
       <c r="B25" t="n">
-        <v>57741</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>599893</v>
+        <v>599883</v>
       </c>
       <c r="R25" t="n">
-        <v>6923773</v>
+        <v>6923768</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3302,7 +3141,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3312,12 +3151,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:35</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3332,22 +3166,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124901634</v>
+        <v>124900773</v>
       </c>
       <c r="B26" t="n">
-        <v>98269</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3355,34 +3189,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>599734</v>
+        <v>599801</v>
       </c>
       <c r="R26" t="n">
-        <v>6923810</v>
+        <v>6923797</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3414,7 +3248,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3424,7 +3258,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3439,22 +3273,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124901921</v>
+        <v>124902839</v>
       </c>
       <c r="B27" t="n">
-        <v>98269</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3462,43 +3296,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>599742</v>
+        <v>599810</v>
       </c>
       <c r="R27" t="n">
-        <v>6923857</v>
+        <v>6923980</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3530,7 +3355,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3540,7 +3365,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3555,22 +3380,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124899564</v>
+        <v>124900226</v>
       </c>
       <c r="B28" t="n">
-        <v>91459</v>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3578,34 +3403,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>599910</v>
+        <v>599882</v>
       </c>
       <c r="R28" t="n">
-        <v>6923786</v>
+        <v>6923778</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3637,7 +3467,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3647,7 +3477,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Över 20 apothecier</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3674,10 +3509,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124901780</v>
+        <v>124900313</v>
       </c>
       <c r="B29" t="n">
-        <v>80028</v>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3705,14 +3540,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>599756</v>
+        <v>599854</v>
       </c>
       <c r="R29" t="n">
-        <v>6923823</v>
+        <v>6923776</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3744,7 +3579,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3754,7 +3589,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3769,61 +3604,57 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124901767</v>
+        <v>124900465</v>
       </c>
       <c r="B30" t="n">
-        <v>98269</v>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>599748</v>
+        <v>599856</v>
       </c>
       <c r="R30" t="n">
-        <v>6923842</v>
+        <v>6923803</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3855,7 +3686,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3865,7 +3696,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3880,12 +3711,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3895,7 +3726,7 @@
         <v>124900661</v>
       </c>
       <c r="B31" t="n">
-        <v>80028</v>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4002,7 +3833,7 @@
         <v>124900663</v>
       </c>
       <c r="B32" t="n">
-        <v>80028</v>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4106,10 +3937,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124900465</v>
+        <v>124900764</v>
       </c>
       <c r="B33" t="n">
-        <v>80028</v>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4141,10 +3972,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>599856</v>
+        <v>599814</v>
       </c>
       <c r="R33" t="n">
-        <v>6923803</v>
+        <v>6923824</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4176,7 +4007,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4186,7 +4017,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4213,10 +4044,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124900863</v>
+        <v>124901679</v>
       </c>
       <c r="B34" t="n">
-        <v>91166</v>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4224,21 +4055,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4248,10 +4079,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>599779</v>
+        <v>599728</v>
       </c>
       <c r="R34" t="n">
-        <v>6923783</v>
+        <v>6923812</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4283,7 +4114,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4293,7 +4124,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4320,10 +4151,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124899195</v>
+        <v>124901780</v>
       </c>
       <c r="B35" t="n">
-        <v>91166</v>
+        <v>80432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4331,21 +4162,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4355,10 +4186,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>599930</v>
+        <v>599756</v>
       </c>
       <c r="R35" t="n">
-        <v>6923840</v>
+        <v>6923823</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4390,7 +4221,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4400,7 +4231,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4427,45 +4258,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124898191</v>
+        <v>124901880</v>
       </c>
       <c r="B36" t="n">
-        <v>91833</v>
+        <v>80432</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>898</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>599930</v>
+        <v>599771</v>
       </c>
       <c r="R36" t="n">
-        <v>6923840</v>
+        <v>6923841</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4497,7 +4328,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4507,7 +4338,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på asp</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4522,22 +4358,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124897942</v>
+        <v>124901889</v>
       </c>
       <c r="B37" t="n">
-        <v>57741</v>
+        <v>80432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4545,39 +4381,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>599929</v>
+        <v>599775</v>
       </c>
       <c r="R37" t="n">
-        <v>6923847</v>
+        <v>6923855</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4609,7 +4440,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4619,12 +4450,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:43</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4639,60 +4465,60 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124899341</v>
+        <v>125685582</v>
       </c>
       <c r="B38" t="n">
-        <v>91131</v>
+        <v>80432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>599908</v>
+        <v>599906</v>
       </c>
       <c r="R38" t="n">
-        <v>6923811</v>
+        <v>6923816</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4716,22 +4542,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>16:23</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>16:23</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4746,57 +4562,57 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124902015</v>
+        <v>126717749</v>
       </c>
       <c r="B39" t="n">
-        <v>91166</v>
+        <v>80461</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>599777</v>
+        <v>599805</v>
       </c>
       <c r="R39" t="n">
-        <v>6923857</v>
+        <v>6923849</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4823,22 +4639,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>18:04</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>18:04</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4853,57 +4659,62 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124898316</v>
+        <v>124900786</v>
       </c>
       <c r="B40" t="n">
-        <v>91459</v>
+        <v>57950</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>599918</v>
+        <v>599791</v>
       </c>
       <c r="R40" t="n">
-        <v>6923822</v>
+        <v>6923786</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4935,7 +4746,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4945,7 +4756,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4960,57 +4771,62 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124899421</v>
+        <v>124900827</v>
       </c>
       <c r="B41" t="n">
-        <v>91166</v>
+        <v>57950</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>599899</v>
+        <v>599787</v>
       </c>
       <c r="R41" t="n">
-        <v>6923798</v>
+        <v>6923799</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5042,7 +4858,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5052,7 +4868,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5067,39 +4883,39 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124902509</v>
+        <v>124902557</v>
       </c>
       <c r="B42" t="n">
-        <v>57741</v>
+        <v>57950</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5110,7 +4926,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5119,10 +4935,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>599754</v>
+        <v>599750</v>
       </c>
       <c r="R42" t="n">
-        <v>6923921</v>
+        <v>6923919</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5154,7 +4970,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5164,12 +4980,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:29</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5196,49 +5007,50 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124902765</v>
+        <v>124897942</v>
       </c>
       <c r="B43" t="n">
-        <v>98269</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>599800</v>
+        <v>599929</v>
       </c>
       <c r="R43" t="n">
-        <v>6923959</v>
+        <v>6923847</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5270,7 +5082,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5280,7 +5092,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5295,22 +5112,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124902691</v>
+        <v>124898290</v>
       </c>
       <c r="B44" t="n">
-        <v>91184</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5318,34 +5135,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>599798</v>
+        <v>599911</v>
       </c>
       <c r="R44" t="n">
-        <v>6923975</v>
+        <v>6923836</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5377,7 +5199,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5387,7 +5209,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5402,22 +5229,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124898168</v>
+        <v>124898571</v>
       </c>
       <c r="B45" t="n">
-        <v>91459</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5425,34 +5252,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>599920</v>
+        <v>599904</v>
       </c>
       <c r="R45" t="n">
-        <v>6923834</v>
+        <v>6923812</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5484,7 +5316,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5494,7 +5326,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5509,49 +5346,50 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124899798</v>
+        <v>124899839</v>
       </c>
       <c r="B46" t="n">
-        <v>98269</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5560,10 +5398,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>599883</v>
+        <v>599893</v>
       </c>
       <c r="R46" t="n">
-        <v>6923782</v>
+        <v>6923773</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5595,7 +5433,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5605,7 +5443,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5620,22 +5463,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124900313</v>
+        <v>124902350</v>
       </c>
       <c r="B47" t="n">
-        <v>80028</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5643,34 +5486,58 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>599854</v>
+        <v>599899</v>
       </c>
       <c r="R47" t="n">
-        <v>6923776</v>
+        <v>6923798</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5702,7 +5569,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5712,7 +5579,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett hona födosöker I en gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5727,22 +5599,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124900226</v>
+        <v>124902509</v>
       </c>
       <c r="B48" t="n">
-        <v>80028</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5750,39 +5622,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>599882</v>
+        <v>599754</v>
       </c>
       <c r="R48" t="n">
-        <v>6923778</v>
+        <v>6923921</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5814,7 +5686,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5824,12 +5696,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Över 20 apothecier</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5844,57 +5716,66 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124899196</v>
+        <v>126717248</v>
       </c>
       <c r="B49" t="n">
-        <v>91617</v>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>599888</v>
+        <v>599930</v>
       </c>
       <c r="R49" t="n">
-        <v>6923798</v>
+        <v>6923840</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5921,22 +5802,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>16:25</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>16:25</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5951,61 +5822,66 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124900025</v>
+        <v>124902196</v>
       </c>
       <c r="B50" t="n">
-        <v>98269</v>
+        <v>57132</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>599878</v>
+        <v>599743</v>
       </c>
       <c r="R50" t="n">
-        <v>6923820</v>
+        <v>6923891</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6037,7 +5913,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6047,7 +5923,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6074,10 +5950,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124900362</v>
+        <v>124899798</v>
       </c>
       <c r="B51" t="n">
-        <v>98269</v>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6104,12 +5980,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6118,10 +5989,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>599864</v>
+        <v>599883</v>
       </c>
       <c r="R51" t="n">
-        <v>6923786</v>
+        <v>6923782</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6153,7 +6024,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6163,7 +6034,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6178,60 +6049,64 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125685122</v>
+        <v>124900025</v>
       </c>
       <c r="B52" t="n">
-        <v>91242</v>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>600013</v>
+        <v>599878</v>
       </c>
       <c r="R52" t="n">
-        <v>6923741</v>
+        <v>6923820</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6255,12 +6130,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6275,60 +6160,60 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125685582</v>
+        <v>124900055</v>
       </c>
       <c r="B53" t="n">
-        <v>80080</v>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>599906</v>
+        <v>599899</v>
       </c>
       <c r="R53" t="n">
-        <v>6923816</v>
+        <v>6923798</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6352,12 +6237,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6372,60 +6267,69 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125685127</v>
+        <v>124900294</v>
       </c>
       <c r="B54" t="n">
-        <v>91207</v>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>600027</v>
+        <v>599864</v>
       </c>
       <c r="R54" t="n">
-        <v>6923772</v>
+        <v>6923773</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6449,12 +6353,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6469,22 +6383,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125685866</v>
+        <v>124900362</v>
       </c>
       <c r="B55" t="n">
-        <v>98352</v>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6511,22 +6425,27 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
+          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>599803</v>
+        <v>599864</v>
       </c>
       <c r="R55" t="n">
-        <v>6923868</v>
+        <v>6923786</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6550,12 +6469,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6570,60 +6499,69 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125685402</v>
+        <v>124901624</v>
       </c>
       <c r="B56" t="n">
-        <v>91538</v>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>599900</v>
+        <v>599703</v>
       </c>
       <c r="R56" t="n">
-        <v>6923788</v>
+        <v>6923832</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6647,12 +6585,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6667,60 +6615,60 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125685331</v>
+        <v>124901634</v>
       </c>
       <c r="B57" t="n">
-        <v>88651</v>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Söderlundsintaget, Söderlundsintaget, Mpd</t>
+          <t>Backtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>599910</v>
+        <v>599734</v>
       </c>
       <c r="R57" t="n">
-        <v>6923817</v>
+        <v>6923810</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6744,12 +6692,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6764,60 +6722,64 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125686610</v>
+        <v>124901767</v>
       </c>
       <c r="B58" t="n">
-        <v>91253</v>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1205</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>599815</v>
+        <v>599748</v>
       </c>
       <c r="R58" t="n">
-        <v>6923786</v>
+        <v>6923842</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6841,12 +6803,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6861,22 +6833,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125686642</v>
+        <v>124901921</v>
       </c>
       <c r="B59" t="n">
-        <v>98352</v>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6903,7 +6875,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6912,13 +6889,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>599816</v>
+        <v>599742</v>
       </c>
       <c r="R59" t="n">
-        <v>6923786</v>
+        <v>6923857</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6942,12 +6919,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6962,57 +6949,61 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126717319</v>
+        <v>124901922</v>
       </c>
       <c r="B60" t="n">
-        <v>91622</v>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>599876</v>
+        <v>599783</v>
       </c>
       <c r="R60" t="n">
-        <v>6923905</v>
+        <v>6923858</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7039,12 +7030,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7059,57 +7060,61 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126717749</v>
+        <v>124902765</v>
       </c>
       <c r="B61" t="n">
-        <v>80146</v>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Svarttjärnsbäcken, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>599805</v>
+        <v>599800</v>
       </c>
       <c r="R61" t="n">
-        <v>6923849</v>
+        <v>6923959</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7136,12 +7141,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7156,69 +7171,64 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126717248</v>
+        <v>125685866</v>
       </c>
       <c r="B62" t="n">
-        <v>57657</v>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>599930</v>
+        <v>599803</v>
       </c>
       <c r="R62" t="n">
-        <v>6923840</v>
+        <v>6923868</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7242,12 +7252,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7262,60 +7272,64 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127945802</v>
+        <v>125686642</v>
       </c>
       <c r="B63" t="n">
-        <v>80152</v>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Backtjärnen, Mpd</t>
+          <t>Svarttjärnsbäcken, Svarttjärnsbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>599734</v>
+        <v>599816</v>
       </c>
       <c r="R63" t="n">
-        <v>6923810</v>
+        <v>6923786</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7339,12 +7353,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7359,44 +7373,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127946712</v>
+        <v>124898995</v>
       </c>
       <c r="B64" t="n">
-        <v>88865</v>
+        <v>97983</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>510</v>
+        <v>221945</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7406,10 +7420,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>599788</v>
+        <v>599930</v>
       </c>
       <c r="R64" t="n">
-        <v>6923908</v>
+        <v>6923840</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7436,12 +7450,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7468,10 +7492,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127944705</v>
+        <v>127939731</v>
       </c>
       <c r="B65" t="n">
-        <v>80152</v>
+        <v>97983</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7479,21 +7503,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229497</v>
+        <v>221945</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7565,10 +7589,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127939731</v>
+        <v>127944705</v>
       </c>
       <c r="B66" t="n">
-        <v>97460</v>
+        <v>80392</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7576,21 +7600,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221945</v>
+        <v>229497</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7659,6 +7683,103 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>127945802</v>
+      </c>
+      <c r="B67" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Backtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>599734</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6923810</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27027-2022 artfynd.xlsx
+++ b/artfynd/A 27027-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AZ67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125685331</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127946712</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124898168</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124898316</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124899564</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1324,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124900330</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1391,6 +1426,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125685402</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126717319</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1595,6 +1640,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124898191</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1702,6 +1752,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124898096</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1809,6 +1864,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124899421</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1916,6 +1976,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124899503</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2023,6 +2088,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124900863</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2130,6 +2200,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124902015</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2227,6 +2302,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125685122</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2324,6 +2404,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125686610</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2431,6 +2516,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124899196</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2538,6 +2628,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124899341</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2635,6 +2730,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125685127</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2747,6 +2847,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124898054</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2854,6 +2959,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124898060</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2961,6 +3071,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124899616</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3068,6 +3183,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124899644</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3175,6 +3295,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124900018</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3282,6 +3407,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124900773</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3389,6 +3519,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124902839</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3506,6 +3641,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124900226</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3613,6 +3753,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124900313</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3720,6 +3865,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124900465</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3827,6 +3977,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124900661</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3934,6 +4089,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124900663</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4041,6 +4201,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124900764</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4148,6 +4313,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124901679</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4255,6 +4425,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124901780</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4367,6 +4542,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124901880</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4474,6 +4654,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124901889</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4571,6 +4756,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125685582</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4668,6 +4858,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126717749</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4780,6 +4975,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124900786</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4892,6 +5092,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124900827</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5004,6 +5209,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124902557</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5121,6 +5331,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124897942</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5238,6 +5453,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124898290</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5355,6 +5575,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124898571</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5472,6 +5697,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124899839</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5608,6 +5838,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124902350</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5725,6 +5960,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124902509</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5831,6 +6071,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126717248</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5947,6 +6192,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124902196</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6058,6 +6308,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124899798</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6169,6 +6424,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124900025</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6276,6 +6536,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124900055</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6392,6 +6657,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124900294</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6508,6 +6778,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124900362</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6624,6 +6899,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124901624</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6731,6 +7011,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124901634</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6842,6 +7127,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124901767</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6958,6 +7248,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124901921</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7069,6 +7364,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124901922</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7180,6 +7480,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124902765</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7281,6 +7586,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125685866</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7382,6 +7692,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125686642</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7489,6 +7804,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124898995</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7586,6 +7906,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127939731</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7683,6 +8008,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127944705</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7780,8 +8110,81 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127945802</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>